--- a/AVIATIONprocessing/SliceVelocityValidation/SSWT_SliceUrmsValidation_FigureData.xlsx
+++ b/AVIATIONprocessing/SliceVelocityValidation/SSWT_SliceUrmsValidation_FigureData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Boller CFD\GitHub\CFDPostprocessingCodes\AVIATIONprocessing\SliceVelocityValidation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F19FEF12-8AC6-4020-8607-87A0D93C7C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA1DED03-C9D4-4429-B299-418F04867611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{12DF1E63-F8AF-48B4-87CD-AC55BD68FC80}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{12DF1E63-F8AF-48B4-87CD-AC55BD68FC80}"/>
   </bookViews>
   <sheets>
     <sheet name="xL=0.17" sheetId="1" r:id="rId1"/>
@@ -112,10 +112,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -438,22 +438,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3"/>
+      <c r="E2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3"/>
+      <c r="K2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="2"/>
+      <c r="L2" s="3"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
@@ -483,7 +483,7 @@
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4">
-        <v>3.1138648065765519E-2</v>
+        <v>2.9119886333881888E-2</v>
       </c>
       <c r="C4">
         <v>-1</v>
@@ -509,7 +509,7 @@
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5">
-        <v>7.033019652637168E-2</v>
+        <v>5.7853198931474045E-2</v>
       </c>
       <c r="C5">
         <v>-0.97979797979797989</v>
@@ -535,7 +535,7 @@
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6">
-        <v>8.1689885669428725E-2</v>
+        <v>6.2515446967269531E-2</v>
       </c>
       <c r="C6">
         <v>-0.95959595959595956</v>
@@ -561,7 +561,7 @@
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7">
-        <v>8.7608477714578803E-2</v>
+        <v>6.386508249900319E-2</v>
       </c>
       <c r="C7">
         <v>-0.93939393939393945</v>
@@ -587,7 +587,7 @@
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8">
-        <v>9.2184279502433644E-2</v>
+        <v>6.4796522951086039E-2</v>
       </c>
       <c r="C8">
         <v>-0.91919191919191912</v>
@@ -613,7 +613,7 @@
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9">
-        <v>9.5894944492481163E-2</v>
+        <v>6.5549535549429813E-2</v>
       </c>
       <c r="C9">
         <v>-0.89898989898989901</v>
@@ -639,7 +639,7 @@
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10">
-        <v>9.9077529970704611E-2</v>
+        <v>6.6141236628584205E-2</v>
       </c>
       <c r="C10">
         <v>-0.8787878787878789</v>
@@ -665,7 +665,7 @@
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11">
-        <v>0.10141100187625193</v>
+        <v>6.6001488430759273E-2</v>
       </c>
       <c r="C11">
         <v>-0.85858585858585856</v>
@@ -691,7 +691,7 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12">
-        <v>0.10347221751277993</v>
+        <v>6.5753317055203778E-2</v>
       </c>
       <c r="C12">
         <v>-0.83838383838383834</v>
@@ -717,7 +717,7 @@
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13">
-        <v>0.10546495171241245</v>
+        <v>6.5732697257002454E-2</v>
       </c>
       <c r="C13">
         <v>-0.81818181818181823</v>
@@ -743,7 +743,7 @@
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14">
-        <v>0.10692226796461321</v>
+        <v>6.5523131200451515E-2</v>
       </c>
       <c r="C14">
         <v>-0.79797979797979801</v>
@@ -769,7 +769,7 @@
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15">
-        <v>0.10778246027375667</v>
+        <v>6.4862496246998066E-2</v>
       </c>
       <c r="C15">
         <v>-0.77777777777777779</v>
@@ -795,7 +795,7 @@
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16">
-        <v>0.10842768529140395</v>
+        <v>6.4095102282604052E-2</v>
       </c>
       <c r="C16">
         <v>-0.75757575757575757</v>
@@ -821,7 +821,7 @@
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17">
-        <v>0.10921454812723137</v>
+        <v>6.3710995546894536E-2</v>
       </c>
       <c r="C17">
         <v>-0.73737373737373746</v>
@@ -847,7 +847,7 @@
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18">
-        <v>0.10942709691421307</v>
+        <v>6.284688023211224E-2</v>
       </c>
       <c r="C18">
         <v>-0.71717171717171713</v>
@@ -873,7 +873,7 @@
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19">
-        <v>0.10947618744944025</v>
+        <v>6.1993492278003846E-2</v>
       </c>
       <c r="C19">
         <v>-0.69696969696969702</v>
@@ -899,7 +899,7 @@
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20">
-        <v>0.10941471746365623</v>
+        <v>6.1240273462718979E-2</v>
       </c>
       <c r="C20">
         <v>-0.67676767676767691</v>
@@ -925,7 +925,7 @@
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21">
-        <v>0.10885778498680308</v>
+        <v>6.0395552427273173E-2</v>
       </c>
       <c r="C21">
         <v>-0.65656565656565657</v>
@@ -951,7 +951,7 @@
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22">
-        <v>0.10836664176782676</v>
+        <v>5.9636877990679085E-2</v>
       </c>
       <c r="C22">
         <v>-0.63636363636363646</v>
@@ -977,7 +977,7 @@
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23">
-        <v>0.10750282327439843</v>
+        <v>5.8620009274685095E-2</v>
       </c>
       <c r="C23">
         <v>-0.61616161616161613</v>
@@ -1003,7 +1003,7 @@
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24">
-        <v>0.10655380543680978</v>
+        <v>5.7863667684671799E-2</v>
       </c>
       <c r="C24">
         <v>-0.59595959595959602</v>
@@ -1029,7 +1029,7 @@
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25">
-        <v>0.10558969070904317</v>
+        <v>5.7341161078859455E-2</v>
       </c>
       <c r="C25">
         <v>-0.5757575757575758</v>
@@ -1055,7 +1055,7 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26">
-        <v>0.10433718490823464</v>
+        <v>5.6572981982397998E-2</v>
       </c>
       <c r="C26">
         <v>-0.55555555555555558</v>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27">
-        <v>0.10322013483343749</v>
+        <v>5.5976106114890262E-2</v>
       </c>
       <c r="C27">
         <v>-0.53535353535353536</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28">
-        <v>0.10187853474516621</v>
+        <v>5.5508157048618688E-2</v>
       </c>
       <c r="C28">
         <v>-0.51515151515151525</v>
@@ -1133,7 +1133,7 @@
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29">
-        <v>0.1005854160097269</v>
+        <v>5.5342078901293681E-2</v>
       </c>
       <c r="C29">
         <v>-0.49494949494949497</v>
@@ -1159,7 +1159,7 @@
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30">
-        <v>9.9218326956116196E-2</v>
+        <v>5.5019487261567752E-2</v>
       </c>
       <c r="C30">
         <v>-0.47474747474747486</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31">
-        <v>9.7871492443061633E-2</v>
+        <v>5.4824945239306734E-2</v>
       </c>
       <c r="C31">
         <v>-0.4545454545454547</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32">
-        <v>9.6350383385239644E-2</v>
+        <v>5.4633508459120676E-2</v>
       </c>
       <c r="C32">
         <v>-0.43434343434343459</v>
@@ -1225,7 +1225,7 @@
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33">
-        <v>9.4705434904405153E-2</v>
+        <v>5.4314204241503336E-2</v>
       </c>
       <c r="C33">
         <v>-0.41414141414141448</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34">
-        <v>9.2866322942450216E-2</v>
+        <v>5.3849020747014725E-2</v>
       </c>
       <c r="C34">
         <v>-0.39393939393939376</v>
@@ -1265,7 +1265,7 @@
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35">
-        <v>9.123231122783014E-2</v>
+        <v>5.3829115907301564E-2</v>
       </c>
       <c r="C35">
         <v>-0.37373737373737365</v>
@@ -1285,7 +1285,7 @@
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B36">
-        <v>8.943604619529151E-2</v>
+        <v>5.394296498977702E-2</v>
       </c>
       <c r="C36">
         <v>-0.35353535353535359</v>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B37">
-        <v>8.7597371491893131E-2</v>
+        <v>5.4036997328039522E-2</v>
       </c>
       <c r="C37">
         <v>-0.33333333333333348</v>
@@ -1325,7 +1325,7 @@
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38">
-        <v>8.5897298618371878E-2</v>
+        <v>5.4387865482130961E-2</v>
       </c>
       <c r="C38">
         <v>-0.31313131313131337</v>
@@ -1345,7 +1345,7 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39">
-        <v>8.4536020670700748E-2</v>
+        <v>5.5190648252833499E-2</v>
       </c>
       <c r="C39">
         <v>-0.29292929292929265</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B40">
-        <v>8.3174617514663193E-2</v>
+        <v>5.5767481595421546E-2</v>
       </c>
       <c r="C40">
         <v>-0.27272727272727254</v>
@@ -1385,7 +1385,7 @@
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B41">
-        <v>8.1507544594199635E-2</v>
+        <v>5.6131930343261222E-2</v>
       </c>
       <c r="C41">
         <v>-0.25252525252525243</v>
@@ -1405,7 +1405,7 @@
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B42">
-        <v>8.001822620788579E-2</v>
+        <v>5.6763584989821508E-2</v>
       </c>
       <c r="C42">
         <v>-0.23232323232323229</v>
@@ -1425,7 +1425,7 @@
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B43">
-        <v>7.884744802745515E-2</v>
+        <v>5.8045006680216095E-2</v>
       </c>
       <c r="C43">
         <v>-0.21212121212121227</v>
@@ -1445,7 +1445,7 @@
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B44">
-        <v>7.7250137357710802E-2</v>
+        <v>5.9042845951885838E-2</v>
       </c>
       <c r="C44">
         <v>-0.19191919191919213</v>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B45">
-        <v>7.5305013967195022E-2</v>
+        <v>6.0484721163454887E-2</v>
       </c>
       <c r="C45">
         <v>-0.17171717171717202</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B46">
-        <v>7.3923155213043948E-2</v>
+        <v>6.3956899141127857E-2</v>
       </c>
       <c r="C46">
         <v>-0.15151515151515133</v>
@@ -1505,7 +1505,7 @@
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B47">
-        <v>7.4179210104070858E-2</v>
+        <v>7.0460439134918659E-2</v>
       </c>
       <c r="C47">
         <v>-0.13131313131313119</v>
@@ -1525,7 +1525,7 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B48">
-        <v>8.0683439540609247E-2</v>
+        <v>8.0627393430383873E-2</v>
       </c>
       <c r="C48">
         <v>-0.11111111111111106</v>
@@ -1545,7 +1545,7 @@
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B49">
-        <v>0.10774421987086492</v>
+        <v>9.6917816554101865E-2</v>
       </c>
       <c r="C49">
         <v>-9.0909090909090939E-2</v>
@@ -1565,7 +1565,7 @@
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B50">
-        <v>0.16153799578397232</v>
+        <v>0.1163382307427837</v>
       </c>
       <c r="C50">
         <v>-7.0707070707070815E-2</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B51">
-        <v>0.23756324727115982</v>
+        <v>0.13438622446840162</v>
       </c>
       <c r="C51">
         <v>-5.0505050505050691E-2</v>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B52">
-        <v>0.32909762220965488</v>
+        <v>0.14313797164805722</v>
       </c>
       <c r="C52">
         <v>-3.0303030303030564E-2</v>
@@ -1625,7 +1625,7 @@
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B53">
-        <v>0.43304285552457278</v>
+        <v>0.14799954701129869</v>
       </c>
       <c r="C53">
         <v>-1.0101010101010064E-2</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B54">
-        <v>0.53851812527446763</v>
+        <v>0.14664729612669164</v>
       </c>
       <c r="C54">
         <v>1.0101010101010064E-2</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B55">
-        <v>0.6307210419731677</v>
+        <v>0.12907826373911335</v>
       </c>
       <c r="C55">
         <v>3.0303030303030189E-2</v>
@@ -1685,7 +1685,7 @@
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56">
-        <v>0.69872169222578073</v>
+        <v>0.10382471919191398</v>
       </c>
       <c r="C56">
         <v>5.0505050505050317E-2</v>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B57">
-        <v>0.74227865728454057</v>
+        <v>8.4868812904935823E-2</v>
       </c>
       <c r="C57">
         <v>7.0707070707070441E-2</v>
@@ -1725,7 +1725,7 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B58">
-        <v>0.76936928564830942</v>
+        <v>7.5704915393507058E-2</v>
       </c>
       <c r="C58">
         <v>9.0909090909091134E-2</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B59">
-        <v>0.78844718489984156</v>
+        <v>7.0747367300967354E-2</v>
       </c>
       <c r="C59">
         <v>0.11111111111111126</v>
@@ -1765,7 +1765,7 @@
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B60">
-        <v>0.80415918823100718</v>
+        <v>6.8128596813771869E-2</v>
       </c>
       <c r="C60">
         <v>0.13131313131313138</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61">
-        <v>0.8183122724263554</v>
+        <v>6.67518803444654E-2</v>
       </c>
       <c r="C61">
         <v>0.15151515151515152</v>
@@ -1805,7 +1805,7 @@
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62">
-        <v>0.83190437335926315</v>
+        <v>6.6106599126586341E-2</v>
       </c>
       <c r="C62">
         <v>0.17171717171717163</v>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63">
-        <v>0.84385409026111013</v>
+        <v>6.3526367646113566E-2</v>
       </c>
       <c r="C63">
         <v>0.19191919191919177</v>
@@ -1845,7 +1845,7 @@
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B64">
-        <v>0.85483037069494683</v>
+        <v>6.2157147757139777E-2</v>
       </c>
       <c r="C64">
         <v>0.21212121212121246</v>
@@ -1865,7 +1865,7 @@
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B65">
-        <v>0.86562074558351143</v>
+        <v>6.070908933823467E-2</v>
       </c>
       <c r="C65">
         <v>0.23232323232323202</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B66">
-        <v>0.87535864365856741</v>
+        <v>5.9443606406672074E-2</v>
       </c>
       <c r="C66">
         <v>0.25252525252525215</v>
@@ -1905,7 +1905,7 @@
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B67">
-        <v>0.88469535831053181</v>
+        <v>5.7211983738918309E-2</v>
       </c>
       <c r="C67">
         <v>0.27272727272727226</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68">
-        <v>0.89370012256832609</v>
+        <v>5.5722858036787906E-2</v>
       </c>
       <c r="C68">
         <v>0.29292929292929332</v>
@@ -1945,7 +1945,7 @@
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69">
-        <v>0.90206196808272021</v>
+        <v>5.4604547930432894E-2</v>
       </c>
       <c r="C69">
         <v>0.31313131313131348</v>
@@ -1965,7 +1965,7 @@
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70">
-        <v>0.9101889449554782</v>
+        <v>5.2955255399552932E-2</v>
       </c>
       <c r="C70">
         <v>0.33333333333333359</v>
@@ -1985,7 +1985,7 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B71">
-        <v>0.91798530661813282</v>
+        <v>5.1361908197476165E-2</v>
       </c>
       <c r="C71">
         <v>0.35353535353535315</v>
@@ -1999,7 +1999,7 @@
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B72">
-        <v>0.9257496414394768</v>
+        <v>5.0360695872077803E-2</v>
       </c>
       <c r="C72">
         <v>0.37373737373737326</v>
@@ -2013,7 +2013,7 @@
     </row>
     <row r="73" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B73">
-        <v>0.93359801152791444</v>
+        <v>4.9663529544552804E-2</v>
       </c>
       <c r="C73">
         <v>0.39393939393939398</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74">
-        <v>0.9415093716808921</v>
+        <v>4.8303481655199085E-2</v>
       </c>
       <c r="C74">
         <v>0.41414141414141464</v>
@@ -2041,7 +2041,7 @@
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B75">
-        <v>0.9490574055961154</v>
+        <v>4.6932037024808845E-2</v>
       </c>
       <c r="C75">
         <v>0.4343434343434342</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B76">
-        <v>0.95626788197170476</v>
+        <v>4.53527798009353E-2</v>
       </c>
       <c r="C76">
         <v>0.45454545454545492</v>
@@ -2069,7 +2069,7 @@
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77">
-        <v>0.96296484883429267</v>
+        <v>4.372944713408574E-2</v>
       </c>
       <c r="C77">
         <v>0.47474747474747503</v>
@@ -2083,7 +2083,7 @@
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78">
-        <v>0.96873555372688491</v>
+        <v>4.191833962967248E-2</v>
       </c>
       <c r="C78">
         <v>0.49494949494949514</v>
@@ -2097,7 +2097,7 @@
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B79">
-        <v>0.97402013139601729</v>
+        <v>4.0346217441907695E-2</v>
       </c>
       <c r="C79">
         <v>0.51515151515151525</v>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B80">
-        <v>0.9790439839722771</v>
+        <v>3.921590479419023E-2</v>
       </c>
       <c r="C80">
         <v>0.53535353535353536</v>
@@ -2125,7 +2125,7 @@
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81">
-        <v>0.98389671107404031</v>
+        <v>3.8027273733670819E-2</v>
       </c>
       <c r="C81">
         <v>0.55555555555555558</v>
@@ -2139,7 +2139,7 @@
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B82">
-        <v>0.98868978494300186</v>
+        <v>3.6629511604344939E-2</v>
       </c>
       <c r="C82">
         <v>0.57575757575757602</v>
@@ -2153,7 +2153,7 @@
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B83">
-        <v>0.99364922265426792</v>
+        <v>3.526092673283588E-2</v>
       </c>
       <c r="C83">
         <v>0.59595959595959558</v>
@@ -2167,7 +2167,7 @@
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B84">
-        <v>0.99839063632566616</v>
+        <v>3.3932600268470996E-2</v>
       </c>
       <c r="C84">
         <v>0.61616161616161624</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85">
-        <v>1.0027429558239567</v>
+        <v>3.2311626811776829E-2</v>
       </c>
       <c r="C85">
         <v>0.63636363636363646</v>
@@ -2195,7 +2195,7 @@
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B86">
-        <v>1.0067990756688607</v>
+        <v>3.0567011836942361E-2</v>
       </c>
       <c r="C86">
         <v>0.65656565656565657</v>
@@ -2209,7 +2209,7 @@
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B87">
-        <v>1.0104824627845985</v>
+        <v>2.8890148589466078E-2</v>
       </c>
       <c r="C87">
         <v>0.67676767676767668</v>
@@ -2223,7 +2223,7 @@
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B88">
-        <v>1.0137780631927706</v>
+        <v>2.7312029175582592E-2</v>
       </c>
       <c r="C88">
         <v>0.69696969696969702</v>
@@ -2237,7 +2237,7 @@
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B89">
-        <v>1.0166119715985056</v>
+        <v>2.5539903851292955E-2</v>
       </c>
       <c r="C89">
         <v>0.71717171717171713</v>
@@ -2251,7 +2251,7 @@
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B90">
-        <v>1.0190130432851698</v>
+        <v>2.3848643482932176E-2</v>
       </c>
       <c r="C90">
         <v>0.73737373737373757</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B91">
-        <v>1.0210017718298705</v>
+        <v>2.2206163939306141E-2</v>
       </c>
       <c r="C91">
         <v>0.75757575757575701</v>
@@ -2279,7 +2279,7 @@
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B92">
-        <v>1.0225915976817332</v>
+        <v>2.0799807150753417E-2</v>
       </c>
       <c r="C92">
         <v>0.7777777777777779</v>
@@ -2293,7 +2293,7 @@
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B93">
-        <v>1.0236696798362097</v>
+        <v>1.9461750846400935E-2</v>
       </c>
       <c r="C93">
         <v>0.79797979797979801</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B94">
-        <v>1.0243939060247604</v>
+        <v>1.8274553043042506E-2</v>
       </c>
       <c r="C94">
         <v>0.81818181818181812</v>
@@ -2321,7 +2321,7 @@
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B95">
-        <v>1.0247500883427625</v>
+        <v>1.7360369557850967E-2</v>
       </c>
       <c r="C95">
         <v>0.83838383838383823</v>
@@ -2335,7 +2335,7 @@
     </row>
     <row r="96" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B96">
-        <v>1.0248078237189948</v>
+        <v>1.6541576328256615E-2</v>
       </c>
       <c r="C96">
         <v>0.85858585858585879</v>
@@ -2349,7 +2349,7 @@
     </row>
     <row r="97" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B97">
-        <v>1.0245924819189793</v>
+        <v>1.5858445415699193E-2</v>
       </c>
       <c r="C97">
         <v>0.8787878787878789</v>
@@ -2363,7 +2363,7 @@
     </row>
     <row r="98" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B98">
-        <v>1.0241250895804599</v>
+        <v>1.5337030977888385E-2</v>
       </c>
       <c r="C98">
         <v>0.89898989898989901</v>
@@ -2377,7 +2377,7 @@
     </row>
     <row r="99" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B99">
-        <v>1.0234575979348604</v>
+        <v>1.4898627883524784E-2</v>
       </c>
       <c r="C99">
         <v>0.91919191919191912</v>
@@ -2391,7 +2391,7 @@
     </row>
     <row r="100" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B100">
-        <v>1.0226119646882963</v>
+        <v>1.4528087903556542E-2</v>
       </c>
       <c r="C100">
         <v>0.93939393939393923</v>
@@ -2405,7 +2405,7 @@
     </row>
     <row r="101" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B101">
-        <v>1.0216356620370775</v>
+        <v>1.4198645349569642E-2</v>
       </c>
       <c r="C101">
         <v>0.95959595959596011</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="102" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B102">
-        <v>1.0205295270264658</v>
+        <v>1.3916392664225265E-2</v>
       </c>
       <c r="C102">
         <v>0.97979797979797989</v>
@@ -2433,7 +2433,7 @@
     </row>
     <row r="103" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B103">
-        <v>1.0193215547911978</v>
+        <v>1.3647747558787851E-2</v>
       </c>
       <c r="C103">
         <v>1</v>
@@ -5677,23 +5677,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3"/>
+      <c r="E2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="2"/>
+      <c r="F2" s="3"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3"/>
+      <c r="K2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="2"/>
+      <c r="L2" s="3"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
@@ -5723,7 +5723,7 @@
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4">
-        <v>7.7755499400935096E-2</v>
+        <v>4.6961075841112677E-2</v>
       </c>
       <c r="C4">
         <v>-1</v>
@@ -5749,7 +5749,7 @@
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5">
-        <v>0.15093548685354294</v>
+        <v>6.663887043102272E-2</v>
       </c>
       <c r="C5">
         <v>-0.97979797979797989</v>
@@ -5775,7 +5775,7 @@
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6">
-        <v>0.17048069023593257</v>
+        <v>6.934838049222615E-2</v>
       </c>
       <c r="C6">
         <v>-0.95959595959595956</v>
@@ -5801,7 +5801,7 @@
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7">
-        <v>0.17698067423790273</v>
+        <v>6.8336716433016975E-2</v>
       </c>
       <c r="C7">
         <v>-0.93939393939393945</v>
@@ -5827,7 +5827,7 @@
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8">
-        <v>0.1793198665397428</v>
+        <v>6.7556384376060777E-2</v>
       </c>
       <c r="C8">
         <v>-0.91919191919191912</v>
@@ -5853,7 +5853,7 @@
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9">
-        <v>0.1798514218065059</v>
+        <v>6.712611518320967E-2</v>
       </c>
       <c r="C9">
         <v>-0.89898989898989901</v>
@@ -5879,7 +5879,7 @@
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10">
-        <v>0.17917472715304436</v>
+        <v>6.6488464946394862E-2</v>
       </c>
       <c r="C10">
         <v>-0.8787878787878789</v>
@@ -5905,7 +5905,7 @@
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11">
-        <v>0.17769648854212233</v>
+        <v>6.5862828560852113E-2</v>
       </c>
       <c r="C11">
         <v>-0.85858585858585856</v>
@@ -5931,7 +5931,7 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12">
-        <v>0.17631550495086037</v>
+        <v>6.6227034766301443E-2</v>
       </c>
       <c r="C12">
         <v>-0.83838383838383834</v>
@@ -5957,7 +5957,7 @@
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13">
-        <v>0.17484265836357091</v>
+        <v>6.6754752202287743E-2</v>
       </c>
       <c r="C13">
         <v>-0.81818181818181823</v>
@@ -5983,7 +5983,7 @@
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14">
-        <v>0.17304954508595072</v>
+        <v>6.7469440871327058E-2</v>
       </c>
       <c r="C14">
         <v>-0.79797979797979801</v>
@@ -6009,7 +6009,7 @@
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15">
-        <v>0.17090210243441786</v>
+        <v>6.7659251418934696E-2</v>
       </c>
       <c r="C15">
         <v>-0.77777777777777779</v>
@@ -6035,7 +6035,7 @@
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16">
-        <v>0.16893270558624915</v>
+        <v>6.8603683093068427E-2</v>
       </c>
       <c r="C16">
         <v>-0.75757575757575757</v>
@@ -6061,7 +6061,7 @@
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17">
-        <v>0.16640486957155692</v>
+        <v>6.9581663025162846E-2</v>
       </c>
       <c r="C17">
         <v>-0.73737373737373746</v>
@@ -6087,7 +6087,7 @@
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18">
-        <v>0.16339696213682117</v>
+        <v>6.9680547435050061E-2</v>
       </c>
       <c r="C18">
         <v>-0.71717171717171713</v>
@@ -6113,7 +6113,7 @@
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19">
-        <v>0.16056017739614467</v>
+        <v>6.9988086523266921E-2</v>
       </c>
       <c r="C19">
         <v>-0.69696969696969702</v>
@@ -6139,7 +6139,7 @@
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20">
-        <v>0.15727427709991137</v>
+        <v>7.0434320953680296E-2</v>
       </c>
       <c r="C20">
         <v>-0.67676767676767691</v>
@@ -6165,7 +6165,7 @@
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21">
-        <v>0.15378785846591556</v>
+        <v>7.0923810717923585E-2</v>
       </c>
       <c r="C21">
         <v>-0.65656565656565657</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22">
-        <v>0.15021312543888285</v>
+        <v>7.1033081878632193E-2</v>
       </c>
       <c r="C22">
         <v>-0.63636363636363646</v>
@@ -6217,7 +6217,7 @@
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23">
-        <v>0.14635798780740661</v>
+        <v>7.1112025540555818E-2</v>
       </c>
       <c r="C23">
         <v>-0.61616161616161613</v>
@@ -6243,7 +6243,7 @@
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24">
-        <v>0.14217712859355275</v>
+        <v>7.1384753912039425E-2</v>
       </c>
       <c r="C24">
         <v>-0.59595959595959602</v>
@@ -6269,7 +6269,7 @@
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25">
-        <v>0.13794687670667899</v>
+        <v>7.1693534908625942E-2</v>
       </c>
       <c r="C25">
         <v>-0.5757575757575758</v>
@@ -6295,7 +6295,7 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26">
-        <v>0.1334764157961274</v>
+        <v>7.2007527519019246E-2</v>
       </c>
       <c r="C26">
         <v>-0.55555555555555558</v>
@@ -6321,7 +6321,7 @@
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27">
-        <v>0.12878811693618095</v>
+        <v>7.2116445989499636E-2</v>
       </c>
       <c r="C27">
         <v>-0.53535353535353536</v>
@@ -6347,7 +6347,7 @@
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28">
-        <v>0.12412643075259588</v>
+        <v>7.2367557805038993E-2</v>
       </c>
       <c r="C28">
         <v>-0.51515151515151525</v>
@@ -6373,7 +6373,7 @@
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29">
-        <v>0.11980627559198921</v>
+        <v>7.2760566990405076E-2</v>
       </c>
       <c r="C29">
         <v>-0.49494949494949497</v>
@@ -6399,7 +6399,7 @@
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30">
-        <v>0.11513413592787432</v>
+        <v>7.2896355053347447E-2</v>
       </c>
       <c r="C30">
         <v>-0.47474747474747486</v>
@@ -6425,7 +6425,7 @@
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31">
-        <v>0.11052553986547341</v>
+        <v>7.3517238667375806E-2</v>
       </c>
       <c r="C31">
         <v>-0.4545454545454547</v>
@@ -6451,7 +6451,7 @@
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32">
-        <v>0.10557954518358972</v>
+        <v>7.3791552757300427E-2</v>
       </c>
       <c r="C32">
         <v>-0.43434343434343459</v>
@@ -6471,7 +6471,7 @@
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33">
-        <v>0.1005057724152979</v>
+        <v>7.3904831190356138E-2</v>
       </c>
       <c r="C33">
         <v>-0.41414141414141448</v>
@@ -6491,7 +6491,7 @@
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34">
-        <v>9.5869658823294637E-2</v>
+        <v>7.4632175284737395E-2</v>
       </c>
       <c r="C34">
         <v>-0.39393939393939376</v>
@@ -6511,7 +6511,7 @@
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35">
-        <v>9.1253659552938488E-2</v>
+        <v>7.5549096064996546E-2</v>
       </c>
       <c r="C35">
         <v>-0.37373737373737365</v>
@@ -6531,7 +6531,7 @@
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B36">
-        <v>8.7194826388169402E-2</v>
+        <v>7.7100118785124003E-2</v>
       </c>
       <c r="C36">
         <v>-0.35353535353535359</v>
@@ -6551,7 +6551,7 @@
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B37">
-        <v>8.3886237685728574E-2</v>
+        <v>7.8579170676090868E-2</v>
       </c>
       <c r="C37">
         <v>-0.33333333333333348</v>
@@ -6571,7 +6571,7 @@
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38">
-        <v>8.3001518591814316E-2</v>
+        <v>8.1333948564899908E-2</v>
       </c>
       <c r="C38">
         <v>-0.31313131313131337</v>
@@ -6591,7 +6591,7 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39">
-        <v>8.5402409571081306E-2</v>
+        <v>8.5390277449613472E-2</v>
       </c>
       <c r="C39">
         <v>-0.29292929292929265</v>
@@ -6611,7 +6611,7 @@
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B40">
-        <v>9.1382998571473459E-2</v>
+        <v>8.9923678279897751E-2</v>
       </c>
       <c r="C40">
         <v>-0.27272727272727254</v>
@@ -6631,7 +6631,7 @@
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B41">
-        <v>0.10215524477167356</v>
+        <v>9.5275620271896969E-2</v>
       </c>
       <c r="C41">
         <v>-0.25252525252525243</v>
@@ -6651,7 +6651,7 @@
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B42">
-        <v>0.11806064482469486</v>
+        <v>0.10152126282927722</v>
       </c>
       <c r="C42">
         <v>-0.23232323232323229</v>
@@ -6671,7 +6671,7 @@
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B43">
-        <v>0.13983694107230057</v>
+        <v>0.10954313300048318</v>
       </c>
       <c r="C43">
         <v>-0.21212121212121227</v>
@@ -6691,7 +6691,7 @@
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B44">
-        <v>0.16453393420985288</v>
+        <v>0.11605865087870264</v>
       </c>
       <c r="C44">
         <v>-0.19191919191919213</v>
@@ -6711,7 +6711,7 @@
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B45">
-        <v>0.19334201025080922</v>
+        <v>0.12250708578062242</v>
       </c>
       <c r="C45">
         <v>-0.17171717171717202</v>
@@ -6731,7 +6731,7 @@
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B46">
-        <v>0.22644827404019469</v>
+        <v>0.13000866362490696</v>
       </c>
       <c r="C46">
         <v>-0.15151515151515133</v>
@@ -6751,7 +6751,7 @@
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B47">
-        <v>0.26275508660492236</v>
+        <v>0.13752326262805648</v>
       </c>
       <c r="C47">
         <v>-0.13131313131313119</v>
@@ -6771,7 +6771,7 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B48">
-        <v>0.30112732270927495</v>
+        <v>0.14167178251253704</v>
       </c>
       <c r="C48">
         <v>-0.11111111111111106</v>
@@ -6791,7 +6791,7 @@
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B49">
-        <v>0.34296213250894453</v>
+        <v>0.14542127663145676</v>
       </c>
       <c r="C49">
         <v>-9.0909090909090939E-2</v>
@@ -6811,7 +6811,7 @@
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B50">
-        <v>0.38780795082594594</v>
+        <v>0.14969256142797363</v>
       </c>
       <c r="C50">
         <v>-7.0707070707070815E-2</v>
@@ -6831,7 +6831,7 @@
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B51">
-        <v>0.43404997195365519</v>
+        <v>0.15268643671162074</v>
       </c>
       <c r="C51">
         <v>-5.0505050505050691E-2</v>
@@ -6851,7 +6851,7 @@
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B52">
-        <v>0.4824031485792411</v>
+        <v>0.1512068047575611</v>
       </c>
       <c r="C52">
         <v>-3.0303030303030564E-2</v>
@@ -6871,7 +6871,7 @@
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B53">
-        <v>0.53278239741577893</v>
+        <v>0.14967135596548112</v>
       </c>
       <c r="C53">
         <v>-1.0101010101010064E-2</v>
@@ -6891,7 +6891,7 @@
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B54">
-        <v>0.58400333151243455</v>
+        <v>0.14749608633767364</v>
       </c>
       <c r="C54">
         <v>1.0101010101010064E-2</v>
@@ -6911,7 +6911,7 @@
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B55">
-        <v>0.63249994054401293</v>
+        <v>0.14058908984956506</v>
       </c>
       <c r="C55">
         <v>3.0303030303030189E-2</v>
@@ -6931,7 +6931,7 @@
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56">
-        <v>0.67846144441658185</v>
+        <v>0.13052489818859497</v>
       </c>
       <c r="C56">
         <v>5.0505050505050317E-2</v>
@@ -6951,7 +6951,7 @@
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B57">
-        <v>0.71936166391033074</v>
+        <v>0.11926818710355182</v>
       </c>
       <c r="C57">
         <v>7.0707070707070441E-2</v>
@@ -6971,7 +6971,7 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B58">
-        <v>0.75486114244540459</v>
+        <v>0.10847390038829119</v>
       </c>
       <c r="C58">
         <v>9.0909090909091134E-2</v>
@@ -6991,7 +6991,7 @@
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B59">
-        <v>0.78444083813939391</v>
+        <v>9.4752629863115875E-2</v>
       </c>
       <c r="C59">
         <v>0.11111111111111126</v>
@@ -7011,7 +7011,7 @@
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B60">
-        <v>0.8081795960819711</v>
+        <v>8.2835780858275962E-2</v>
       </c>
       <c r="C60">
         <v>0.13131313131313138</v>
@@ -7031,7 +7031,7 @@
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61">
-        <v>0.82689989173479406</v>
+        <v>7.4574032378645558E-2</v>
       </c>
       <c r="C61">
         <v>0.15151515151515152</v>
@@ -7051,7 +7051,7 @@
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62">
-        <v>0.84219171100779333</v>
+        <v>6.9495212033879275E-2</v>
       </c>
       <c r="C62">
         <v>0.17171717171717163</v>
@@ -7071,7 +7071,7 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63">
-        <v>0.85537657606725848</v>
+        <v>6.5091752440096864E-2</v>
       </c>
       <c r="C63">
         <v>0.19191919191919177</v>
@@ -7091,7 +7091,7 @@
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B64">
-        <v>0.86703038846947578</v>
+        <v>6.2071719102701539E-2</v>
       </c>
       <c r="C64">
         <v>0.21212121212121246</v>
@@ -7111,7 +7111,7 @@
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B65">
-        <v>0.87744898399191584</v>
+        <v>6.0324390406559007E-2</v>
       </c>
       <c r="C65">
         <v>0.23232323232323202</v>
@@ -7131,7 +7131,7 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B66">
-        <v>0.88734600686681275</v>
+        <v>5.8779303302153633E-2</v>
       </c>
       <c r="C66">
         <v>0.25252525252525215</v>
@@ -7151,7 +7151,7 @@
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B67">
-        <v>0.89665473137197604</v>
+        <v>5.681638794871248E-2</v>
       </c>
       <c r="C67">
         <v>0.27272727272727226</v>
@@ -7171,7 +7171,7 @@
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68">
-        <v>0.90566402901843668</v>
+        <v>5.5035222558894759E-2</v>
       </c>
       <c r="C68">
         <v>0.29292929292929332</v>
@@ -7191,7 +7191,7 @@
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69">
-        <v>0.91426660366538992</v>
+        <v>5.3740160887369111E-2</v>
       </c>
       <c r="C69">
         <v>0.31313131313131348</v>
@@ -7211,7 +7211,7 @@
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70">
-        <v>0.92216842740295668</v>
+        <v>5.2115634560732101E-2</v>
       </c>
       <c r="C70">
         <v>0.33333333333333359</v>
@@ -7231,7 +7231,7 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B71">
-        <v>0.92985936236489786</v>
+        <v>5.0403228136734084E-2</v>
       </c>
       <c r="C71">
         <v>0.35353535353535315</v>
@@ -7251,7 +7251,7 @@
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B72">
-        <v>0.93742890803596313</v>
+        <v>4.9191366443633602E-2</v>
       </c>
       <c r="C72">
         <v>0.37373737373737326</v>
@@ -7271,7 +7271,7 @@
     </row>
     <row r="73" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B73">
-        <v>0.94439167408498681</v>
+        <v>4.8246242274796756E-2</v>
       </c>
       <c r="C73">
         <v>0.39393939393939398</v>
@@ -7291,7 +7291,7 @@
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74">
-        <v>0.95128266693094055</v>
+        <v>4.6375369786087861E-2</v>
       </c>
       <c r="C74">
         <v>0.41414141414141464</v>
@@ -7311,7 +7311,7 @@
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B75">
-        <v>0.95783901449452047</v>
+        <v>4.4900660386367808E-2</v>
       </c>
       <c r="C75">
         <v>0.4343434343434342</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B76">
-        <v>0.9642833696744475</v>
+        <v>4.3678372449187534E-2</v>
       </c>
       <c r="C76">
         <v>0.45454545454545492</v>
@@ -7351,7 +7351,7 @@
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77">
-        <v>0.97035884664650074</v>
+        <v>4.2744816014891301E-2</v>
       </c>
       <c r="C77">
         <v>0.47474747474747503</v>
@@ -7371,7 +7371,7 @@
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78">
-        <v>0.97614855808286904</v>
+        <v>4.1166710077335938E-2</v>
       </c>
       <c r="C78">
         <v>0.49494949494949514</v>
@@ -7391,7 +7391,7 @@
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B79">
-        <v>0.9817027647683263</v>
+        <v>3.9947180174098915E-2</v>
       </c>
       <c r="C79">
         <v>0.51515151515151525</v>
@@ -7411,7 +7411,7 @@
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B80">
-        <v>0.98702698844111547</v>
+        <v>3.8593468573903472E-2</v>
       </c>
       <c r="C80">
         <v>0.53535353535353536</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81">
-        <v>0.99209294821905958</v>
+        <v>3.7400073582826848E-2</v>
       </c>
       <c r="C81">
         <v>0.55555555555555558</v>
@@ -7451,7 +7451,7 @@
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B82">
-        <v>0.99681064446065337</v>
+        <v>3.5788861941683833E-2</v>
       </c>
       <c r="C82">
         <v>0.57575757575757602</v>
@@ -7471,7 +7471,7 @@
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B83">
-        <v>1.0011508045922946</v>
+        <v>3.4376426605138947E-2</v>
       </c>
       <c r="C83">
         <v>0.59595959595959558</v>
@@ -7491,7 +7491,7 @@
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B84">
-        <v>1.0052426127991752</v>
+        <v>3.2947412035330477E-2</v>
       </c>
       <c r="C84">
         <v>0.61616161616161624</v>
@@ -7511,7 +7511,7 @@
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85">
-        <v>1.0090174506879739</v>
+        <v>3.1375802153822449E-2</v>
       </c>
       <c r="C85">
         <v>0.63636363636363646</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B86">
-        <v>1.0124825426308326</v>
+        <v>2.9725335102851067E-2</v>
       </c>
       <c r="C86">
         <v>0.65656565656565657</v>
@@ -7545,7 +7545,7 @@
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B87">
-        <v>1.0155905754003804</v>
+        <v>2.8162289201994626E-2</v>
       </c>
       <c r="C87">
         <v>0.67676767676767668</v>
@@ -7559,7 +7559,7 @@
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B88">
-        <v>1.0182753781052618</v>
+        <v>2.6688640484431869E-2</v>
       </c>
       <c r="C88">
         <v>0.69696969696969702</v>
@@ -7573,7 +7573,7 @@
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B89">
-        <v>1.0205062860594409</v>
+        <v>2.5087861211771787E-2</v>
       </c>
       <c r="C89">
         <v>0.71717171717171713</v>
@@ -7587,7 +7587,7 @@
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B90">
-        <v>1.0222580494595737</v>
+        <v>2.3545904988847635E-2</v>
       </c>
       <c r="C90">
         <v>0.73737373737373757</v>
@@ -7601,7 +7601,7 @@
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B91">
-        <v>1.0236689195708157</v>
+        <v>2.2038273592147176E-2</v>
       </c>
       <c r="C91">
         <v>0.75757575757575701</v>
@@ -7615,7 +7615,7 @@
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B92">
-        <v>1.0247430871938672</v>
+        <v>2.0780286730030142E-2</v>
       </c>
       <c r="C92">
         <v>0.7777777777777779</v>
@@ -7629,7 +7629,7 @@
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B93">
-        <v>1.0254783239648497</v>
+        <v>1.9589569037040965E-2</v>
       </c>
       <c r="C93">
         <v>0.79797979797979801</v>
@@ -7643,7 +7643,7 @@
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B94">
-        <v>1.0258901235651385</v>
+        <v>1.8481751045771599E-2</v>
       </c>
       <c r="C94">
         <v>0.81818181818181812</v>
@@ -7657,7 +7657,7 @@
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B95">
-        <v>1.0259854267718351</v>
+        <v>1.7648374042361498E-2</v>
       </c>
       <c r="C95">
         <v>0.83838383838383823</v>
@@ -7671,7 +7671,7 @@
     </row>
     <row r="96" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B96">
-        <v>1.0257929013772205</v>
+        <v>1.6785917316417941E-2</v>
       </c>
       <c r="C96">
         <v>0.85858585858585879</v>
@@ -7685,7 +7685,7 @@
     </row>
     <row r="97" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B97">
-        <v>1.0253485629252497</v>
+        <v>1.6028406253314181E-2</v>
       </c>
       <c r="C97">
         <v>0.8787878787878789</v>
@@ -7699,7 +7699,7 @@
     </row>
     <row r="98" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B98">
-        <v>1.0246495492308758</v>
+        <v>1.5456957070579338E-2</v>
       </c>
       <c r="C98">
         <v>0.89898989898989901</v>
@@ -7713,7 +7713,7 @@
     </row>
     <row r="99" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B99">
-        <v>1.0237629784971027</v>
+        <v>1.4991620310731528E-2</v>
       </c>
       <c r="C99">
         <v>0.91919191919191912</v>
@@ -7727,7 +7727,7 @@
     </row>
     <row r="100" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B100">
-        <v>1.0227971129018043</v>
+        <v>1.4538306711807305E-2</v>
       </c>
       <c r="C100">
         <v>0.93939393939393923</v>
@@ -7741,7 +7741,7 @@
     </row>
     <row r="101" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B101">
-        <v>1.0218023152722147</v>
+        <v>1.4111511877716348E-2</v>
       </c>
       <c r="C101">
         <v>0.95959595959596011</v>
@@ -7755,7 +7755,7 @@
     </row>
     <row r="102" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B102">
-        <v>1.0207910101260165</v>
+        <v>1.3724831628902296E-2</v>
       </c>
       <c r="C102">
         <v>0.97979797979797989</v>
@@ -7769,7 +7769,7 @@
     </row>
     <row r="103" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B103">
-        <v>1.0197315352459209</v>
+        <v>1.3407948074780072E-2</v>
       </c>
       <c r="C103">
         <v>1</v>
@@ -11009,23 +11009,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3"/>
+      <c r="E2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="2"/>
+      <c r="F2" s="3"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3"/>
+      <c r="K2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="2"/>
+      <c r="L2" s="3"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
@@ -11055,7 +11055,7 @@
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4">
-        <v>0.16066629363988616</v>
+        <v>6.8805858444211415E-2</v>
       </c>
       <c r="C4">
         <v>-0.9115258430592158</v>
@@ -11081,7 +11081,7 @@
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5">
-        <v>0.17712821797006223</v>
+        <v>7.1229469359072289E-2</v>
       </c>
       <c r="C5">
         <v>-0.89132382285719569</v>
@@ -11107,7 +11107,7 @@
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6">
-        <v>0.20457614607703517</v>
+        <v>7.8268466894337613E-2</v>
       </c>
       <c r="C6">
         <v>-0.87112180265517536</v>
@@ -11133,7 +11133,7 @@
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7">
-        <v>0.21753160062361312</v>
+        <v>8.1564064706722408E-2</v>
       </c>
       <c r="C7">
         <v>-0.85091978245315525</v>
@@ -11159,7 +11159,7 @@
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8">
-        <v>0.22222317922207682</v>
+        <v>8.410902820048273E-2</v>
       </c>
       <c r="C8">
         <v>-0.83071776225113503</v>
@@ -11185,7 +11185,7 @@
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9">
-        <v>0.22424901293565258</v>
+        <v>8.7678669157088426E-2</v>
       </c>
       <c r="C9">
         <v>-0.81051574204911481</v>
@@ -11211,7 +11211,7 @@
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10">
-        <v>0.22504188035728084</v>
+        <v>9.1515386068285187E-2</v>
       </c>
       <c r="C10">
         <v>-0.79031372184709459</v>
@@ -11237,7 +11237,7 @@
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11">
-        <v>0.22390923134460794</v>
+        <v>9.3605099120918578E-2</v>
       </c>
       <c r="C11">
         <v>-0.77011170164507448</v>
@@ -11263,7 +11263,7 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12">
-        <v>0.22320437081988717</v>
+        <v>9.654989057302224E-2</v>
       </c>
       <c r="C12">
         <v>-0.74990968144305425</v>
@@ -11289,7 +11289,7 @@
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13">
-        <v>0.22190860401662521</v>
+        <v>9.9901095388629124E-2</v>
       </c>
       <c r="C13">
         <v>-0.72970766124103403</v>
@@ -11315,7 +11315,7 @@
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14">
-        <v>0.21986370871547192</v>
+        <v>0.10282177420988435</v>
       </c>
       <c r="C14">
         <v>-0.70950564103901381</v>
@@ -11341,7 +11341,7 @@
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15">
-        <v>0.21684809277785275</v>
+        <v>0.10450926699902013</v>
       </c>
       <c r="C15">
         <v>-0.6893036208369937</v>
@@ -11367,7 +11367,7 @@
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16">
-        <v>0.21330996649083012</v>
+        <v>0.10678375934515907</v>
       </c>
       <c r="C16">
         <v>-0.66910160063497348</v>
@@ -11393,7 +11393,7 @@
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17">
-        <v>0.20938192504372061</v>
+        <v>0.1100120178264798</v>
       </c>
       <c r="C17">
         <v>-0.64889958043295326</v>
@@ -11419,7 +11419,7 @@
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18">
-        <v>0.20422535484688775</v>
+        <v>0.11233301467652224</v>
       </c>
       <c r="C18">
         <v>-0.62869756023093304</v>
@@ -11445,7 +11445,7 @@
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19">
-        <v>0.1983811950989566</v>
+        <v>0.11423202156555082</v>
       </c>
       <c r="C19">
         <v>-0.60849554002891282</v>
@@ -11471,7 +11471,7 @@
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20">
-        <v>0.19293854934123442</v>
+        <v>0.11720357870693657</v>
       </c>
       <c r="C20">
         <v>-0.5882935198268926</v>
@@ -11497,7 +11497,7 @@
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21">
-        <v>0.18689930728984222</v>
+        <v>0.11992062586657001</v>
       </c>
       <c r="C21">
         <v>-0.56809149962487238</v>
@@ -11523,7 +11523,7 @@
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22">
-        <v>0.17921700548080186</v>
+        <v>0.12127650864541917</v>
       </c>
       <c r="C22">
         <v>-0.54788947942285215</v>
@@ -11549,7 +11549,7 @@
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23">
-        <v>0.17173390896825519</v>
+        <v>0.12310600590376768</v>
       </c>
       <c r="C23">
         <v>-0.52768745922083193</v>
@@ -11575,7 +11575,7 @@
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24">
-        <v>0.16422889445674252</v>
+        <v>0.1252259130501536</v>
       </c>
       <c r="C24">
         <v>-0.50748543901881171</v>
@@ -11601,7 +11601,7 @@
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25">
-        <v>0.15672207052223489</v>
+        <v>0.12755247243846357</v>
       </c>
       <c r="C25">
         <v>-0.48728341881679155</v>
@@ -11627,7 +11627,7 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26">
-        <v>0.14889843387791832</v>
+        <v>0.12870255522440804</v>
       </c>
       <c r="C26">
         <v>-0.46708139861477121</v>
@@ -11653,7 +11653,7 @@
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27">
-        <v>0.14199573935679974</v>
+        <v>0.12991006334889324</v>
       </c>
       <c r="C27">
         <v>-0.44687937841275099</v>
@@ -11679,7 +11679,7 @@
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28">
-        <v>0.13706046762453714</v>
+        <v>0.13150631131871215</v>
       </c>
       <c r="C28">
         <v>-0.42667735821073088</v>
@@ -11705,7 +11705,7 @@
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29">
-        <v>0.13467892207684637</v>
+        <v>0.13339633458122907</v>
       </c>
       <c r="C29">
         <v>-0.40647533800871077</v>
@@ -11731,7 +11731,7 @@
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30">
-        <v>0.13487253958400114</v>
+        <v>0.13485445953371533</v>
       </c>
       <c r="C30">
         <v>-0.38627331780669061</v>
@@ -11757,7 +11757,7 @@
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31">
-        <v>0.13849464739647424</v>
+        <v>0.13632678916999116</v>
       </c>
       <c r="C31">
         <v>-0.3660712976046705</v>
@@ -11777,7 +11777,7 @@
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32">
-        <v>0.14694616444466715</v>
+        <v>0.13869550720371288</v>
       </c>
       <c r="C32">
         <v>-0.34586927740264983</v>
@@ -11797,7 +11797,7 @@
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33">
-        <v>0.15798600029295692</v>
+        <v>0.13973068643918965</v>
       </c>
       <c r="C33">
         <v>-0.32566725720062978</v>
@@ -11817,7 +11817,7 @@
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34">
-        <v>0.17272454305172394</v>
+        <v>0.14111515164882599</v>
       </c>
       <c r="C34">
         <v>-0.30546523699860967</v>
@@ -11837,7 +11837,7 @@
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35">
-        <v>0.19040630984127563</v>
+        <v>0.14232415889087638</v>
       </c>
       <c r="C35">
         <v>-0.28526321679658956</v>
@@ -11857,7 +11857,7 @@
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B36">
-        <v>0.21184060223255419</v>
+        <v>0.14425057142074307</v>
       </c>
       <c r="C36">
         <v>-0.26506119659456939</v>
@@ -11877,7 +11877,7 @@
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B37">
-        <v>0.23502107375119366</v>
+        <v>0.14527449717887636</v>
       </c>
       <c r="C37">
         <v>-0.24485917639254928</v>
@@ -11897,7 +11897,7 @@
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38">
-        <v>0.26002463176956975</v>
+        <v>0.14596287297074437</v>
       </c>
       <c r="C38">
         <v>-0.22465715619052914</v>
@@ -11917,7 +11917,7 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39">
-        <v>0.28667458066199608</v>
+        <v>0.14785608827049523</v>
       </c>
       <c r="C39">
         <v>-0.20445513598850848</v>
@@ -11937,7 +11937,7 @@
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B40">
-        <v>0.31557984747153173</v>
+        <v>0.14978519173119986</v>
       </c>
       <c r="C40">
         <v>-0.18425311578648843</v>
@@ -11957,7 +11957,7 @@
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B41">
-        <v>0.34476355078643822</v>
+        <v>0.15002175982131008</v>
       </c>
       <c r="C41">
         <v>-0.16405109558446831</v>
@@ -11977,7 +11977,7 @@
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B42">
-        <v>0.37538066594937014</v>
+        <v>0.15093241576677638</v>
       </c>
       <c r="C42">
         <v>-0.14384907538244818</v>
@@ -11997,7 +11997,7 @@
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B43">
-        <v>0.40741989729277733</v>
+        <v>0.15288784891159193</v>
       </c>
       <c r="C43">
         <v>-0.12364705518042805</v>
@@ -12017,7 +12017,7 @@
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B44">
-        <v>0.44009068837888876</v>
+        <v>0.15294489171804998</v>
       </c>
       <c r="C44">
         <v>-0.10344503497840793</v>
@@ -12037,7 +12037,7 @@
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B45">
-        <v>0.4738531179819736</v>
+        <v>0.15209299565740675</v>
       </c>
       <c r="C45">
         <v>-8.3243014776387805E-2</v>
@@ -12057,7 +12057,7 @@
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B46">
-        <v>0.5082512436237504</v>
+        <v>0.15106292122987305</v>
       </c>
       <c r="C46">
         <v>-6.3040994574367112E-2</v>
@@ -12077,7 +12077,7 @@
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B47">
-        <v>0.54310472014375422</v>
+        <v>0.1508458824616507</v>
       </c>
       <c r="C47">
         <v>-4.2838974372346988E-2</v>
@@ -12097,7 +12097,7 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B48">
-        <v>0.57737170979236319</v>
+        <v>0.14747937805409367</v>
       </c>
       <c r="C48">
         <v>-2.2636954170326861E-2</v>
@@ -12117,7 +12117,7 @@
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B49">
-        <v>0.61198702506496816</v>
+        <v>0.14319409983103137</v>
       </c>
       <c r="C49">
         <v>-2.4349339683067358E-3</v>
@@ -12137,7 +12137,7 @@
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B50">
-        <v>0.64696642152118999</v>
+        <v>0.13942154245741087</v>
       </c>
       <c r="C50">
         <v>1.776708623371339E-2</v>
@@ -12157,7 +12157,7 @@
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B51">
-        <v>0.68142255218318082</v>
+        <v>0.13580098415050365</v>
       </c>
       <c r="C51">
         <v>3.7969106435733889E-2</v>
@@ -12177,7 +12177,7 @@
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B52">
-        <v>0.71414695243050674</v>
+        <v>0.12758406304976133</v>
       </c>
       <c r="C52">
         <v>5.817112663775402E-2</v>
@@ -12197,7 +12197,7 @@
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B53">
-        <v>0.74472783023488121</v>
+        <v>0.11933037745654196</v>
       </c>
       <c r="C53">
         <v>7.8373146839774144E-2</v>
@@ -12217,7 +12217,7 @@
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B54">
-        <v>0.77286612446963399</v>
+        <v>0.11110452314018029</v>
       </c>
       <c r="C54">
         <v>9.8575167041794268E-2</v>
@@ -12237,7 +12237,7 @@
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B55">
-        <v>0.79869340176171166</v>
+        <v>0.10236414717221769</v>
       </c>
       <c r="C55">
         <v>0.11877718724381439</v>
@@ -12257,7 +12257,7 @@
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56">
-        <v>0.82080764166627618</v>
+        <v>9.2103530412938894E-2</v>
       </c>
       <c r="C56">
         <v>0.13897920744583453</v>
@@ -12277,7 +12277,7 @@
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B57">
-        <v>0.84011823078805925</v>
+        <v>8.3461411991145026E-2</v>
       </c>
       <c r="C57">
         <v>0.15918122764785464</v>
@@ -12297,7 +12297,7 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B58">
-        <v>0.85674489910348739</v>
+        <v>7.6378817837139512E-2</v>
       </c>
       <c r="C58">
         <v>0.17938324784987533</v>
@@ -12317,7 +12317,7 @@
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B59">
-        <v>0.87102391279403846</v>
+        <v>6.9799091848896933E-2</v>
       </c>
       <c r="C59">
         <v>0.19958526805189547</v>
@@ -12337,7 +12337,7 @@
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B60">
-        <v>0.88344924392902924</v>
+        <v>6.4345889424872432E-2</v>
       </c>
       <c r="C60">
         <v>0.21978728825391558</v>
@@ -12357,7 +12357,7 @@
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61">
-        <v>0.89434490349057805</v>
+        <v>6.0349216382244317E-2</v>
       </c>
       <c r="C61">
         <v>0.23998930845593572</v>
@@ -12377,7 +12377,7 @@
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62">
-        <v>0.90384020926671838</v>
+        <v>5.8144259805039476E-2</v>
       </c>
       <c r="C62">
         <v>0.26019132865795586</v>
@@ -12397,7 +12397,7 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63">
-        <v>0.91280779872912909</v>
+        <v>5.5303661758206876E-2</v>
       </c>
       <c r="C63">
         <v>0.28039334885997597</v>
@@ -12417,7 +12417,7 @@
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B64">
-        <v>0.92097145996802543</v>
+        <v>5.317491092176755E-2</v>
       </c>
       <c r="C64">
         <v>0.30059536906199608</v>
@@ -12437,7 +12437,7 @@
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B65">
-        <v>0.92861513116250038</v>
+        <v>5.1651343844989692E-2</v>
       </c>
       <c r="C65">
         <v>0.32079738926401624</v>
@@ -12457,7 +12457,7 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B66">
-        <v>0.93617318908753511</v>
+        <v>5.0390848637542514E-2</v>
       </c>
       <c r="C66">
         <v>0.34099940946603674</v>
@@ -12477,7 +12477,7 @@
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B67">
-        <v>0.94330099545509749</v>
+        <v>4.8441920741876469E-2</v>
       </c>
       <c r="C67">
         <v>0.36120142966805685</v>
@@ -12497,7 +12497,7 @@
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68">
-        <v>0.94999388624254066</v>
+        <v>4.6883087547086109E-2</v>
       </c>
       <c r="C68">
         <v>0.38140344987007696</v>
@@ -12517,7 +12517,7 @@
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69">
-        <v>0.95653193652015756</v>
+        <v>4.5584338578896759E-2</v>
       </c>
       <c r="C69">
         <v>0.40160547007209713</v>
@@ -12537,7 +12537,7 @@
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70">
-        <v>0.96262728123673924</v>
+        <v>4.4502804216820908E-2</v>
       </c>
       <c r="C70">
         <v>0.42180749027411724</v>
@@ -12557,7 +12557,7 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B71">
-        <v>0.96839643855096114</v>
+        <v>4.3001808213136136E-2</v>
       </c>
       <c r="C71">
         <v>0.4420095104761379</v>
@@ -12577,7 +12577,7 @@
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B72">
-        <v>0.97409346959521736</v>
+        <v>4.1616547366345548E-2</v>
       </c>
       <c r="C72">
         <v>0.46221153067815807</v>
@@ -12597,7 +12597,7 @@
     </row>
     <row r="73" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B73">
-        <v>0.97971325232290596</v>
+        <v>4.0567787313443689E-2</v>
       </c>
       <c r="C73">
         <v>0.48241355088017818</v>
@@ -12617,7 +12617,7 @@
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74">
-        <v>0.98487641862399555</v>
+        <v>3.9205746258520649E-2</v>
       </c>
       <c r="C74">
         <v>0.5026155710821989</v>
@@ -12637,7 +12637,7 @@
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B75">
-        <v>0.99000403184204178</v>
+        <v>3.7640584599474308E-2</v>
       </c>
       <c r="C75">
         <v>0.52281759128421845</v>
@@ -12657,7 +12657,7 @@
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B76">
-        <v>0.99467997861630697</v>
+        <v>3.6315119444819563E-2</v>
       </c>
       <c r="C76">
         <v>0.54301961148623856</v>
@@ -12677,7 +12677,7 @@
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77">
-        <v>0.99918932210385059</v>
+        <v>3.5300029123671327E-2</v>
       </c>
       <c r="C77">
         <v>0.56322163168825923</v>
@@ -12697,7 +12697,7 @@
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78">
-        <v>1.0034054537162664</v>
+        <v>3.3711532413369757E-2</v>
       </c>
       <c r="C78">
         <v>0.58342365189027934</v>
@@ -12717,7 +12717,7 @@
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B79">
-        <v>1.0074125842969728</v>
+        <v>3.2368884482586097E-2</v>
       </c>
       <c r="C79">
         <v>0.60362567209229934</v>
@@ -12737,7 +12737,7 @@
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B80">
-        <v>1.0112003375080896</v>
+        <v>3.0809799724075115E-2</v>
       </c>
       <c r="C80">
         <v>0.62382769229431945</v>
@@ -12757,7 +12757,7 @@
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81">
-        <v>1.0147006817503397</v>
+        <v>2.9323783248316297E-2</v>
       </c>
       <c r="C81">
         <v>0.64402971249633956</v>
@@ -12777,7 +12777,7 @@
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B82">
-        <v>1.0176772431296799</v>
+        <v>2.7792329388754883E-2</v>
       </c>
       <c r="C82">
         <v>0.66423173269836022</v>
@@ -12797,7 +12797,7 @@
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B83">
-        <v>1.020388372399093</v>
+        <v>2.6354925806466294E-2</v>
       </c>
       <c r="C83">
         <v>0.68443375290037978</v>
@@ -12817,7 +12817,7 @@
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B84">
-        <v>1.0227070897523731</v>
+        <v>2.5029294625256514E-2</v>
       </c>
       <c r="C84">
         <v>0.70463577310240066</v>
@@ -12837,7 +12837,7 @@
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85">
-        <v>1.0246271299776541</v>
+        <v>2.3694960061025647E-2</v>
       </c>
       <c r="C85">
         <v>0.72483779330442077</v>
@@ -12857,7 +12857,7 @@
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B86">
-        <v>1.0262824388661307</v>
+        <v>2.23160884533402E-2</v>
       </c>
       <c r="C86">
         <v>0.74503981350644055</v>
@@ -12877,7 +12877,7 @@
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B87">
-        <v>1.0275601946019284</v>
+        <v>2.1163332579619856E-2</v>
       </c>
       <c r="C87">
         <v>0.76524183370846066</v>
@@ -12897,7 +12897,7 @@
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B88">
-        <v>1.0284228231246511</v>
+        <v>2.0194481149191961E-2</v>
       </c>
       <c r="C88">
         <v>0.78544385391048077</v>
@@ -12917,7 +12917,7 @@
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B89">
-        <v>1.0290034242190749</v>
+        <v>1.919819070798242E-2</v>
       </c>
       <c r="C89">
         <v>0.80564587411250099</v>
@@ -12937,7 +12937,7 @@
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B90">
-        <v>1.0292934374601286</v>
+        <v>1.8336506994275203E-2</v>
       </c>
       <c r="C90">
         <v>0.82584789431452177</v>
@@ -12957,7 +12957,7 @@
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B91">
-        <v>1.0293093768972441</v>
+        <v>1.7644430992525807E-2</v>
       </c>
       <c r="C91">
         <v>0.84604991451654121</v>
@@ -12977,7 +12977,7 @@
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B92">
-        <v>1.0291421587101244</v>
+        <v>1.7075799416184582E-2</v>
       </c>
       <c r="C92">
         <v>0.8662519347185621</v>
@@ -12997,7 +12997,7 @@
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B93">
-        <v>1.0287459084525321</v>
+        <v>1.6557123394050719E-2</v>
       </c>
       <c r="C93">
         <v>0.88645395492058221</v>
@@ -13017,7 +13017,7 @@
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B94">
-        <v>1.0281946525580496</v>
+        <v>1.6087486016569379E-2</v>
       </c>
       <c r="C94">
         <v>0.90665597512260232</v>
@@ -13037,7 +13037,7 @@
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B95">
-        <v>1.0274797790109027</v>
+        <v>1.5701114119446368E-2</v>
       </c>
       <c r="C95">
         <v>0.92685799532462243</v>
@@ -13051,7 +13051,7 @@
     </row>
     <row r="96" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B96">
-        <v>1.0266151842368487</v>
+        <v>1.544969264653402E-2</v>
       </c>
       <c r="C96">
         <v>0.94706001552664298</v>
@@ -13065,7 +13065,7 @@
     </row>
     <row r="97" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B97">
-        <v>1.0255523626155758</v>
+        <v>1.5174283343724624E-2</v>
       </c>
       <c r="C97">
         <v>0.96726203572866309</v>
@@ -13079,7 +13079,7 @@
     </row>
     <row r="98" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B98">
-        <v>1.0243050995934828</v>
+        <v>1.4933334615174985E-2</v>
       </c>
       <c r="C98">
         <v>0.9874640559306832</v>
@@ -13093,7 +13093,7 @@
     </row>
     <row r="99" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B99">
-        <v>1.0228748089865718</v>
+        <v>1.4705680117485477E-2</v>
       </c>
       <c r="C99">
         <v>1.0076660761327034</v>
@@ -13107,7 +13107,7 @@
     </row>
     <row r="100" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B100">
-        <v>1.0212611266939231</v>
+        <v>1.4528695037724495E-2</v>
       </c>
       <c r="C100">
         <v>1.0278680963347235</v>
@@ -13121,7 +13121,7 @@
     </row>
     <row r="101" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B101">
-        <v>1.019505445630817</v>
+        <v>1.438737799443637E-2</v>
       </c>
       <c r="C101">
         <v>1.0480701165367439</v>
@@ -13135,7 +13135,7 @@
     </row>
     <row r="102" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B102">
-        <v>1.0176326092781562</v>
+        <v>1.423079406984663E-2</v>
       </c>
       <c r="C102">
         <v>1.068272136738764</v>
@@ -13149,7 +13149,7 @@
     </row>
     <row r="103" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B103">
-        <v>1.0156724424700876</v>
+        <v>1.403054711580318E-2</v>
       </c>
       <c r="C103">
         <v>1.0884741569407843</v>
@@ -16389,23 +16389,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3"/>
+      <c r="E2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="2"/>
+      <c r="F2" s="3"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3"/>
+      <c r="K2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="2"/>
+      <c r="L2" s="3"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
@@ -16434,10 +16434,10 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="3">
-        <v>0.12292481515768039</v>
-      </c>
-      <c r="C4" s="3">
+      <c r="B4">
+        <v>8.0611968469488732E-2</v>
+      </c>
+      <c r="C4">
         <v>-0.50002689184101534</v>
       </c>
       <c r="E4">
@@ -16460,10 +16460,10 @@
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="3">
-        <v>0.17328682749258975</v>
-      </c>
-      <c r="C5" s="3">
+      <c r="B5">
+        <v>0.11169200231920448</v>
+      </c>
+      <c r="C5">
         <v>-0.47980042451079935</v>
       </c>
       <c r="E5">
@@ -16486,10 +16486,10 @@
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B6" s="3">
-        <v>0.17307899147030029</v>
-      </c>
-      <c r="C6" s="3">
+      <c r="B6">
+        <v>0.12098547105155709</v>
+      </c>
+      <c r="C6">
         <v>-0.45957395718058347</v>
       </c>
       <c r="E6">
@@ -16512,10 +16512,10 @@
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="3">
-        <v>0.17166859483126123</v>
-      </c>
-      <c r="C7" s="3">
+      <c r="B7">
+        <v>0.13047865258938604</v>
+      </c>
+      <c r="C7">
         <v>-0.43934748985036726</v>
       </c>
       <c r="E7">
@@ -16538,10 +16538,10 @@
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B8" s="3">
-        <v>0.17023480831687263</v>
-      </c>
-      <c r="C8" s="3">
+      <c r="B8">
+        <v>0.1399755365752671</v>
+      </c>
+      <c r="C8">
         <v>-0.41912102252015104</v>
       </c>
       <c r="E8">
@@ -16564,10 +16564,10 @@
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="3">
-        <v>0.17098969984313717</v>
-      </c>
-      <c r="C9" s="3">
+      <c r="B9">
+        <v>0.15018358453215794</v>
+      </c>
+      <c r="C9">
         <v>-0.39889455518993489</v>
       </c>
       <c r="E9">
@@ -16590,10 +16590,10 @@
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="3">
-        <v>0.17033055940838285</v>
-      </c>
-      <c r="C10" s="3">
+      <c r="B10">
+        <v>0.15721839206896626</v>
+      </c>
+      <c r="C10">
         <v>-0.37866808785971917</v>
       </c>
       <c r="E10">
@@ -16616,10 +16616,10 @@
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="3">
-        <v>0.17208535801437783</v>
-      </c>
-      <c r="C11" s="3">
+      <c r="B11">
+        <v>0.16523260101225562</v>
+      </c>
+      <c r="C11">
         <v>-0.35844162052950301</v>
       </c>
       <c r="E11">
@@ -16642,10 +16642,10 @@
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="3">
-        <v>0.17649286067231296</v>
-      </c>
-      <c r="C12" s="3">
+      <c r="B12">
+        <v>0.17393946745278963</v>
+      </c>
+      <c r="C12">
         <v>-0.3382151531992868</v>
       </c>
       <c r="E12">
@@ -16668,10 +16668,10 @@
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="3">
-        <v>0.18190983937441457</v>
-      </c>
-      <c r="C13" s="3">
+      <c r="B13">
+        <v>0.18165568298252233</v>
+      </c>
+      <c r="C13">
         <v>-0.31798868586907114</v>
       </c>
       <c r="E13">
@@ -16694,10 +16694,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="3">
-        <v>0.18670625047840228</v>
-      </c>
-      <c r="C14" s="3">
+      <c r="B14">
+        <v>0.18634404535076007</v>
+      </c>
+      <c r="C14">
         <v>-0.29776221853885493</v>
       </c>
       <c r="E14">
@@ -16720,10 +16720,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B15" s="3">
-        <v>0.1946886724538428</v>
-      </c>
-      <c r="C15" s="3">
+      <c r="B15">
+        <v>0.19159880925297695</v>
+      </c>
+      <c r="C15">
         <v>-0.27753575120863871</v>
       </c>
       <c r="E15">
@@ -16746,10 +16746,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="3">
-        <v>0.20668226721810257</v>
-      </c>
-      <c r="C16" s="3">
+      <c r="B16">
+        <v>0.19795694349887738</v>
+      </c>
+      <c r="C16">
         <v>-0.25730928387842245</v>
       </c>
       <c r="E16">
@@ -16772,10 +16772,10 @@
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B17" s="3">
-        <v>0.21999431282967535</v>
-      </c>
-      <c r="C17" s="3">
+      <c r="B17">
+        <v>0.20225049239030879</v>
+      </c>
+      <c r="C17">
         <v>-0.23708281654820682</v>
       </c>
       <c r="E17">
@@ -16798,10 +16798,10 @@
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="3">
-        <v>0.23579105705895045</v>
-      </c>
-      <c r="C18" s="3">
+      <c r="B18">
+        <v>0.20575323921670474</v>
+      </c>
+      <c r="C18">
         <v>-0.2168563492179906</v>
       </c>
       <c r="E18">
@@ -16824,10 +16824,10 @@
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="3">
-        <v>0.25428972241185632</v>
-      </c>
-      <c r="C19" s="3">
+      <c r="B19">
+        <v>0.20899145027592664</v>
+      </c>
+      <c r="C19">
         <v>-0.19662988188777436</v>
       </c>
       <c r="E19">
@@ -16850,10 +16850,10 @@
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="3">
-        <v>0.27647220993734684</v>
-      </c>
-      <c r="C20" s="3">
+      <c r="B20">
+        <v>0.21316809851739352</v>
+      </c>
+      <c r="C20">
         <v>-0.1764034145575587</v>
       </c>
       <c r="E20">
@@ -16876,10 +16876,10 @@
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B21" s="3">
-        <v>0.29895340328695358</v>
-      </c>
-      <c r="C21" s="3">
+      <c r="B21">
+        <v>0.21462750266650085</v>
+      </c>
+      <c r="C21">
         <v>-0.15617694722734249</v>
       </c>
       <c r="E21">
@@ -16902,10 +16902,10 @@
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B22" s="3">
-        <v>0.32321264243627912</v>
-      </c>
-      <c r="C22" s="3">
+      <c r="B22">
+        <v>0.21402510128411656</v>
+      </c>
+      <c r="C22">
         <v>-0.13595047989712625</v>
       </c>
       <c r="E22">
@@ -16922,10 +16922,10 @@
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B23" s="3">
-        <v>0.35018466406735882</v>
-      </c>
-      <c r="C23" s="3">
+      <c r="B23">
+        <v>0.2140245851051317</v>
+      </c>
+      <c r="C23">
         <v>-0.11572401256691059</v>
       </c>
       <c r="E23">
@@ -16942,10 +16942,10 @@
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B24" s="3">
-        <v>0.37955284174757592</v>
-      </c>
-      <c r="C24" s="3">
+      <c r="B24">
+        <v>0.21409360152711124</v>
+      </c>
+      <c r="C24">
         <v>-9.5497545236694376E-2</v>
       </c>
       <c r="E24">
@@ -16962,10 +16962,10 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B25" s="3">
-        <v>0.40925451050439737</v>
-      </c>
-      <c r="C25" s="3">
+      <c r="B25">
+        <v>0.20997119740296138</v>
+      </c>
+      <c r="C25">
         <v>-7.5271077906478148E-2</v>
       </c>
       <c r="E25">
@@ -16982,10 +16982,10 @@
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B26" s="3">
-        <v>0.44129160840663939</v>
-      </c>
-      <c r="C26" s="3">
+      <c r="B26">
+        <v>0.20610241743687693</v>
+      </c>
+      <c r="C26">
         <v>-5.504461057626249E-2</v>
       </c>
       <c r="E26">
@@ -17002,10 +17002,10 @@
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B27" s="3">
-        <v>0.47419554554970433</v>
-      </c>
-      <c r="C27" s="3">
+      <c r="B27">
+        <v>0.20273482119589858</v>
+      </c>
+      <c r="C27">
         <v>-3.4818143246046263E-2</v>
       </c>
       <c r="E27">
@@ -17022,10 +17022,10 @@
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B28" s="3">
-        <v>0.50728105053574735</v>
-      </c>
-      <c r="C28" s="3">
+      <c r="B28">
+        <v>0.19794726084051786</v>
+      </c>
+      <c r="C28">
         <v>-1.4591675915830042E-2</v>
       </c>
       <c r="E28">
@@ -17042,10 +17042,10 @@
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B29" s="3">
-        <v>0.54084994201378411</v>
-      </c>
-      <c r="C29" s="3">
+      <c r="B29">
+        <v>0.19044677976513286</v>
+      </c>
+      <c r="C29">
         <v>5.6347914143861791E-3</v>
       </c>
       <c r="E29">
@@ -17062,10 +17062,10 @@
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B30" s="3">
-        <v>0.57530167105851182</v>
-      </c>
-      <c r="C30" s="3">
+      <c r="B30">
+        <v>0.18376568441408792</v>
+      </c>
+      <c r="C30">
         <v>2.5861258744601844E-2</v>
       </c>
       <c r="E30">
@@ -17082,10 +17082,10 @@
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B31" s="3">
-        <v>0.60955154263129607</v>
-      </c>
-      <c r="C31" s="3">
+      <c r="B31">
+        <v>0.17739396522482595</v>
+      </c>
+      <c r="C31">
         <v>4.6087726074818064E-2</v>
       </c>
       <c r="E31">
@@ -17102,10 +17102,10 @@
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B32" s="3">
-        <v>0.64329153447923504</v>
-      </c>
-      <c r="C32" s="3">
+      <c r="B32">
+        <v>0.16790165367930576</v>
+      </c>
+      <c r="C32">
         <v>6.6314193405034291E-2</v>
       </c>
       <c r="E32">
@@ -17122,10 +17122,10 @@
       </c>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B33" s="3">
-        <v>0.67650830516501892</v>
-      </c>
-      <c r="C33" s="3">
+      <c r="B33">
+        <v>0.15780848128745836</v>
+      </c>
+      <c r="C33">
         <v>8.6540660735250505E-2</v>
       </c>
       <c r="E33">
@@ -17142,10 +17142,10 @@
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B34" s="3">
-        <v>0.70847368948208189</v>
-      </c>
-      <c r="C34" s="3">
+      <c r="B34">
+        <v>0.1468925310591902</v>
+      </c>
+      <c r="C34">
         <v>0.10676712806546618</v>
       </c>
       <c r="E34">
@@ -17162,10 +17162,10 @@
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B35" s="3">
-        <v>0.7389366242968346</v>
-      </c>
-      <c r="C35" s="3">
+      <c r="B35">
+        <v>0.13681998593840858</v>
+      </c>
+      <c r="C35">
         <v>0.12699359539568239</v>
       </c>
       <c r="E35">
@@ -17182,10 +17182,10 @@
       </c>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B36" s="3">
-        <v>0.76709548627791257</v>
-      </c>
-      <c r="C36" s="3">
+      <c r="B36">
+        <v>0.12367990647257585</v>
+      </c>
+      <c r="C36">
         <v>0.1472200627258986</v>
       </c>
       <c r="E36">
@@ -17202,10 +17202,10 @@
       </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B37" s="3">
-        <v>0.79287455966132803</v>
-      </c>
-      <c r="C37" s="3">
+      <c r="B37">
+        <v>0.11194324800860254</v>
+      </c>
+      <c r="C37">
         <v>0.16744653005611429</v>
       </c>
       <c r="E37">
@@ -17222,10 +17222,10 @@
       </c>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B38" s="3">
-        <v>0.816507044265811</v>
-      </c>
-      <c r="C38" s="3">
+      <c r="B38">
+        <v>0.10137102681034038</v>
+      </c>
+      <c r="C38">
         <v>0.1876729973863305</v>
       </c>
       <c r="E38">
@@ -17242,10 +17242,10 @@
       </c>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B39" s="3">
-        <v>0.83760580571841325</v>
-      </c>
-      <c r="C39" s="3">
+      <c r="B39">
+        <v>9.1374699781281446E-2</v>
+      </c>
+      <c r="C39">
         <v>0.20789946471654672</v>
       </c>
       <c r="E39">
@@ -17262,10 +17262,10 @@
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B40" s="3">
-        <v>0.85613028906501565</v>
-      </c>
-      <c r="C40" s="3">
+      <c r="B40">
+        <v>8.1622967552995473E-2</v>
+      </c>
+      <c r="C40">
         <v>0.22812593204676238</v>
       </c>
       <c r="E40">
@@ -17282,10 +17282,10 @@
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B41" s="3">
-        <v>0.87231030401583765</v>
-      </c>
-      <c r="C41" s="3">
+      <c r="B41">
+        <v>7.4392311636197792E-2</v>
+      </c>
+      <c r="C41">
         <v>0.24835239937697862</v>
       </c>
       <c r="E41">
@@ -17302,10 +17302,10 @@
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B42" s="3">
-        <v>0.88719313226796082</v>
-      </c>
-      <c r="C42" s="3">
+      <c r="B42">
+        <v>6.8263048998298867E-2</v>
+      </c>
+      <c r="C42">
         <v>0.26857886670719483</v>
       </c>
       <c r="E42">
@@ -17322,10 +17322,10 @@
       </c>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B43" s="3">
-        <v>0.90068560637441875</v>
-      </c>
-      <c r="C43" s="3">
+      <c r="B43">
+        <v>6.331282054535442E-2</v>
+      </c>
+      <c r="C43">
         <v>0.28880533403741049</v>
       </c>
       <c r="E43">
@@ -17342,10 +17342,10 @@
       </c>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B44" s="3">
-        <v>0.91262388705655961</v>
-      </c>
-      <c r="C44" s="3">
+      <c r="B44">
+        <v>5.8997067117677715E-2</v>
+      </c>
+      <c r="C44">
         <v>0.3090318013676267</v>
       </c>
       <c r="E44">
@@ -17362,10 +17362,10 @@
       </c>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B45" s="3">
-        <v>0.9235173221896682</v>
-      </c>
-      <c r="C45" s="3">
+      <c r="B45">
+        <v>5.5873891203477681E-2</v>
+      </c>
+      <c r="C45">
         <v>0.32925826869784292</v>
       </c>
       <c r="E45">
@@ -17382,10 +17382,10 @@
       </c>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B46" s="3">
-        <v>0.93360760135345755</v>
-      </c>
-      <c r="C46" s="3">
+      <c r="B46">
+        <v>5.348406104085119E-2</v>
+      </c>
+      <c r="C46">
         <v>0.34948473602805863</v>
       </c>
       <c r="E46">
@@ -17402,10 +17402,10 @@
       </c>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B47" s="3">
-        <v>0.94326757174775755</v>
-      </c>
-      <c r="C47" s="3">
+      <c r="B47">
+        <v>5.0484054445296717E-2</v>
+      </c>
+      <c r="C47">
         <v>0.36971120335827484</v>
       </c>
       <c r="E47">
@@ -17422,10 +17422,10 @@
       </c>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B48" s="3">
-        <v>0.95218093881313348</v>
-      </c>
-      <c r="C48" s="3">
+      <c r="B48">
+        <v>4.8291691855913962E-2</v>
+      </c>
+      <c r="C48">
         <v>0.38993767068849083</v>
       </c>
       <c r="E48">
@@ -17442,10 +17442,10 @@
       </c>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B49" s="3">
-        <v>0.9602588028601875</v>
-      </c>
-      <c r="C49" s="3">
+      <c r="B49">
+        <v>4.6368603200687114E-2</v>
+      </c>
+      <c r="C49">
         <v>0.41016413801870671</v>
       </c>
       <c r="E49">
@@ -17462,10 +17462,10 @@
       </c>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B50" s="3">
-        <v>0.96771398607695014</v>
-      </c>
-      <c r="C50" s="3">
+      <c r="B50">
+        <v>4.4850787669419225E-2</v>
+      </c>
+      <c r="C50">
         <v>0.43039060534892332</v>
       </c>
       <c r="E50">
@@ -17482,10 +17482,10 @@
       </c>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B51" s="3">
-        <v>0.97446720147971821</v>
-      </c>
-      <c r="C51" s="3">
+      <c r="B51">
+        <v>4.3123330602659909E-2</v>
+      </c>
+      <c r="C51">
         <v>0.45061707267913953</v>
       </c>
       <c r="E51">
@@ -17502,10 +17502,10 @@
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B52" s="3">
-        <v>0.98084063358724571</v>
-      </c>
-      <c r="C52" s="3">
+      <c r="B52">
+        <v>4.1399726456609096E-2</v>
+      </c>
+      <c r="C52">
         <v>0.47084354000935574</v>
       </c>
       <c r="E52">
@@ -17522,10 +17522,10 @@
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B53" s="3">
-        <v>0.98652773978367669</v>
-      </c>
-      <c r="C53" s="3">
+      <c r="B53">
+        <v>4.0138469874965228E-2</v>
+      </c>
+      <c r="C53">
         <v>0.4910700073395714</v>
       </c>
       <c r="E53">
@@ -17542,10 +17542,10 @@
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B54" s="3">
-        <v>0.99163008615130255</v>
-      </c>
-      <c r="C54" s="3">
+      <c r="B54">
+        <v>3.8685739920152291E-2</v>
+      </c>
+      <c r="C54">
         <v>0.51129647466978767</v>
       </c>
       <c r="E54">
@@ -17562,10 +17562,10 @@
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B55" s="3">
-        <v>0.99635192436333242</v>
-      </c>
-      <c r="C55" s="3">
+      <c r="B55">
+        <v>3.6966064907241455E-2</v>
+      </c>
+      <c r="C55">
         <v>0.53152294200000327</v>
       </c>
       <c r="E55">
@@ -17582,10 +17582,10 @@
       </c>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B56" s="3">
-        <v>1.0009065704131108</v>
-      </c>
-      <c r="C56" s="3">
+      <c r="B56">
+        <v>3.5465029843547366E-2</v>
+      </c>
+      <c r="C56">
         <v>0.55174940933021954</v>
       </c>
       <c r="E56">
@@ -17602,10 +17602,10 @@
       </c>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B57" s="3">
-        <v>1.0052391706987052</v>
-      </c>
-      <c r="C57" s="3">
+      <c r="B57">
+        <v>3.4027886957892682E-2</v>
+      </c>
+      <c r="C57">
         <v>0.5719758766604357</v>
       </c>
       <c r="E57">
@@ -17622,10 +17622,10 @@
       </c>
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B58" s="3">
-        <v>1.0092154098120631</v>
-      </c>
-      <c r="C58" s="3">
+      <c r="B58">
+        <v>3.2297299384417145E-2</v>
+      </c>
+      <c r="C58">
         <v>0.59220234399065141</v>
       </c>
       <c r="E58">
@@ -17642,10 +17642,10 @@
       </c>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B59" s="3">
-        <v>1.0127694008404149</v>
-      </c>
-      <c r="C59" s="3">
+      <c r="B59">
+        <v>3.0743513621653371E-2</v>
+      </c>
+      <c r="C59">
         <v>0.61242881132086768</v>
       </c>
       <c r="E59">
@@ -17662,10 +17662,10 @@
       </c>
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B60" s="3">
-        <v>1.0160077651517017</v>
-      </c>
-      <c r="C60" s="3">
+      <c r="B60">
+        <v>2.9166162713509278E-2</v>
+      </c>
+      <c r="C60">
         <v>0.63265527865108384</v>
       </c>
       <c r="E60">
@@ -17682,10 +17682,10 @@
       </c>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B61" s="3">
-        <v>1.0188761708931173</v>
-      </c>
-      <c r="C61" s="3">
+      <c r="B61">
+        <v>2.7787181713062884E-2</v>
+      </c>
+      <c r="C61">
         <v>0.65288174598129955</v>
       </c>
       <c r="E61">
@@ -17702,10 +17702,10 @@
       </c>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B62" s="3">
-        <v>1.0214364898767672</v>
-      </c>
-      <c r="C62" s="3">
+      <c r="B62">
+        <v>2.6127695904431817E-2</v>
+      </c>
+      <c r="C62">
         <v>0.67310821331151571</v>
       </c>
       <c r="E62">
@@ -17722,10 +17722,10 @@
       </c>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B63" s="3">
-        <v>1.023502617611747</v>
-      </c>
-      <c r="C63" s="3">
+      <c r="B63">
+        <v>2.4676618895332767E-2</v>
+      </c>
+      <c r="C63">
         <v>0.69333468064173209</v>
       </c>
       <c r="E63">
@@ -17742,10 +17742,10 @@
       </c>
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B64" s="3">
-        <v>1.0251919846026467</v>
-      </c>
-      <c r="C64" s="3">
+      <c r="B64">
+        <v>2.3346138733856211E-2</v>
+      </c>
+      <c r="C64">
         <v>0.71356114797194781</v>
       </c>
       <c r="E64">
@@ -17762,10 +17762,10 @@
       </c>
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B65" s="3">
-        <v>1.0264391228213869</v>
-      </c>
-      <c r="C65" s="3">
+      <c r="B65">
+        <v>2.2094704246628127E-2</v>
+      </c>
+      <c r="C65">
         <v>0.73378761530216463</v>
       </c>
       <c r="E65">
@@ -17782,10 +17782,10 @@
       </c>
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B66" s="3">
-        <v>1.0272441577726308</v>
-      </c>
-      <c r="C66" s="3">
+      <c r="B66">
+        <v>2.0978878828287941E-2</v>
+      </c>
+      <c r="C66">
         <v>0.75401408263238023</v>
       </c>
       <c r="E66">
@@ -17802,10 +17802,10 @@
       </c>
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B67" s="3">
-        <v>1.0277095138425412</v>
-      </c>
-      <c r="C67" s="3">
+      <c r="B67">
+        <v>1.9959181479060908E-2</v>
+      </c>
+      <c r="C67">
         <v>0.77424054996259628</v>
       </c>
       <c r="E67">
@@ -17822,10 +17822,10 @@
       </c>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B68" s="3">
-        <v>1.0278136683042502</v>
-      </c>
-      <c r="C68" s="3">
+      <c r="B68">
+        <v>1.9114042197135431E-2</v>
+      </c>
+      <c r="C68">
         <v>0.79446701729281199</v>
       </c>
       <c r="E68">
@@ -17842,10 +17842,10 @@
       </c>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B69" s="3">
-        <v>1.0276015203175421</v>
-      </c>
-      <c r="C69" s="3">
+      <c r="B69">
+        <v>1.8376029310535762E-2</v>
+      </c>
+      <c r="C69">
         <v>0.81469348462302837</v>
       </c>
       <c r="E69">
@@ -17862,10 +17862,10 @@
       </c>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B70" s="3">
-        <v>1.0271666474193961</v>
-      </c>
-      <c r="C70" s="3">
+      <c r="B70">
+        <v>1.7692861973869926E-2</v>
+      </c>
+      <c r="C70">
         <v>0.83491995195324442</v>
       </c>
       <c r="E70">
@@ -17882,10 +17882,10 @@
       </c>
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B71" s="3">
-        <v>1.0264742697496381</v>
-      </c>
-      <c r="C71" s="3">
+      <c r="B71">
+        <v>1.7205147746084511E-2</v>
+      </c>
+      <c r="C71">
         <v>0.85514641928346002</v>
       </c>
       <c r="E71">
@@ -17902,10 +17902,10 @@
       </c>
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B72" s="3">
-        <v>1.0255443691235462</v>
-      </c>
-      <c r="C72" s="3">
+      <c r="B72">
+        <v>1.6732014335257377E-2</v>
+      </c>
+      <c r="C72">
         <v>0.87537288661367607</v>
       </c>
       <c r="H72">
@@ -17916,10 +17916,10 @@
       </c>
     </row>
     <row r="73" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B73" s="3">
-        <v>1.0244704418874793</v>
-      </c>
-      <c r="C73" s="3">
+      <c r="B73">
+        <v>1.6282634149742146E-2</v>
+      </c>
+      <c r="C73">
         <v>0.89559935394389245</v>
       </c>
       <c r="H73">
@@ -17930,10 +17930,10 @@
       </c>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B74" s="3">
-        <v>1.0232743902778021</v>
-      </c>
-      <c r="C74" s="3">
+      <c r="B74">
+        <v>1.5867930774954683E-2</v>
+      </c>
+      <c r="C74">
         <v>0.9158258212741085</v>
       </c>
       <c r="H74">
@@ -17944,10 +17944,10 @@
       </c>
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B75" s="3">
-        <v>1.0219329032867606</v>
-      </c>
-      <c r="C75" s="3">
+      <c r="B75">
+        <v>1.555229275418232E-2</v>
+      </c>
+      <c r="C75">
         <v>0.93605228860432421</v>
       </c>
       <c r="H75">
@@ -17958,10 +17958,10 @@
       </c>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B76" s="3">
-        <v>1.0204996731402813</v>
-      </c>
-      <c r="C76" s="3">
+      <c r="B76">
+        <v>1.5268176211137607E-2</v>
+      </c>
+      <c r="C76">
         <v>0.95627875593454059</v>
       </c>
       <c r="H76">
@@ -17972,10 +17972,10 @@
       </c>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B77" s="3">
-        <v>1.0189825970276187</v>
-      </c>
-      <c r="C77" s="3">
+      <c r="B77">
+        <v>1.4896721695963806E-2</v>
+      </c>
+      <c r="C77">
         <v>0.97650522326475664</v>
       </c>
       <c r="H77">
@@ -17986,10 +17986,10 @@
       </c>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B78" s="3">
-        <v>1.017444336962315</v>
-      </c>
-      <c r="C78" s="3">
+      <c r="B78">
+        <v>1.4552405299149121E-2</v>
+      </c>
+      <c r="C78">
         <v>0.99673169059497235</v>
       </c>
       <c r="H78">
@@ -18000,10 +18000,10 @@
       </c>
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B79" s="3">
-        <v>1.0158821026662028</v>
-      </c>
-      <c r="C79" s="3">
+      <c r="B79">
+        <v>1.4225288159624873E-2</v>
+      </c>
+      <c r="C79">
         <v>1.0169581579251887</v>
       </c>
       <c r="H79">
@@ -18014,10 +18014,10 @@
       </c>
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B80" s="3">
-        <v>1.0143590320520532</v>
-      </c>
-      <c r="C80" s="3">
+      <c r="B80">
+        <v>1.3973382685954565E-2</v>
+      </c>
+      <c r="C80">
         <v>1.0371846252554047</v>
       </c>
       <c r="H80">
@@ -18028,10 +18028,10 @@
       </c>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B81" s="3">
-        <v>1.0128666891688605</v>
-      </c>
-      <c r="C81" s="3">
+      <c r="B81">
+        <v>1.3734413342739522E-2</v>
+      </c>
+      <c r="C81">
         <v>1.0574110925856213</v>
       </c>
       <c r="H81">
@@ -18042,10 +18042,10 @@
       </c>
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B82" s="3">
-        <v>1.011413796900996</v>
-      </c>
-      <c r="C82" s="3">
+      <c r="B82">
+        <v>1.355577053743464E-2</v>
+      </c>
+      <c r="C82">
         <v>1.0776375599158368</v>
       </c>
       <c r="H82">
@@ -18056,10 +18056,10 @@
       </c>
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B83" s="3">
-        <v>1.0100174697172177</v>
-      </c>
-      <c r="C83" s="3">
+      <c r="B83">
+        <v>1.3365494183707565E-2</v>
+      </c>
+      <c r="C83">
         <v>1.0978640272460529</v>
       </c>
       <c r="H83">
@@ -18070,10 +18070,10 @@
       </c>
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B84" s="3">
-        <v>1.0086875712272942</v>
-      </c>
-      <c r="C84" s="3">
+      <c r="B84">
+        <v>1.3182626419615645E-2</v>
+      </c>
+      <c r="C84">
         <v>1.1180904945762693</v>
       </c>
       <c r="H84">
@@ -18084,10 +18084,10 @@
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B85" s="3">
-        <v>1.0074203836697115</v>
-      </c>
-      <c r="C85" s="3">
+      <c r="B85">
+        <v>1.2980210756905161E-2</v>
+      </c>
+      <c r="C85">
         <v>1.138316961906485</v>
       </c>
       <c r="H85">
@@ -18098,10 +18098,10 @@
       </c>
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B86" s="3">
-        <v>1.0062575618660567</v>
-      </c>
-      <c r="C86" s="3">
+      <c r="B86">
+        <v>1.2776184984851608E-2</v>
+      </c>
+      <c r="C86">
         <v>1.158543429236701</v>
       </c>
       <c r="H86">
@@ -18112,10 +18112,10 @@
       </c>
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B87" s="3">
-        <v>1.0052018070062791</v>
-      </c>
-      <c r="C87" s="3">
+      <c r="B87">
+        <v>1.2577389552124479E-2</v>
+      </c>
+      <c r="C87">
         <v>1.1787698965669173</v>
       </c>
       <c r="H87">
@@ -18126,10 +18126,10 @@
       </c>
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B88" s="3">
-        <v>1.0042730381734122</v>
-      </c>
-      <c r="C88" s="3">
+      <c r="B88">
+        <v>1.2388420889767852E-2</v>
+      </c>
+      <c r="C88">
         <v>1.198996363897133</v>
       </c>
       <c r="H88">
@@ -18140,10 +18140,10 @@
       </c>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B89" s="3">
-        <v>1.0034790507151554</v>
-      </c>
-      <c r="C89" s="3">
+      <c r="B89">
+        <v>1.2233672137083842E-2</v>
+      </c>
+      <c r="C89">
         <v>1.219222831227349</v>
       </c>
       <c r="H89">
@@ -18154,10 +18154,10 @@
       </c>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B90" s="3">
-        <v>1.0028137698581767</v>
-      </c>
-      <c r="C90" s="3">
+      <c r="B90">
+        <v>1.2100895708163544E-2</v>
+      </c>
+      <c r="C90">
         <v>1.2394492985575647</v>
       </c>
       <c r="H90">
@@ -18168,10 +18168,10 @@
       </c>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B91" s="3">
-        <v>1.0022675141178199</v>
-      </c>
-      <c r="C91" s="3">
+      <c r="B91">
+        <v>1.1959651360399894E-2</v>
+      </c>
+      <c r="C91">
         <v>1.2596757658877815</v>
       </c>
       <c r="H91">
@@ -18182,10 +18182,10 @@
       </c>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B92" s="3">
-        <v>1.0018398011064</v>
-      </c>
-      <c r="C92" s="3">
+      <c r="B92">
+        <v>1.18376006743687E-2</v>
+      </c>
+      <c r="C92">
         <v>1.2799022332179972</v>
       </c>
       <c r="H92">
@@ -18196,10 +18196,10 @@
       </c>
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B93" s="3">
-        <v>1.0015210423656014</v>
-      </c>
-      <c r="C93" s="3">
+      <c r="B93">
+        <v>1.1735080391976575E-2</v>
+      </c>
+      <c r="C93">
         <v>1.3001287005482129</v>
       </c>
       <c r="H93">
@@ -18210,10 +18210,10 @@
       </c>
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B94" s="3">
-        <v>1.0012967577805634</v>
-      </c>
-      <c r="C94" s="3">
+      <c r="B94">
+        <v>1.1649016966491505E-2</v>
+      </c>
+      <c r="C94">
         <v>1.3203551678784293</v>
       </c>
       <c r="H94">
@@ -18224,10 +18224,10 @@
       </c>
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B95" s="3">
-        <v>1.0011789341782911</v>
-      </c>
-      <c r="C95" s="3">
+      <c r="B95">
+        <v>1.1570830935281618E-2</v>
+      </c>
+      <c r="C95">
         <v>1.3405816352086459</v>
       </c>
       <c r="H95">
@@ -18238,10 +18238,10 @@
       </c>
     </row>
     <row r="96" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B96" s="3">
-        <v>1.0011673639371512</v>
-      </c>
-      <c r="C96" s="3">
+      <c r="B96">
+        <v>1.149292957877137E-2</v>
+      </c>
+      <c r="C96">
         <v>1.360808102538861</v>
       </c>
       <c r="H96">
@@ -18252,10 +18252,10 @@
       </c>
     </row>
     <row r="97" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B97" s="3">
-        <v>1.0012441249569091</v>
-      </c>
-      <c r="C97" s="3">
+      <c r="B97">
+        <v>1.1425902164617098E-2</v>
+      </c>
+      <c r="C97">
         <v>1.3810345698690778</v>
       </c>
       <c r="H97">
@@ -18266,10 +18266,10 @@
       </c>
     </row>
     <row r="98" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B98" s="3">
-        <v>1.0014001925747149</v>
-      </c>
-      <c r="C98" s="3">
+      <c r="B98">
+        <v>1.136981738816821E-2</v>
+      </c>
+      <c r="C98">
         <v>1.4012610371992942</v>
       </c>
       <c r="H98">
@@ -18280,10 +18280,10 @@
       </c>
     </row>
     <row r="99" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B99" s="3">
-        <v>1.0016289730965742</v>
-      </c>
-      <c r="C99" s="3">
+      <c r="B99">
+        <v>1.1309701642326656E-2</v>
+      </c>
+      <c r="C99">
         <v>1.4214875045295099</v>
       </c>
       <c r="H99">
@@ -18294,10 +18294,10 @@
       </c>
     </row>
     <row r="100" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B100" s="3">
-        <v>1.0019234630179328</v>
-      </c>
-      <c r="C100" s="3">
+      <c r="B100">
+        <v>1.1258766563353314E-2</v>
+      </c>
+      <c r="C100">
         <v>1.4417139718597258</v>
       </c>
       <c r="H100">
@@ -18308,10 +18308,10 @@
       </c>
     </row>
     <row r="101" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B101" s="3">
-        <v>1.0022703091945919</v>
-      </c>
-      <c r="C101" s="3">
+      <c r="B101">
+        <v>1.1207100769976898E-2</v>
+      </c>
+      <c r="C101">
         <v>1.4619404391899422</v>
       </c>
       <c r="H101">
@@ -18322,10 +18322,10 @@
       </c>
     </row>
     <row r="102" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B102" s="3">
-        <v>1.0026631519690379</v>
-      </c>
-      <c r="C102" s="3">
+      <c r="B102">
+        <v>1.1132218332182219E-2</v>
+      </c>
+      <c r="C102">
         <v>1.4821669065201579</v>
       </c>
       <c r="H102">
@@ -18336,10 +18336,10 @@
       </c>
     </row>
     <row r="103" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B103" s="3">
-        <v>1.0030850489823961</v>
-      </c>
-      <c r="C103" s="3">
+      <c r="B103">
+        <v>1.1057094228213892E-2</v>
+      </c>
+      <c r="C103">
         <v>1.5023933738503739</v>
       </c>
       <c r="H103">
@@ -18350,8 +18350,8 @@
       </c>
     </row>
     <row r="104" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B104" s="3"/>
-      <c r="C104" s="3"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
       <c r="H104">
         <v>0.16339625360230547</v>
       </c>
@@ -18360,8 +18360,8 @@
       </c>
     </row>
     <row r="105" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B105" s="3"/>
-      <c r="C105" s="3"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
       <c r="H105">
         <v>0.1629034582132565</v>
       </c>
@@ -18370,8 +18370,8 @@
       </c>
     </row>
     <row r="106" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B106" s="3"/>
-      <c r="C106" s="3"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
       <c r="H106">
         <v>0.16235590778097983</v>
       </c>
@@ -18380,8 +18380,8 @@
       </c>
     </row>
     <row r="107" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B107" s="3"/>
-      <c r="C107" s="3"/>
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
       <c r="H107">
         <v>0.16181123919308357</v>
       </c>
@@ -18390,8 +18390,8 @@
       </c>
     </row>
     <row r="108" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B108" s="3"/>
-      <c r="C108" s="3"/>
+      <c r="B108" s="2"/>
+      <c r="C108" s="2"/>
       <c r="H108">
         <v>0.16120461095100866</v>
       </c>
@@ -18400,8 +18400,8 @@
       </c>
     </row>
     <row r="109" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B109" s="3"/>
-      <c r="C109" s="3"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
       <c r="H109">
         <v>0.16052881844380404</v>
       </c>
@@ -18410,8 +18410,8 @@
       </c>
     </row>
     <row r="110" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B110" s="3"/>
-      <c r="C110" s="3"/>
+      <c r="B110" s="2"/>
+      <c r="C110" s="2"/>
       <c r="H110">
         <v>0.15985446685878962</v>
       </c>
@@ -18420,8 +18420,8 @@
       </c>
     </row>
     <row r="111" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B111" s="3"/>
-      <c r="C111" s="3"/>
+      <c r="B111" s="2"/>
+      <c r="C111" s="2"/>
       <c r="H111">
         <v>0.15917579250720462</v>
       </c>
@@ -18430,8 +18430,8 @@
       </c>
     </row>
     <row r="112" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B112" s="3"/>
-      <c r="C112" s="3"/>
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
       <c r="H112">
         <v>0.15850144092219021</v>
       </c>
@@ -18440,8 +18440,8 @@
       </c>
     </row>
     <row r="113" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B113" s="3"/>
-      <c r="C113" s="3"/>
+      <c r="B113" s="2"/>
+      <c r="C113" s="2"/>
       <c r="H113">
         <v>0.15778097982708933</v>
       </c>
@@ -18450,8 +18450,8 @@
       </c>
     </row>
     <row r="114" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B114" s="3"/>
-      <c r="C114" s="3"/>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
       <c r="H114">
         <v>0.15701873198847263</v>
       </c>
@@ -18460,8 +18460,8 @@
       </c>
     </row>
     <row r="115" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B115" s="3"/>
-      <c r="C115" s="3"/>
+      <c r="B115" s="2"/>
+      <c r="C115" s="2"/>
       <c r="H115">
         <v>0.1561599423631124</v>
       </c>
@@ -18470,8 +18470,8 @@
       </c>
     </row>
     <row r="116" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B116" s="3"/>
-      <c r="C116" s="3"/>
+      <c r="B116" s="2"/>
+      <c r="C116" s="2"/>
       <c r="H116">
         <v>0.15526657060518731</v>
       </c>
@@ -18480,8 +18480,8 @@
       </c>
     </row>
     <row r="117" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B117" s="3"/>
-      <c r="C117" s="3"/>
+      <c r="B117" s="2"/>
+      <c r="C117" s="2"/>
       <c r="H117">
         <v>0.15433429394812681</v>
       </c>
@@ -18490,8 +18490,8 @@
       </c>
     </row>
     <row r="118" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B118" s="3"/>
-      <c r="C118" s="3"/>
+      <c r="B118" s="2"/>
+      <c r="C118" s="2"/>
       <c r="H118">
         <v>0.153321325648415</v>
       </c>
@@ -18500,8 +18500,8 @@
       </c>
     </row>
     <row r="119" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B119" s="3"/>
-      <c r="C119" s="3"/>
+      <c r="B119" s="2"/>
+      <c r="C119" s="2"/>
       <c r="H119">
         <v>0.15229682997118155</v>
       </c>
@@ -18510,8 +18510,8 @@
       </c>
     </row>
     <row r="120" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B120" s="3"/>
-      <c r="C120" s="3"/>
+      <c r="B120" s="2"/>
+      <c r="C120" s="2"/>
       <c r="H120">
         <v>0.15126224783861672</v>
       </c>
@@ -18520,8 +18520,8 @@
       </c>
     </row>
     <row r="121" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B121" s="3"/>
-      <c r="C121" s="3"/>
+      <c r="B121" s="2"/>
+      <c r="C121" s="2"/>
       <c r="H121">
         <v>0.15013256484149856</v>
       </c>
@@ -18530,8 +18530,8 @@
       </c>
     </row>
     <row r="122" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B122" s="3"/>
-      <c r="C122" s="3"/>
+      <c r="B122" s="2"/>
+      <c r="C122" s="2"/>
       <c r="H122">
         <v>0.14901729106628242</v>
       </c>
@@ -18540,8 +18540,8 @@
       </c>
     </row>
     <row r="123" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B123" s="3"/>
-      <c r="C123" s="3"/>
+      <c r="B123" s="2"/>
+      <c r="C123" s="2"/>
       <c r="H123">
         <v>0.14784582132564841</v>
       </c>
@@ -18550,8 +18550,8 @@
       </c>
     </row>
     <row r="124" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B124" s="3"/>
-      <c r="C124" s="3"/>
+      <c r="B124" s="2"/>
+      <c r="C124" s="2"/>
       <c r="H124">
         <v>0.14661095100864555</v>
       </c>
@@ -18560,8 +18560,8 @@
       </c>
     </row>
     <row r="125" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B125" s="3"/>
-      <c r="C125" s="3"/>
+      <c r="B125" s="2"/>
+      <c r="C125" s="2"/>
       <c r="H125">
         <v>0.14537031700288183</v>
       </c>
@@ -18570,8 +18570,8 @@
       </c>
     </row>
     <row r="126" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B126" s="3"/>
-      <c r="C126" s="3"/>
+      <c r="B126" s="2"/>
+      <c r="C126" s="2"/>
       <c r="H126">
         <v>0.14397737752161383</v>
       </c>
@@ -18580,8 +18580,8 @@
       </c>
     </row>
     <row r="127" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B127" s="3"/>
-      <c r="C127" s="3"/>
+      <c r="B127" s="2"/>
+      <c r="C127" s="2"/>
       <c r="H127">
         <v>0.14252982708933717</v>
       </c>
@@ -18590,8 +18590,8 @@
       </c>
     </row>
     <row r="128" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B128" s="3"/>
-      <c r="C128" s="3"/>
+      <c r="B128" s="2"/>
+      <c r="C128" s="2"/>
       <c r="H128">
         <v>0.14108544668587897</v>
       </c>
@@ -18600,8 +18600,8 @@
       </c>
     </row>
     <row r="129" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B129" s="3"/>
-      <c r="C129" s="3"/>
+      <c r="B129" s="2"/>
+      <c r="C129" s="2"/>
       <c r="H129">
         <v>0.13962002881844379</v>
       </c>
@@ -18610,8 +18610,8 @@
       </c>
     </row>
     <row r="130" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B130" s="3"/>
-      <c r="C130" s="3"/>
+      <c r="B130" s="2"/>
+      <c r="C130" s="2"/>
       <c r="H130">
         <v>0.13810100864553315</v>
       </c>
@@ -18620,8 +18620,8 @@
       </c>
     </row>
     <row r="131" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B131" s="3"/>
-      <c r="C131" s="3"/>
+      <c r="B131" s="2"/>
+      <c r="C131" s="2"/>
       <c r="H131">
         <v>0.13645201729106629</v>
       </c>
@@ -18630,8 +18630,8 @@
       </c>
     </row>
     <row r="132" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B132" s="3"/>
-      <c r="C132" s="3"/>
+      <c r="B132" s="2"/>
+      <c r="C132" s="2"/>
       <c r="H132">
         <v>0.13480504322766571</v>
       </c>
@@ -18640,8 +18640,8 @@
       </c>
     </row>
     <row r="133" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B133" s="3"/>
-      <c r="C133" s="3"/>
+      <c r="B133" s="2"/>
+      <c r="C133" s="2"/>
       <c r="H133">
         <v>0.13314495677233432</v>
       </c>
@@ -18650,8 +18650,8 @@
       </c>
     </row>
     <row r="134" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B134" s="3"/>
-      <c r="C134" s="3"/>
+      <c r="B134" s="2"/>
+      <c r="C134" s="2"/>
       <c r="H134">
         <v>0.13145547550432277</v>
       </c>
@@ -18660,8 +18660,8 @@
       </c>
     </row>
     <row r="135" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B135" s="3"/>
-      <c r="C135" s="3"/>
+      <c r="B135" s="2"/>
+      <c r="C135" s="2"/>
       <c r="H135">
         <v>0.12963112391930837</v>
       </c>
@@ -18670,8 +18670,8 @@
       </c>
     </row>
     <row r="136" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B136" s="3"/>
-      <c r="C136" s="3"/>
+      <c r="B136" s="2"/>
+      <c r="C136" s="2"/>
       <c r="H136">
         <v>0.12780634005763689</v>
       </c>
@@ -18680,8 +18680,8 @@
       </c>
     </row>
     <row r="137" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B137" s="3"/>
-      <c r="C137" s="3"/>
+      <c r="B137" s="2"/>
+      <c r="C137" s="2"/>
       <c r="H137">
         <v>0.12598674351585012</v>
       </c>
@@ -18690,8 +18690,8 @@
       </c>
     </row>
     <row r="138" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B138" s="3"/>
-      <c r="C138" s="3"/>
+      <c r="B138" s="2"/>
+      <c r="C138" s="2"/>
       <c r="H138">
         <v>0.12409394812680115</v>
       </c>
@@ -18700,8 +18700,8 @@
       </c>
     </row>
     <row r="139" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B139" s="3"/>
-      <c r="C139" s="3"/>
+      <c r="B139" s="2"/>
+      <c r="C139" s="2"/>
       <c r="H139">
         <v>0.12219827089337175</v>
       </c>
@@ -18710,8 +18710,8 @@
       </c>
     </row>
     <row r="140" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B140" s="3"/>
-      <c r="C140" s="3"/>
+      <c r="B140" s="2"/>
+      <c r="C140" s="2"/>
       <c r="H140">
         <v>0.12029020172910662</v>
       </c>
@@ -18720,8 +18720,8 @@
       </c>
     </row>
     <row r="141" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B141" s="3"/>
-      <c r="C141" s="3"/>
+      <c r="B141" s="2"/>
+      <c r="C141" s="2"/>
       <c r="H141">
         <v>0.118335734870317</v>
       </c>
@@ -18730,8 +18730,8 @@
       </c>
     </row>
     <row r="142" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B142" s="3"/>
-      <c r="C142" s="3"/>
+      <c r="B142" s="2"/>
+      <c r="C142" s="2"/>
       <c r="H142">
         <v>0.1162951008645533</v>
       </c>
@@ -18740,8 +18740,8 @@
       </c>
     </row>
     <row r="143" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B143" s="3"/>
-      <c r="C143" s="3"/>
+      <c r="B143" s="2"/>
+      <c r="C143" s="2"/>
       <c r="H143">
         <v>0.11426815561959654</v>
       </c>
@@ -18750,8 +18750,8 @@
       </c>
     </row>
     <row r="144" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B144" s="3"/>
-      <c r="C144" s="3"/>
+      <c r="B144" s="2"/>
+      <c r="C144" s="2"/>
       <c r="H144">
         <v>0.11223731988472624</v>
       </c>
@@ -18760,8 +18760,8 @@
       </c>
     </row>
     <row r="145" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B145" s="3"/>
-      <c r="C145" s="3"/>
+      <c r="B145" s="2"/>
+      <c r="C145" s="2"/>
       <c r="H145">
         <v>0.11012031700288186</v>
       </c>
@@ -18770,8 +18770,8 @@
       </c>
     </row>
     <row r="146" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B146" s="3"/>
-      <c r="C146" s="3"/>
+      <c r="B146" s="2"/>
+      <c r="C146" s="2"/>
       <c r="H146">
         <v>0.10801412103746397</v>
       </c>
@@ -18780,8 +18780,8 @@
       </c>
     </row>
     <row r="147" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B147" s="3"/>
-      <c r="C147" s="3"/>
+      <c r="B147" s="2"/>
+      <c r="C147" s="2"/>
       <c r="H147">
         <v>0.10584265129682997</v>
       </c>
@@ -18790,8 +18790,8 @@
       </c>
     </row>
     <row r="148" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B148" s="3"/>
-      <c r="C148" s="3"/>
+      <c r="B148" s="2"/>
+      <c r="C148" s="2"/>
       <c r="H148">
         <v>0.10369279538904899</v>
       </c>
@@ -18800,8 +18800,8 @@
       </c>
     </row>
     <row r="149" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B149" s="3"/>
-      <c r="C149" s="3"/>
+      <c r="B149" s="2"/>
+      <c r="C149" s="2"/>
       <c r="H149">
         <v>0.10145504322766571</v>
       </c>
@@ -18810,8 +18810,8 @@
       </c>
     </row>
     <row r="150" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B150" s="3"/>
-      <c r="C150" s="3"/>
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
       <c r="H150">
         <v>9.9215706051873201E-2</v>
       </c>
@@ -18820,8 +18820,8 @@
       </c>
     </row>
     <row r="151" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B151" s="3"/>
-      <c r="C151" s="3"/>
+      <c r="B151" s="2"/>
+      <c r="C151" s="2"/>
       <c r="H151">
         <v>9.7027377521613833E-2</v>
       </c>
@@ -18830,8 +18830,8 @@
       </c>
     </row>
     <row r="152" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B152" s="3"/>
-      <c r="C152" s="3"/>
+      <c r="B152" s="2"/>
+      <c r="C152" s="2"/>
       <c r="H152">
         <v>9.4836167146974057E-2</v>
       </c>
@@ -18840,8 +18840,8 @@
       </c>
     </row>
     <row r="153" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B153" s="3"/>
-      <c r="C153" s="3"/>
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
       <c r="H153">
         <v>9.2636023054755046E-2</v>
       </c>
@@ -18850,8 +18850,8 @@
       </c>
     </row>
     <row r="154" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B154" s="3"/>
-      <c r="C154" s="3"/>
+      <c r="B154" s="2"/>
+      <c r="C154" s="2"/>
       <c r="H154">
         <v>9.0429538904899132E-2</v>
       </c>
@@ -18860,8 +18860,8 @@
       </c>
     </row>
     <row r="155" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B155" s="3"/>
-      <c r="C155" s="3"/>
+      <c r="B155" s="2"/>
+      <c r="C155" s="2"/>
       <c r="H155">
         <v>8.8237175792507214E-2</v>
       </c>
@@ -18870,8 +18870,8 @@
       </c>
     </row>
     <row r="156" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B156" s="3"/>
-      <c r="C156" s="3"/>
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
       <c r="H156">
         <v>8.6127953890489911E-2</v>
       </c>
@@ -18880,8 +18880,8 @@
       </c>
     </row>
     <row r="157" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B157" s="3"/>
-      <c r="C157" s="3"/>
+      <c r="B157" s="2"/>
+      <c r="C157" s="2"/>
       <c r="H157">
         <v>8.3911959654178678E-2</v>
       </c>
@@ -18890,8 +18890,8 @@
       </c>
     </row>
     <row r="158" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B158" s="3"/>
-      <c r="C158" s="3"/>
+      <c r="B158" s="2"/>
+      <c r="C158" s="2"/>
       <c r="H158">
         <v>8.1723487031700279E-2</v>
       </c>
@@ -18900,8 +18900,8 @@
       </c>
     </row>
     <row r="159" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B159" s="3"/>
-      <c r="C159" s="3"/>
+      <c r="B159" s="2"/>
+      <c r="C159" s="2"/>
       <c r="H159">
         <v>7.9643227665706043E-2</v>
       </c>
@@ -18910,8 +18910,8 @@
       </c>
     </row>
     <row r="160" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B160" s="3"/>
-      <c r="C160" s="3"/>
+      <c r="B160" s="2"/>
+      <c r="C160" s="2"/>
       <c r="H160">
         <v>7.7548126801152736E-2</v>
       </c>
@@ -18920,8 +18920,8 @@
       </c>
     </row>
     <row r="161" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B161" s="3"/>
-      <c r="C161" s="3"/>
+      <c r="B161" s="2"/>
+      <c r="C161" s="2"/>
       <c r="H161">
         <v>7.5498847262247842E-2</v>
       </c>
@@ -18930,8 +18930,8 @@
       </c>
     </row>
     <row r="162" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B162" s="3"/>
-      <c r="C162" s="3"/>
+      <c r="B162" s="2"/>
+      <c r="C162" s="2"/>
       <c r="H162">
         <v>7.346325648414985E-2</v>
       </c>
@@ -18940,8 +18940,8 @@
       </c>
     </row>
     <row r="163" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B163" s="3"/>
-      <c r="C163" s="3"/>
+      <c r="B163" s="2"/>
+      <c r="C163" s="2"/>
       <c r="H163">
         <v>7.1568443804034584E-2</v>
       </c>
@@ -18950,8 +18950,8 @@
       </c>
     </row>
     <row r="164" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B164" s="3"/>
-      <c r="C164" s="3"/>
+      <c r="B164" s="2"/>
+      <c r="C164" s="2"/>
       <c r="H164">
         <v>6.9715706051873202E-2</v>
       </c>
@@ -18960,8 +18960,8 @@
       </c>
     </row>
     <row r="165" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B165" s="3"/>
-      <c r="C165" s="3"/>
+      <c r="B165" s="2"/>
+      <c r="C165" s="2"/>
       <c r="H165">
         <v>6.7827809798270897E-2</v>
       </c>
@@ -18970,8 +18970,8 @@
       </c>
     </row>
     <row r="166" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B166" s="3"/>
-      <c r="C166" s="3"/>
+      <c r="B166" s="2"/>
+      <c r="C166" s="2"/>
       <c r="H166">
         <v>6.599135446685879E-2</v>
       </c>
@@ -18980,8 +18980,8 @@
       </c>
     </row>
     <row r="167" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B167" s="3"/>
-      <c r="C167" s="3"/>
+      <c r="B167" s="2"/>
+      <c r="C167" s="2"/>
       <c r="H167">
         <v>6.4181556195965425E-2</v>
       </c>
@@ -18990,8 +18990,8 @@
       </c>
     </row>
     <row r="168" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B168" s="3"/>
-      <c r="C168" s="3"/>
+      <c r="B168" s="2"/>
+      <c r="C168" s="2"/>
       <c r="H168">
         <v>6.242680115273775E-2</v>
       </c>
@@ -19000,8 +19000,8 @@
       </c>
     </row>
     <row r="169" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B169" s="3"/>
-      <c r="C169" s="3"/>
+      <c r="B169" s="2"/>
+      <c r="C169" s="2"/>
       <c r="H169">
         <v>6.072809798270893E-2</v>
       </c>
@@ -19010,8 +19010,8 @@
       </c>
     </row>
     <row r="170" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B170" s="3"/>
-      <c r="C170" s="3"/>
+      <c r="B170" s="2"/>
+      <c r="C170" s="2"/>
       <c r="H170">
         <v>5.9057925072046102E-2</v>
       </c>
@@ -19020,8 +19020,8 @@
       </c>
     </row>
     <row r="171" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B171" s="3"/>
-      <c r="C171" s="3"/>
+      <c r="B171" s="2"/>
+      <c r="C171" s="2"/>
       <c r="H171">
         <v>5.7483861671469738E-2</v>
       </c>
@@ -19030,8 +19030,8 @@
       </c>
     </row>
     <row r="172" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B172" s="3"/>
-      <c r="C172" s="3"/>
+      <c r="B172" s="2"/>
+      <c r="C172" s="2"/>
       <c r="H172">
         <v>5.5948414985590784E-2</v>
       </c>
@@ -19040,8 +19040,8 @@
       </c>
     </row>
     <row r="173" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B173" s="3"/>
-      <c r="C173" s="3"/>
+      <c r="B173" s="2"/>
+      <c r="C173" s="2"/>
       <c r="H173">
         <v>5.448487031700288E-2</v>
       </c>
@@ -19050,8 +19050,8 @@
       </c>
     </row>
     <row r="174" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B174" s="3"/>
-      <c r="C174" s="3"/>
+      <c r="B174" s="2"/>
+      <c r="C174" s="2"/>
       <c r="H174">
         <v>5.3028962536023058E-2</v>
       </c>
@@ -19060,8 +19060,8 @@
       </c>
     </row>
     <row r="175" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B175" s="3"/>
-      <c r="C175" s="3"/>
+      <c r="B175" s="2"/>
+      <c r="C175" s="2"/>
       <c r="H175">
         <v>5.1638904899135453E-2</v>
       </c>
@@ -19070,8 +19070,8 @@
       </c>
     </row>
     <row r="176" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B176" s="3"/>
-      <c r="C176" s="3"/>
+      <c r="B176" s="2"/>
+      <c r="C176" s="2"/>
       <c r="H176">
         <v>5.0304899135446689E-2</v>
       </c>
@@ -19080,8 +19080,8 @@
       </c>
     </row>
     <row r="177" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B177" s="3"/>
-      <c r="C177" s="3"/>
+      <c r="B177" s="2"/>
+      <c r="C177" s="2"/>
       <c r="H177">
         <v>4.9052881844380405E-2</v>
       </c>
@@ -19090,8 +19090,8 @@
       </c>
     </row>
     <row r="178" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B178" s="3"/>
-      <c r="C178" s="3"/>
+      <c r="B178" s="2"/>
+      <c r="C178" s="2"/>
       <c r="H178">
         <v>4.7850144092219021E-2</v>
       </c>
@@ -19100,8 +19100,8 @@
       </c>
     </row>
     <row r="179" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B179" s="3"/>
-      <c r="C179" s="3"/>
+      <c r="B179" s="2"/>
+      <c r="C179" s="2"/>
       <c r="H179">
         <v>4.6691642651296834E-2</v>
       </c>
@@ -19110,8 +19110,8 @@
       </c>
     </row>
     <row r="180" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B180" s="3"/>
-      <c r="C180" s="3"/>
+      <c r="B180" s="2"/>
+      <c r="C180" s="2"/>
       <c r="H180">
         <v>4.5578097982708933E-2</v>
       </c>
@@ -19120,8 +19120,8 @@
       </c>
     </row>
     <row r="181" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B181" s="3"/>
-      <c r="C181" s="3"/>
+      <c r="B181" s="2"/>
+      <c r="C181" s="2"/>
       <c r="H181">
         <v>4.4505043227665707E-2</v>
       </c>
@@ -19130,8 +19130,8 @@
       </c>
     </row>
     <row r="182" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B182" s="3"/>
-      <c r="C182" s="3"/>
+      <c r="B182" s="2"/>
+      <c r="C182" s="2"/>
       <c r="H182">
         <v>4.3476657060518731E-2</v>
       </c>
@@ -19140,8 +19140,8 @@
       </c>
     </row>
     <row r="183" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B183" s="3"/>
-      <c r="C183" s="3"/>
+      <c r="B183" s="2"/>
+      <c r="C183" s="2"/>
       <c r="H183">
         <v>4.256368876080692E-2</v>
       </c>
@@ -19150,8 +19150,8 @@
       </c>
     </row>
     <row r="184" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B184" s="3"/>
-      <c r="C184" s="3"/>
+      <c r="B184" s="2"/>
+      <c r="C184" s="2"/>
       <c r="H184">
         <v>4.1652305475504324E-2</v>
       </c>
@@ -19160,8 +19160,8 @@
       </c>
     </row>
     <row r="185" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B185" s="3"/>
-      <c r="C185" s="3"/>
+      <c r="B185" s="2"/>
+      <c r="C185" s="2"/>
       <c r="H185">
         <v>4.0756916426512968E-2</v>
       </c>
@@ -19170,8 +19170,8 @@
       </c>
     </row>
     <row r="186" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B186" s="3"/>
-      <c r="C186" s="3"/>
+      <c r="B186" s="2"/>
+      <c r="C186" s="2"/>
       <c r="H186">
         <v>3.9864697406340056E-2</v>
       </c>
@@ -19180,8 +19180,8 @@
       </c>
     </row>
     <row r="187" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B187" s="3"/>
-      <c r="C187" s="3"/>
+      <c r="B187" s="2"/>
+      <c r="C187" s="2"/>
       <c r="H187">
         <v>3.9053746397694523E-2</v>
       </c>
@@ -19190,8 +19190,8 @@
       </c>
     </row>
     <row r="188" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B188" s="3"/>
-      <c r="C188" s="3"/>
+      <c r="B188" s="2"/>
+      <c r="C188" s="2"/>
       <c r="H188">
         <v>3.8234726224783862E-2</v>
       </c>
@@ -19200,8 +19200,8 @@
       </c>
     </row>
     <row r="189" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B189" s="3"/>
-      <c r="C189" s="3"/>
+      <c r="B189" s="2"/>
+      <c r="C189" s="2"/>
       <c r="H189">
         <v>3.7466858789625357E-2</v>
       </c>
@@ -19210,8 +19210,8 @@
       </c>
     </row>
     <row r="190" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B190" s="3"/>
-      <c r="C190" s="3"/>
+      <c r="B190" s="2"/>
+      <c r="C190" s="2"/>
       <c r="H190">
         <v>3.676541786743516E-2</v>
       </c>
@@ -19220,8 +19220,8 @@
       </c>
     </row>
     <row r="191" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B191" s="3"/>
-      <c r="C191" s="3"/>
+      <c r="B191" s="2"/>
+      <c r="C191" s="2"/>
       <c r="H191">
         <v>3.6106484149855907E-2</v>
       </c>
@@ -19230,8 +19230,8 @@
       </c>
     </row>
     <row r="192" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B192" s="3"/>
-      <c r="C192" s="3"/>
+      <c r="B192" s="2"/>
+      <c r="C192" s="2"/>
       <c r="H192">
         <v>3.5407925072046112E-2</v>
       </c>
@@ -19240,8 +19240,8 @@
       </c>
     </row>
     <row r="193" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B193" s="3"/>
-      <c r="C193" s="3"/>
+      <c r="B193" s="2"/>
+      <c r="C193" s="2"/>
       <c r="H193">
         <v>3.4765129682997116E-2</v>
       </c>
@@ -19250,8 +19250,8 @@
       </c>
     </row>
     <row r="194" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B194" s="3"/>
-      <c r="C194" s="3"/>
+      <c r="B194" s="2"/>
+      <c r="C194" s="2"/>
       <c r="H194">
         <v>3.4118299711815563E-2</v>
       </c>
@@ -19260,8 +19260,8 @@
       </c>
     </row>
     <row r="195" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B195" s="3"/>
-      <c r="C195" s="3"/>
+      <c r="B195" s="2"/>
+      <c r="C195" s="2"/>
       <c r="H195">
         <v>3.346815561959654E-2</v>
       </c>
@@ -19270,8 +19270,8 @@
       </c>
     </row>
     <row r="196" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B196" s="3"/>
-      <c r="C196" s="3"/>
+      <c r="B196" s="2"/>
+      <c r="C196" s="2"/>
       <c r="H196">
         <v>3.2868587896253604E-2</v>
       </c>
@@ -19280,8 +19280,8 @@
       </c>
     </row>
     <row r="197" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B197" s="3"/>
-      <c r="C197" s="3"/>
+      <c r="B197" s="2"/>
+      <c r="C197" s="2"/>
       <c r="H197">
         <v>3.2299423631123918E-2</v>
       </c>
@@ -19290,8 +19290,8 @@
       </c>
     </row>
     <row r="198" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B198" s="3"/>
-      <c r="C198" s="3"/>
+      <c r="B198" s="2"/>
+      <c r="C198" s="2"/>
       <c r="H198">
         <v>3.1732853025936598E-2</v>
       </c>
@@ -19300,8 +19300,8 @@
       </c>
     </row>
     <row r="199" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B199" s="3"/>
-      <c r="C199" s="3"/>
+      <c r="B199" s="2"/>
+      <c r="C199" s="2"/>
       <c r="H199">
         <v>3.1174783861671471E-2</v>
       </c>
@@ -19310,8 +19310,8 @@
       </c>
     </row>
     <row r="200" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B200" s="3"/>
-      <c r="C200" s="3"/>
+      <c r="B200" s="2"/>
+      <c r="C200" s="2"/>
       <c r="H200">
         <v>3.0608213256484152E-2</v>
       </c>
@@ -19320,8 +19320,8 @@
       </c>
     </row>
     <row r="201" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B201" s="3"/>
-      <c r="C201" s="3"/>
+      <c r="B201" s="2"/>
+      <c r="C201" s="2"/>
       <c r="H201">
         <v>3.0046109510086457E-2</v>
       </c>
@@ -19330,8 +19330,8 @@
       </c>
     </row>
     <row r="202" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B202" s="3"/>
-      <c r="C202" s="3"/>
+      <c r="B202" s="2"/>
+      <c r="C202" s="2"/>
       <c r="H202">
         <v>2.9496541786743519E-2</v>
       </c>
@@ -19340,8 +19340,8 @@
       </c>
     </row>
     <row r="203" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B203" s="3"/>
-      <c r="C203" s="3"/>
+      <c r="B203" s="2"/>
+      <c r="C203" s="2"/>
       <c r="H203">
         <v>2.8947982708933718E-2</v>
       </c>
@@ -19350,8 +19350,8 @@
       </c>
     </row>
     <row r="204" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B204" s="3"/>
-      <c r="C204" s="3"/>
+      <c r="B204" s="2"/>
+      <c r="C204" s="2"/>
       <c r="H204">
         <v>2.8407492795389049E-2</v>
       </c>
@@ -19360,8 +19360,8 @@
       </c>
     </row>
     <row r="205" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B205" s="3"/>
-      <c r="C205" s="3"/>
+      <c r="B205" s="2"/>
+      <c r="C205" s="2"/>
       <c r="H205">
         <v>2.7912824207492797E-2</v>
       </c>
@@ -19370,8 +19370,8 @@
       </c>
     </row>
     <row r="206" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B206" s="3"/>
-      <c r="C206" s="3"/>
+      <c r="B206" s="2"/>
+      <c r="C206" s="2"/>
       <c r="H206">
         <v>2.7405907780979826E-2</v>
       </c>
@@ -19380,8 +19380,8 @@
       </c>
     </row>
     <row r="207" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B207" s="3"/>
-      <c r="C207" s="3"/>
+      <c r="B207" s="2"/>
+      <c r="C207" s="2"/>
       <c r="H207">
         <v>2.6894380403458214E-2</v>
       </c>
@@ -19390,8 +19390,8 @@
       </c>
     </row>
     <row r="208" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B208" s="3"/>
-      <c r="C208" s="3"/>
+      <c r="B208" s="2"/>
+      <c r="C208" s="2"/>
       <c r="H208">
         <v>2.636801152737752E-2</v>
       </c>
@@ -19400,8 +19400,8 @@
       </c>
     </row>
     <row r="209" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B209" s="3"/>
-      <c r="C209" s="3"/>
+      <c r="B209" s="2"/>
+      <c r="C209" s="2"/>
       <c r="H209">
         <v>2.5832564841498561E-2</v>
       </c>
@@ -19410,8 +19410,8 @@
       </c>
     </row>
     <row r="210" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B210" s="3"/>
-      <c r="C210" s="3"/>
+      <c r="B210" s="2"/>
+      <c r="C210" s="2"/>
       <c r="H210">
         <v>2.5290778097982709E-2</v>
       </c>
@@ -19420,8 +19420,8 @@
       </c>
     </row>
     <row r="211" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B211" s="3"/>
-      <c r="C211" s="3"/>
+      <c r="B211" s="2"/>
+      <c r="C211" s="2"/>
       <c r="H211">
         <v>2.4753170028818442E-2</v>
       </c>
@@ -19430,8 +19430,8 @@
       </c>
     </row>
     <row r="212" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B212" s="3"/>
-      <c r="C212" s="3"/>
+      <c r="B212" s="2"/>
+      <c r="C212" s="2"/>
       <c r="H212">
         <v>2.4219164265129683E-2</v>
       </c>
@@ -19440,8 +19440,8 @@
       </c>
     </row>
     <row r="213" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B213" s="3"/>
-      <c r="C213" s="3"/>
+      <c r="B213" s="2"/>
+      <c r="C213" s="2"/>
       <c r="H213">
         <v>2.3686887608069165E-2</v>
       </c>
@@ -19450,8 +19450,8 @@
       </c>
     </row>
     <row r="214" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B214" s="3"/>
-      <c r="C214" s="3"/>
+      <c r="B214" s="2"/>
+      <c r="C214" s="2"/>
       <c r="H214">
         <v>2.3166138328530261E-2</v>
       </c>
@@ -19460,8 +19460,8 @@
       </c>
     </row>
     <row r="215" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B215" s="3"/>
-      <c r="C215" s="3"/>
+      <c r="B215" s="2"/>
+      <c r="C215" s="2"/>
       <c r="H215">
         <v>2.2641930835734871E-2</v>
       </c>
@@ -19470,8 +19470,8 @@
       </c>
     </row>
     <row r="216" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B216" s="3"/>
-      <c r="C216" s="3"/>
+      <c r="B216" s="2"/>
+      <c r="C216" s="2"/>
       <c r="H216">
         <v>2.2120749279538904E-2</v>
       </c>
@@ -19480,8 +19480,8 @@
       </c>
     </row>
     <row r="217" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B217" s="3"/>
-      <c r="C217" s="3"/>
+      <c r="B217" s="2"/>
+      <c r="C217" s="2"/>
       <c r="H217">
         <v>2.1585734870317001E-2</v>
       </c>
@@ -19490,8 +19490,8 @@
       </c>
     </row>
     <row r="218" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B218" s="3"/>
-      <c r="C218" s="3"/>
+      <c r="B218" s="2"/>
+      <c r="C218" s="2"/>
       <c r="H218">
         <v>2.1052305475504324E-2</v>
       </c>
@@ -19500,8 +19500,8 @@
       </c>
     </row>
     <row r="219" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B219" s="3"/>
-      <c r="C219" s="3"/>
+      <c r="B219" s="2"/>
+      <c r="C219" s="2"/>
       <c r="H219">
         <v>2.0510374639769451E-2</v>
       </c>
@@ -19510,8 +19510,8 @@
       </c>
     </row>
     <row r="220" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B220" s="3"/>
-      <c r="C220" s="3"/>
+      <c r="B220" s="2"/>
+      <c r="C220" s="2"/>
       <c r="H220">
         <v>1.9963112391930837E-2</v>
       </c>
@@ -19520,8 +19520,8 @@
       </c>
     </row>
     <row r="221" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B221" s="3"/>
-      <c r="C221" s="3"/>
+      <c r="B221" s="2"/>
+      <c r="C221" s="2"/>
       <c r="H221">
         <v>1.9415273775216138E-2</v>
       </c>
@@ -19530,8 +19530,8 @@
       </c>
     </row>
     <row r="222" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B222" s="3"/>
-      <c r="C222" s="3"/>
+      <c r="B222" s="2"/>
+      <c r="C222" s="2"/>
       <c r="H222">
         <v>1.8857636887608067E-2</v>
       </c>
@@ -19540,8 +19540,8 @@
       </c>
     </row>
     <row r="223" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B223" s="3"/>
-      <c r="C223" s="3"/>
+      <c r="B223" s="2"/>
+      <c r="C223" s="2"/>
       <c r="H223">
         <v>1.8297262247838616E-2</v>
       </c>
@@ -19550,8 +19550,8 @@
       </c>
     </row>
     <row r="224" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B224" s="3"/>
-      <c r="C224" s="3"/>
+      <c r="B224" s="2"/>
+      <c r="C224" s="2"/>
       <c r="H224">
         <v>1.7745677233429395E-2</v>
       </c>
@@ -19560,8 +19560,8 @@
       </c>
     </row>
     <row r="225" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B225" s="3"/>
-      <c r="C225" s="3"/>
+      <c r="B225" s="2"/>
+      <c r="C225" s="2"/>
       <c r="H225">
         <v>1.718184438040346E-2</v>
       </c>
@@ -19570,8 +19570,8 @@
       </c>
     </row>
     <row r="226" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B226" s="3"/>
-      <c r="C226" s="3"/>
+      <c r="B226" s="2"/>
+      <c r="C226" s="2"/>
       <c r="H226">
         <v>1.6614121037463979E-2</v>
       </c>
@@ -19580,8 +19580,8 @@
       </c>
     </row>
     <row r="227" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B227" s="3"/>
-      <c r="C227" s="3"/>
+      <c r="B227" s="2"/>
+      <c r="C227" s="2"/>
       <c r="H227">
         <v>1.6043371757925071E-2</v>
       </c>
@@ -19590,8 +19590,8 @@
       </c>
     </row>
     <row r="228" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B228" s="3"/>
-      <c r="C228" s="3"/>
+      <c r="B228" s="2"/>
+      <c r="C228" s="2"/>
       <c r="H228">
         <v>1.5474351585014409E-2</v>
       </c>
@@ -19600,8 +19600,8 @@
       </c>
     </row>
     <row r="229" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B229" s="3"/>
-      <c r="C229" s="3"/>
+      <c r="B229" s="2"/>
+      <c r="C229" s="2"/>
       <c r="H229">
         <v>1.4889481268011527E-2</v>
       </c>
@@ -19610,8 +19610,8 @@
       </c>
     </row>
     <row r="230" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B230" s="3"/>
-      <c r="C230" s="3"/>
+      <c r="B230" s="2"/>
+      <c r="C230" s="2"/>
       <c r="H230">
         <v>1.4290187319884726E-2</v>
       </c>
@@ -19620,8 +19620,8 @@
       </c>
     </row>
     <row r="231" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B231" s="3"/>
-      <c r="C231" s="3"/>
+      <c r="B231" s="2"/>
+      <c r="C231" s="2"/>
       <c r="H231">
         <v>1.3682463976945246E-2</v>
       </c>
@@ -19630,8 +19630,8 @@
       </c>
     </row>
     <row r="232" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B232" s="3"/>
-      <c r="C232" s="3"/>
+      <c r="B232" s="2"/>
+      <c r="C232" s="2"/>
       <c r="H232">
         <v>1.3067795389048993E-2</v>
       </c>
@@ -19640,8 +19640,8 @@
       </c>
     </row>
     <row r="233" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B233" s="3"/>
-      <c r="C233" s="3"/>
+      <c r="B233" s="2"/>
+      <c r="C233" s="2"/>
       <c r="H233">
         <v>1.2425244956772335E-2</v>
       </c>
@@ -19650,8 +19650,8 @@
       </c>
     </row>
     <row r="234" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B234" s="3"/>
-      <c r="C234" s="3"/>
+      <c r="B234" s="2"/>
+      <c r="C234" s="2"/>
       <c r="H234">
         <v>1.1774293948126801E-2</v>
       </c>
@@ -19660,8 +19660,8 @@
       </c>
     </row>
     <row r="235" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B235" s="3"/>
-      <c r="C235" s="3"/>
+      <c r="B235" s="2"/>
+      <c r="C235" s="2"/>
       <c r="H235">
         <v>1.1129697406340058E-2</v>
       </c>
@@ -19670,8 +19670,8 @@
       </c>
     </row>
     <row r="236" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B236" s="3"/>
-      <c r="C236" s="3"/>
+      <c r="B236" s="2"/>
+      <c r="C236" s="2"/>
       <c r="H236">
         <v>1.0448746397694525E-2</v>
       </c>
@@ -19680,8 +19680,8 @@
       </c>
     </row>
     <row r="237" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B237" s="3"/>
-      <c r="C237" s="3"/>
+      <c r="B237" s="2"/>
+      <c r="C237" s="2"/>
       <c r="H237">
         <v>9.7219452449567711E-3</v>
       </c>
@@ -19690,8 +19690,8 @@
       </c>
     </row>
     <row r="238" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B238" s="3"/>
-      <c r="C238" s="3"/>
+      <c r="B238" s="2"/>
+      <c r="C238" s="2"/>
       <c r="H238">
         <v>8.9593227665706043E-3</v>
       </c>
@@ -19700,8 +19700,8 @@
       </c>
     </row>
     <row r="239" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B239" s="3"/>
-      <c r="C239" s="3"/>
+      <c r="B239" s="2"/>
+      <c r="C239" s="2"/>
       <c r="H239">
         <v>8.1966282420749288E-3</v>
       </c>
@@ -19710,8 +19710,8 @@
       </c>
     </row>
     <row r="240" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B240" s="3"/>
-      <c r="C240" s="3"/>
+      <c r="B240" s="2"/>
+      <c r="C240" s="2"/>
       <c r="H240">
         <v>7.2943804034582126E-3</v>
       </c>
@@ -19720,8 +19720,8 @@
       </c>
     </row>
     <row r="241" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B241" s="3"/>
-      <c r="C241" s="3"/>
+      <c r="B241" s="2"/>
+      <c r="C241" s="2"/>
       <c r="H241">
         <v>6.3574927953890482E-3</v>
       </c>
@@ -19730,8 +19730,8 @@
       </c>
     </row>
     <row r="242" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B242" s="3"/>
-      <c r="C242" s="3"/>
+      <c r="B242" s="2"/>
+      <c r="C242" s="2"/>
       <c r="H242">
         <v>5.397651296829971E-3</v>
       </c>
@@ -19740,8 +19740,8 @@
       </c>
     </row>
     <row r="243" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B243" s="3"/>
-      <c r="C243" s="3"/>
+      <c r="B243" s="2"/>
+      <c r="C243" s="2"/>
       <c r="H243">
         <v>4.1598703170028818E-3</v>
       </c>
@@ -19750,8 +19750,8 @@
       </c>
     </row>
     <row r="244" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B244" s="3"/>
-      <c r="C244" s="3"/>
+      <c r="B244" s="2"/>
+      <c r="C244" s="2"/>
       <c r="H244">
         <v>2.9015417867435155E-3</v>
       </c>
@@ -19760,8 +19760,8 @@
       </c>
     </row>
     <row r="245" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B245" s="3"/>
-      <c r="C245" s="3"/>
+      <c r="B245" s="2"/>
+      <c r="C245" s="2"/>
       <c r="H245">
         <v>1.7372046109510085E-3</v>
       </c>
@@ -19770,8 +19770,8 @@
       </c>
     </row>
     <row r="246" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B246" s="3"/>
-      <c r="C246" s="3"/>
+      <c r="B246" s="2"/>
+      <c r="C246" s="2"/>
       <c r="H246">
         <v>9.8418155619596536E-4</v>
       </c>
@@ -19780,8 +19780,8 @@
       </c>
     </row>
     <row r="247" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B247" s="3"/>
-      <c r="C247" s="3"/>
+      <c r="B247" s="2"/>
+      <c r="C247" s="2"/>
       <c r="H247">
         <v>6.1698991354466859E-4</v>
       </c>
@@ -19790,8 +19790,8 @@
       </c>
     </row>
     <row r="248" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B248" s="3"/>
-      <c r="C248" s="3"/>
+      <c r="B248" s="2"/>
+      <c r="C248" s="2"/>
       <c r="H248">
         <v>3.4201585014409221E-4</v>
       </c>
@@ -19800,8 +19800,8 @@
       </c>
     </row>
     <row r="249" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B249" s="3"/>
-      <c r="C249" s="3"/>
+      <c r="B249" s="2"/>
+      <c r="C249" s="2"/>
       <c r="H249">
         <v>2.5147838616714695E-4</v>
       </c>
@@ -19810,8 +19810,8 @@
       </c>
     </row>
     <row r="250" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B250" s="3"/>
-      <c r="C250" s="3"/>
+      <c r="B250" s="2"/>
+      <c r="C250" s="2"/>
       <c r="H250">
         <v>1.7618011527377521E-4</v>
       </c>
@@ -19820,8 +19820,8 @@
       </c>
     </row>
     <row r="251" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B251" s="3"/>
-      <c r="C251" s="3"/>
+      <c r="B251" s="2"/>
+      <c r="C251" s="2"/>
       <c r="H251">
         <v>1.4388097982708932E-4</v>
       </c>
@@ -19830,8 +19830,8 @@
       </c>
     </row>
     <row r="252" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B252" s="3"/>
-      <c r="C252" s="3"/>
+      <c r="B252" s="2"/>
+      <c r="C252" s="2"/>
       <c r="H252">
         <v>1.1847939481268011E-4</v>
       </c>
@@ -19840,8 +19840,8 @@
       </c>
     </row>
     <row r="253" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B253" s="3"/>
-      <c r="C253" s="3"/>
+      <c r="B253" s="2"/>
+      <c r="C253" s="2"/>
       <c r="H253">
         <v>1.0996945244956774E-4</v>
       </c>
@@ -19850,8 +19850,8 @@
       </c>
     </row>
     <row r="254" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B254" s="3"/>
-      <c r="C254" s="3"/>
+      <c r="B254" s="2"/>
+      <c r="C254" s="2"/>
       <c r="H254">
         <v>1.076092219020173E-4</v>
       </c>
@@ -19860,8 +19860,8 @@
       </c>
     </row>
     <row r="255" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B255" s="3"/>
-      <c r="C255" s="3"/>
+      <c r="B255" s="2"/>
+      <c r="C255" s="2"/>
       <c r="H255">
         <v>1.068543227665706E-4</v>
       </c>
@@ -19870,8 +19870,8 @@
       </c>
     </row>
     <row r="256" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B256" s="3"/>
-      <c r="C256" s="3"/>
+      <c r="B256" s="2"/>
+      <c r="C256" s="2"/>
       <c r="H256">
         <v>1.0336484149855908E-4</v>
       </c>
@@ -19880,8 +19880,8 @@
       </c>
     </row>
     <row r="257" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B257" s="3"/>
-      <c r="C257" s="3"/>
+      <c r="B257" s="2"/>
+      <c r="C257" s="2"/>
       <c r="H257">
         <v>9.7402017291066284E-5</v>
       </c>
@@ -19890,8 +19890,8 @@
       </c>
     </row>
     <row r="258" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B258" s="3"/>
-      <c r="C258" s="3"/>
+      <c r="B258" s="2"/>
+      <c r="C258" s="2"/>
       <c r="H258">
         <v>9.3970605187319878E-5</v>
       </c>
@@ -19900,8 +19900,8 @@
       </c>
     </row>
     <row r="259" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B259" s="3"/>
-      <c r="C259" s="3"/>
+      <c r="B259" s="2"/>
+      <c r="C259" s="2"/>
       <c r="H259">
         <v>9.2046541786743513E-5</v>
       </c>
@@ -19910,8 +19910,8 @@
       </c>
     </row>
     <row r="260" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B260" s="3"/>
-      <c r="C260" s="3"/>
+      <c r="B260" s="2"/>
+      <c r="C260" s="2"/>
       <c r="H260">
         <v>9.0206484149855904E-5</v>
       </c>
@@ -19920,8 +19920,8 @@
       </c>
     </row>
     <row r="261" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B261" s="3"/>
-      <c r="C261" s="3"/>
+      <c r="B261" s="2"/>
+      <c r="C261" s="2"/>
       <c r="H261">
         <v>8.868818443804035E-5</v>
       </c>
@@ -19930,8 +19930,8 @@
       </c>
     </row>
     <row r="262" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B262" s="3"/>
-      <c r="C262" s="3"/>
+      <c r="B262" s="2"/>
+      <c r="C262" s="2"/>
       <c r="H262">
         <v>8.7957348703170029E-5</v>
       </c>
@@ -19940,8 +19940,8 @@
       </c>
     </row>
     <row r="263" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B263" s="3"/>
-      <c r="C263" s="3"/>
+      <c r="B263" s="2"/>
+      <c r="C263" s="2"/>
       <c r="H263">
         <v>8.7260662824207495E-5</v>
       </c>
@@ -19950,8 +19950,8 @@
       </c>
     </row>
     <row r="264" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B264" s="3"/>
-      <c r="C264" s="3"/>
+      <c r="B264" s="2"/>
+      <c r="C264" s="2"/>
       <c r="H264">
         <v>8.672074927953891E-5</v>
       </c>
@@ -19960,8 +19960,8 @@
       </c>
     </row>
     <row r="265" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B265" s="3"/>
-      <c r="C265" s="3"/>
+      <c r="B265" s="2"/>
+      <c r="C265" s="2"/>
       <c r="H265">
         <v>8.6175504322766566E-5</v>
       </c>
@@ -19970,8 +19970,8 @@
       </c>
     </row>
     <row r="266" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B266" s="3"/>
-      <c r="C266" s="3"/>
+      <c r="B266" s="2"/>
+      <c r="C266" s="2"/>
       <c r="H266">
         <v>8.6214265129683004E-5</v>
       </c>
@@ -19980,8 +19980,8 @@
       </c>
     </row>
     <row r="267" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B267" s="3"/>
-      <c r="C267" s="3"/>
+      <c r="B267" s="2"/>
+      <c r="C267" s="2"/>
       <c r="H267">
         <v>8.6192507204610943E-5</v>
       </c>
@@ -19990,8 +19990,8 @@
       </c>
     </row>
     <row r="268" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B268" s="3"/>
-      <c r="C268" s="3"/>
+      <c r="B268" s="2"/>
+      <c r="C268" s="2"/>
       <c r="H268">
         <v>8.5883861671469736E-5</v>
       </c>
@@ -20000,8 +20000,8 @@
       </c>
     </row>
     <row r="269" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B269" s="3"/>
-      <c r="C269" s="3"/>
+      <c r="B269" s="2"/>
+      <c r="C269" s="2"/>
       <c r="H269">
         <v>8.5483573487031702E-5</v>
       </c>
@@ -20010,8 +20010,8 @@
       </c>
     </row>
     <row r="270" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B270" s="3"/>
-      <c r="C270" s="3"/>
+      <c r="B270" s="2"/>
+      <c r="C270" s="2"/>
       <c r="H270">
         <v>8.5342795389048987E-5</v>
       </c>
@@ -20020,8 +20020,8 @@
       </c>
     </row>
     <row r="271" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B271" s="3"/>
-      <c r="C271" s="3"/>
+      <c r="B271" s="2"/>
+      <c r="C271" s="2"/>
       <c r="H271">
         <v>8.527276657060519E-5</v>
       </c>
@@ -20030,8 +20030,8 @@
       </c>
     </row>
     <row r="272" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B272" s="3"/>
-      <c r="C272" s="3"/>
+      <c r="B272" s="2"/>
+      <c r="C272" s="2"/>
       <c r="H272">
         <v>8.5156772334293954E-5</v>
       </c>
@@ -20040,8 +20040,8 @@
       </c>
     </row>
     <row r="273" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B273" s="3"/>
-      <c r="C273" s="3"/>
+      <c r="B273" s="2"/>
+      <c r="C273" s="2"/>
       <c r="H273">
         <v>8.516916426512968E-5</v>
       </c>
@@ -20050,8 +20050,8 @@
       </c>
     </row>
     <row r="274" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B274" s="3"/>
-      <c r="C274" s="3"/>
+      <c r="B274" s="2"/>
+      <c r="C274" s="2"/>
       <c r="H274">
         <v>8.5220893371757933E-5</v>
       </c>
@@ -20060,8 +20060,8 @@
       </c>
     </row>
     <row r="275" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B275" s="3"/>
-      <c r="C275" s="3"/>
+      <c r="B275" s="2"/>
+      <c r="C275" s="2"/>
       <c r="H275">
         <v>8.5203890489913542E-5</v>
       </c>
@@ -20070,8 +20070,8 @@
       </c>
     </row>
     <row r="276" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B276" s="3"/>
-      <c r="C276" s="3"/>
+      <c r="B276" s="2"/>
+      <c r="C276" s="2"/>
       <c r="H276">
         <v>8.5217579250720463E-5</v>
       </c>
@@ -20080,8 +20080,8 @@
       </c>
     </row>
     <row r="277" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B277" s="3"/>
-      <c r="C277" s="3"/>
+      <c r="B277" s="2"/>
+      <c r="C277" s="2"/>
       <c r="H277">
         <v>8.5206051873198849E-5</v>
       </c>
@@ -20090,8 +20090,8 @@
       </c>
     </row>
     <row r="278" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B278" s="3"/>
-      <c r="C278" s="3"/>
+      <c r="B278" s="2"/>
+      <c r="C278" s="2"/>
       <c r="H278">
         <v>8.519827089337176E-5</v>
       </c>
@@ -20100,8 +20100,8 @@
       </c>
     </row>
     <row r="279" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B279" s="3"/>
-      <c r="C279" s="3"/>
+      <c r="B279" s="2"/>
+      <c r="C279" s="2"/>
       <c r="H279">
         <v>8.5210951008645537E-5</v>
       </c>
@@ -20110,8 +20110,8 @@
       </c>
     </row>
     <row r="280" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B280" s="3"/>
-      <c r="C280" s="3"/>
+      <c r="B280" s="2"/>
+      <c r="C280" s="2"/>
       <c r="H280">
         <v>8.5232997118155621E-5</v>
       </c>
@@ -20120,8 +20120,8 @@
       </c>
     </row>
     <row r="281" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B281" s="3"/>
-      <c r="C281" s="3"/>
+      <c r="B281" s="2"/>
+      <c r="C281" s="2"/>
       <c r="H281">
         <v>8.5252593659942361E-5</v>
       </c>
@@ -20130,8 +20130,8 @@
       </c>
     </row>
     <row r="282" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B282" s="3"/>
-      <c r="C282" s="3"/>
+      <c r="B282" s="2"/>
+      <c r="C282" s="2"/>
       <c r="H282">
         <v>8.5277377521613827E-5</v>
       </c>
@@ -20140,8 +20140,8 @@
       </c>
     </row>
     <row r="283" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B283" s="3"/>
-      <c r="C283" s="3"/>
+      <c r="B283" s="2"/>
+      <c r="C283" s="2"/>
       <c r="H283">
         <v>8.5305187319884726E-5</v>
       </c>
@@ -20150,8 +20150,8 @@
       </c>
     </row>
     <row r="284" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B284" s="3"/>
-      <c r="C284" s="3"/>
+      <c r="B284" s="2"/>
+      <c r="C284" s="2"/>
       <c r="H284">
         <v>8.5377377521613843E-5</v>
       </c>
@@ -20160,8 +20160,8 @@
       </c>
     </row>
     <row r="285" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B285" s="3"/>
-      <c r="C285" s="3"/>
+      <c r="B285" s="2"/>
+      <c r="C285" s="2"/>
       <c r="H285">
         <v>8.5435302593659938E-5</v>
       </c>
@@ -20170,8 +20170,8 @@
       </c>
     </row>
     <row r="286" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B286" s="3"/>
-      <c r="C286" s="3"/>
+      <c r="B286" s="2"/>
+      <c r="C286" s="2"/>
       <c r="H286">
         <v>8.5565417867435164E-5</v>
       </c>
@@ -20180,8 +20180,8 @@
       </c>
     </row>
     <row r="287" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B287" s="3"/>
-      <c r="C287" s="3"/>
+      <c r="B287" s="2"/>
+      <c r="C287" s="2"/>
       <c r="H287">
         <v>8.5713976945244954E-5</v>
       </c>
@@ -20190,8 +20190,8 @@
       </c>
     </row>
     <row r="288" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B288" s="3"/>
-      <c r="C288" s="3"/>
+      <c r="B288" s="2"/>
+      <c r="C288" s="2"/>
       <c r="H288">
         <v>8.5818443804034576E-5</v>
       </c>
@@ -20200,8 +20200,8 @@
       </c>
     </row>
     <row r="289" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B289" s="3"/>
-      <c r="C289" s="3"/>
+      <c r="B289" s="2"/>
+      <c r="C289" s="2"/>
       <c r="H289">
         <v>8.5849423631123925E-5</v>
       </c>
@@ -20210,8 +20210,8 @@
       </c>
     </row>
     <row r="290" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B290" s="3"/>
-      <c r="C290" s="3"/>
+      <c r="B290" s="2"/>
+      <c r="C290" s="2"/>
       <c r="H290">
         <v>8.587867435158501E-5</v>
       </c>
@@ -20220,8 +20220,8 @@
       </c>
     </row>
     <row r="291" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B291" s="3"/>
-      <c r="C291" s="3"/>
+      <c r="B291" s="2"/>
+      <c r="C291" s="2"/>
       <c r="H291">
         <v>8.5907780979827089E-5</v>
       </c>
@@ -20230,8 +20230,8 @@
       </c>
     </row>
     <row r="292" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B292" s="3"/>
-      <c r="C292" s="3"/>
+      <c r="B292" s="2"/>
+      <c r="C292" s="2"/>
       <c r="H292">
         <v>8.5954034582132565E-5</v>
       </c>
@@ -20240,8 +20240,8 @@
       </c>
     </row>
     <row r="293" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B293" s="3"/>
-      <c r="C293" s="3"/>
+      <c r="B293" s="2"/>
+      <c r="C293" s="2"/>
       <c r="H293">
         <v>8.6004466858789622E-5</v>
       </c>
@@ -20250,8 +20250,8 @@
       </c>
     </row>
     <row r="294" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B294" s="3"/>
-      <c r="C294" s="3"/>
+      <c r="B294" s="2"/>
+      <c r="C294" s="2"/>
       <c r="H294">
         <v>8.6040057636887609E-5</v>
       </c>
@@ -20260,8 +20260,8 @@
       </c>
     </row>
     <row r="295" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B295" s="3"/>
-      <c r="C295" s="3"/>
+      <c r="B295" s="2"/>
+      <c r="C295" s="2"/>
       <c r="H295">
         <v>8.6075792507204615E-5</v>
       </c>
@@ -20270,8 +20270,8 @@
       </c>
     </row>
     <row r="296" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B296" s="3"/>
-      <c r="C296" s="3"/>
+      <c r="B296" s="2"/>
+      <c r="C296" s="2"/>
       <c r="H296">
         <v>8.6097406340057643E-5</v>
       </c>
@@ -20280,8 +20280,8 @@
       </c>
     </row>
     <row r="297" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B297" s="3"/>
-      <c r="C297" s="3"/>
+      <c r="B297" s="2"/>
+      <c r="C297" s="2"/>
       <c r="H297">
         <v>8.6159510086455333E-5</v>
       </c>
@@ -20290,8 +20290,8 @@
       </c>
     </row>
     <row r="298" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B298" s="3"/>
-      <c r="C298" s="3"/>
+      <c r="B298" s="2"/>
+      <c r="C298" s="2"/>
       <c r="H298">
         <v>8.6253458213256484E-5</v>
       </c>
@@ -20300,8 +20300,8 @@
       </c>
     </row>
     <row r="299" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B299" s="3"/>
-      <c r="C299" s="3"/>
+      <c r="B299" s="2"/>
+      <c r="C299" s="2"/>
       <c r="H299">
         <v>8.6344236311239198E-5</v>
       </c>
@@ -20310,8 +20310,8 @@
       </c>
     </row>
     <row r="300" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B300" s="3"/>
-      <c r="C300" s="3"/>
+      <c r="B300" s="2"/>
+      <c r="C300" s="2"/>
       <c r="H300">
         <v>8.6427953890489916E-5</v>
       </c>
@@ -20320,8 +20320,8 @@
       </c>
     </row>
     <row r="301" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B301" s="3"/>
-      <c r="C301" s="3"/>
+      <c r="B301" s="2"/>
+      <c r="C301" s="2"/>
       <c r="H301">
         <v>8.6498559077809802E-5</v>
       </c>
@@ -20330,8 +20330,8 @@
       </c>
     </row>
     <row r="302" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B302" s="3"/>
-      <c r="C302" s="3"/>
+      <c r="B302" s="2"/>
+      <c r="C302" s="2"/>
       <c r="H302">
         <v>8.6557636887608073E-5</v>
       </c>
@@ -20340,8 +20340,8 @@
       </c>
     </row>
     <row r="303" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B303" s="3"/>
-      <c r="C303" s="3"/>
+      <c r="B303" s="2"/>
+      <c r="C303" s="2"/>
       <c r="H303">
         <v>8.6613256484149856E-5</v>
       </c>
@@ -20350,8 +20350,8 @@
       </c>
     </row>
     <row r="304" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B304" s="3"/>
-      <c r="C304" s="3"/>
+      <c r="B304" s="2"/>
+      <c r="C304" s="2"/>
       <c r="H304">
         <v>8.6669164265129676E-5</v>
       </c>
@@ -20360,8 +20360,8 @@
       </c>
     </row>
     <row r="305" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B305" s="3"/>
-      <c r="C305" s="3"/>
+      <c r="B305" s="2"/>
+      <c r="C305" s="2"/>
       <c r="H305">
         <v>8.6725216138328529E-5</v>
       </c>
@@ -20370,8 +20370,8 @@
       </c>
     </row>
     <row r="306" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B306" s="3"/>
-      <c r="C306" s="3"/>
+      <c r="B306" s="2"/>
+      <c r="C306" s="2"/>
       <c r="H306">
         <v>8.6769740634005767E-5</v>
       </c>
@@ -20380,8 +20380,8 @@
       </c>
     </row>
     <row r="307" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B307" s="3"/>
-      <c r="C307" s="3"/>
+      <c r="B307" s="2"/>
+      <c r="C307" s="2"/>
       <c r="H307">
         <v>8.6812824207492791E-5</v>
       </c>
@@ -20390,8 +20390,8 @@
       </c>
     </row>
     <row r="308" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B308" s="3"/>
-      <c r="C308" s="3"/>
+      <c r="B308" s="2"/>
+      <c r="C308" s="2"/>
       <c r="H308">
         <v>8.6852881844380411E-5</v>
       </c>
@@ -20400,8 +20400,8 @@
       </c>
     </row>
     <row r="309" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B309" s="3"/>
-      <c r="C309" s="3"/>
+      <c r="B309" s="2"/>
+      <c r="C309" s="2"/>
       <c r="H309">
         <v>8.6885014409221909E-5</v>
       </c>
@@ -20410,8 +20410,8 @@
       </c>
     </row>
     <row r="310" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B310" s="3"/>
-      <c r="C310" s="3"/>
+      <c r="B310" s="2"/>
+      <c r="C310" s="2"/>
       <c r="H310">
         <v>8.6908069164265124E-5</v>
       </c>
@@ -20420,8 +20420,8 @@
       </c>
     </row>
     <row r="311" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B311" s="3"/>
-      <c r="C311" s="3"/>
+      <c r="B311" s="2"/>
+      <c r="C311" s="2"/>
       <c r="H311">
         <v>8.6929106628242078E-5</v>
       </c>
@@ -20430,8 +20430,8 @@
       </c>
     </row>
     <row r="312" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B312" s="3"/>
-      <c r="C312" s="3"/>
+      <c r="B312" s="2"/>
+      <c r="C312" s="2"/>
       <c r="H312">
         <v>8.6952305475504325E-5</v>
       </c>
@@ -20440,8 +20440,8 @@
       </c>
     </row>
     <row r="313" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B313" s="3"/>
-      <c r="C313" s="3"/>
+      <c r="B313" s="2"/>
+      <c r="C313" s="2"/>
       <c r="H313">
         <v>8.6984582132564842E-5</v>
       </c>
@@ -20450,8 +20450,8 @@
       </c>
     </row>
     <row r="314" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B314" s="3"/>
-      <c r="C314" s="3"/>
+      <c r="B314" s="2"/>
+      <c r="C314" s="2"/>
       <c r="H314">
         <v>8.7017435158501447E-5</v>
       </c>
@@ -20460,8 +20460,8 @@
       </c>
     </row>
     <row r="315" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B315" s="3"/>
-      <c r="C315" s="3"/>
+      <c r="B315" s="2"/>
+      <c r="C315" s="2"/>
       <c r="H315">
         <v>8.7042939481268006E-5</v>
       </c>
@@ -20470,8 +20470,8 @@
       </c>
     </row>
     <row r="316" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B316" s="3"/>
-      <c r="C316" s="3"/>
+      <c r="B316" s="2"/>
+      <c r="C316" s="2"/>
       <c r="H316">
         <v>8.7066570605187309E-5</v>
       </c>
@@ -20480,8 +20480,8 @@
       </c>
     </row>
     <row r="317" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B317" s="3"/>
-      <c r="C317" s="3"/>
+      <c r="B317" s="2"/>
+      <c r="C317" s="2"/>
       <c r="H317">
         <v>8.7090345821325645E-5</v>
       </c>
@@ -20490,8 +20490,8 @@
       </c>
     </row>
     <row r="318" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B318" s="3"/>
-      <c r="C318" s="3"/>
+      <c r="B318" s="2"/>
+      <c r="C318" s="2"/>
       <c r="H318">
         <v>8.7109510086455329E-5</v>
       </c>
@@ -20500,8 +20500,8 @@
       </c>
     </row>
     <row r="319" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B319" s="3"/>
-      <c r="C319" s="3"/>
+      <c r="B319" s="2"/>
+      <c r="C319" s="2"/>
       <c r="H319">
         <v>8.7132708933717576E-5</v>
       </c>
@@ -20510,8 +20510,8 @@
       </c>
     </row>
     <row r="320" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B320" s="3"/>
-      <c r="C320" s="3"/>
+      <c r="B320" s="2"/>
+      <c r="C320" s="2"/>
       <c r="H320">
         <v>8.7148847262247841E-5</v>
       </c>
@@ -20520,8 +20520,8 @@
       </c>
     </row>
     <row r="321" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B321" s="3"/>
-      <c r="C321" s="3"/>
+      <c r="B321" s="2"/>
+      <c r="C321" s="2"/>
       <c r="H321">
         <v>8.7162680115273781E-5</v>
       </c>
@@ -20530,8 +20530,8 @@
       </c>
     </row>
     <row r="322" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B322" s="3"/>
-      <c r="C322" s="3"/>
+      <c r="B322" s="2"/>
+      <c r="C322" s="2"/>
       <c r="H322">
         <v>8.718429394812681E-5</v>
       </c>
@@ -20540,8 +20540,8 @@
       </c>
     </row>
     <row r="323" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B323" s="3"/>
-      <c r="C323" s="3"/>
+      <c r="B323" s="2"/>
+      <c r="C323" s="2"/>
       <c r="H323">
         <v>8.7209077809798275E-5</v>
       </c>
@@ -20550,8 +20550,8 @@
       </c>
     </row>
     <row r="324" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B324" s="3"/>
-      <c r="C324" s="3"/>
+      <c r="B324" s="2"/>
+      <c r="C324" s="2"/>
       <c r="H324">
         <v>8.7233861671469741E-5</v>
       </c>
@@ -20560,8 +20560,8 @@
       </c>
     </row>
     <row r="325" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B325" s="3"/>
-      <c r="C325" s="3"/>
+      <c r="B325" s="2"/>
+      <c r="C325" s="2"/>
       <c r="H325">
         <v>8.725691642651297E-5</v>
       </c>
@@ -20570,8 +20570,8 @@
       </c>
     </row>
     <row r="326" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B326" s="3"/>
-      <c r="C326" s="3"/>
+      <c r="B326" s="2"/>
+      <c r="C326" s="2"/>
       <c r="H326">
         <v>8.7286023054755036E-5</v>
       </c>
@@ -20580,8 +20580,8 @@
       </c>
     </row>
     <row r="327" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B327" s="3"/>
-      <c r="C327" s="3"/>
+      <c r="B327" s="2"/>
+      <c r="C327" s="2"/>
       <c r="H327">
         <v>8.7314409221902022E-5</v>
       </c>
@@ -20590,8 +20590,8 @@
       </c>
     </row>
     <row r="328" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B328" s="3"/>
-      <c r="C328" s="3"/>
+      <c r="B328" s="2"/>
+      <c r="C328" s="2"/>
       <c r="H328">
         <v>8.7340057636887614E-5</v>
       </c>
@@ -20600,8 +20600,8 @@
       </c>
     </row>
     <row r="329" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B329" s="3"/>
-      <c r="C329" s="3"/>
+      <c r="B329" s="2"/>
+      <c r="C329" s="2"/>
       <c r="H329">
         <v>8.736657060518733E-5</v>
       </c>
@@ -20610,8 +20610,8 @@
       </c>
     </row>
     <row r="330" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B330" s="3"/>
-      <c r="C330" s="3"/>
+      <c r="B330" s="2"/>
+      <c r="C330" s="2"/>
       <c r="H330">
         <v>8.7393083573487034E-5</v>
       </c>
@@ -20620,8 +20620,8 @@
       </c>
     </row>
     <row r="331" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B331" s="3"/>
-      <c r="C331" s="3"/>
+      <c r="B331" s="2"/>
+      <c r="C331" s="2"/>
       <c r="H331">
         <v>8.7419020172910662E-5</v>
       </c>
@@ -20630,8 +20630,8 @@
       </c>
     </row>
     <row r="332" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B332" s="3"/>
-      <c r="C332" s="3"/>
+      <c r="B332" s="2"/>
+      <c r="C332" s="2"/>
       <c r="H332">
         <v>8.7444956772334291E-5</v>
       </c>
@@ -20640,8 +20640,8 @@
       </c>
     </row>
     <row r="333" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B333" s="3"/>
-      <c r="C333" s="3"/>
+      <c r="B333" s="2"/>
+      <c r="C333" s="2"/>
       <c r="H333">
         <v>8.7467002881844389E-5</v>
       </c>
@@ -20650,8 +20650,8 @@
       </c>
     </row>
     <row r="334" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B334" s="3"/>
-      <c r="C334" s="3"/>
+      <c r="B334" s="2"/>
+      <c r="C334" s="2"/>
       <c r="H334">
         <v>8.7488184438040348E-5</v>
       </c>
@@ -20660,8 +20660,8 @@
       </c>
     </row>
     <row r="335" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B335" s="3"/>
-      <c r="C335" s="3"/>
+      <c r="B335" s="2"/>
+      <c r="C335" s="2"/>
       <c r="H335">
         <v>8.7509510086455325E-5</v>
       </c>
@@ -20670,8 +20670,8 @@
       </c>
     </row>
     <row r="336" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B336" s="3"/>
-      <c r="C336" s="3"/>
+      <c r="B336" s="2"/>
+      <c r="C336" s="2"/>
       <c r="H336">
         <v>8.7530835734870316E-5</v>
       </c>
@@ -20680,8 +20680,8 @@
       </c>
     </row>
     <row r="337" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B337" s="3"/>
-      <c r="C337" s="3"/>
+      <c r="B337" s="2"/>
+      <c r="C337" s="2"/>
       <c r="H337">
         <v>8.7551729106628238E-5</v>
       </c>
@@ -20690,8 +20690,8 @@
       </c>
     </row>
     <row r="338" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B338" s="3"/>
-      <c r="C338" s="3"/>
+      <c r="B338" s="2"/>
+      <c r="C338" s="2"/>
       <c r="H338">
         <v>8.7572622478386173E-5</v>
       </c>
@@ -20700,8 +20700,8 @@
       </c>
     </row>
     <row r="339" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B339" s="3"/>
-      <c r="C339" s="3"/>
+      <c r="B339" s="2"/>
+      <c r="C339" s="2"/>
       <c r="H339">
         <v>8.7593515850144094E-5</v>
       </c>
@@ -20710,8 +20710,8 @@
       </c>
     </row>
     <row r="340" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B340" s="3"/>
-      <c r="C340" s="3"/>
+      <c r="B340" s="2"/>
+      <c r="C340" s="2"/>
       <c r="H340">
         <v>8.7607492795389053E-5</v>
       </c>
@@ -20720,8 +20720,8 @@
       </c>
     </row>
     <row r="341" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B341" s="3"/>
-      <c r="C341" s="3"/>
+      <c r="B341" s="2"/>
+      <c r="C341" s="2"/>
       <c r="H341">
         <v>8.7620317002881848E-5</v>
       </c>
@@ -20730,8 +20730,8 @@
       </c>
     </row>
     <row r="342" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B342" s="3"/>
-      <c r="C342" s="3"/>
+      <c r="B342" s="2"/>
+      <c r="C342" s="2"/>
       <c r="H342">
         <v>8.7633141210374644E-5</v>
       </c>
@@ -20740,8 +20740,8 @@
       </c>
     </row>
     <row r="343" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B343" s="3"/>
-      <c r="C343" s="3"/>
+      <c r="B343" s="2"/>
+      <c r="C343" s="2"/>
       <c r="H343">
         <v>8.7647118155619603E-5</v>
       </c>
@@ -20750,8 +20750,8 @@
       </c>
     </row>
     <row r="344" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B344" s="3"/>
-      <c r="C344" s="3"/>
+      <c r="B344" s="2"/>
+      <c r="C344" s="2"/>
       <c r="H344">
         <v>8.7663832853025943E-5</v>
       </c>
@@ -20760,8 +20760,8 @@
       </c>
     </row>
     <row r="345" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B345" s="3"/>
-      <c r="C345" s="3"/>
+      <c r="B345" s="2"/>
+      <c r="C345" s="2"/>
       <c r="H345">
         <v>8.7680115273775213E-5</v>
       </c>
@@ -20770,8 +20770,8 @@
       </c>
     </row>
     <row r="346" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B346" s="3"/>
-      <c r="C346" s="3"/>
+      <c r="B346" s="2"/>
+      <c r="C346" s="2"/>
       <c r="H346">
         <v>8.7696397694524497E-5</v>
       </c>
@@ -20780,8 +20780,8 @@
       </c>
     </row>
     <row r="347" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B347" s="3"/>
-      <c r="C347" s="3"/>
+      <c r="B347" s="2"/>
+      <c r="C347" s="2"/>
       <c r="H347">
         <v>8.7713256484149856E-5</v>
       </c>
@@ -20790,8 +20790,8 @@
       </c>
     </row>
     <row r="348" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B348" s="3"/>
-      <c r="C348" s="3"/>
+      <c r="B348" s="2"/>
+      <c r="C348" s="2"/>
       <c r="H348">
         <v>8.7730547550432284E-5</v>
       </c>
@@ -20800,8 +20800,8 @@
       </c>
     </row>
     <row r="349" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B349" s="3"/>
-      <c r="C349" s="3"/>
+      <c r="B349" s="2"/>
+      <c r="C349" s="2"/>
       <c r="H349">
         <v>8.7747550432276661E-5</v>
       </c>
@@ -20810,8 +20810,8 @@
       </c>
     </row>
     <row r="350" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B350" s="3"/>
-      <c r="C350" s="3"/>
+      <c r="B350" s="2"/>
+      <c r="C350" s="2"/>
       <c r="H350">
         <v>8.7760230547550424E-5</v>
       </c>
@@ -20820,8 +20820,8 @@
       </c>
     </row>
     <row r="351" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B351" s="3"/>
-      <c r="C351" s="3"/>
+      <c r="B351" s="2"/>
+      <c r="C351" s="2"/>
       <c r="H351">
         <v>8.7772910662824201E-5</v>
       </c>
@@ -20830,8 +20830,8 @@
       </c>
     </row>
     <row r="352" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B352" s="3"/>
-      <c r="C352" s="3"/>
+      <c r="B352" s="2"/>
+      <c r="C352" s="2"/>
       <c r="H352">
         <v>8.7785590778097978E-5</v>
       </c>
@@ -20840,8 +20840,8 @@
       </c>
     </row>
     <row r="353" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B353" s="3"/>
-      <c r="C353" s="3"/>
+      <c r="B353" s="2"/>
+      <c r="C353" s="2"/>
       <c r="H353">
         <v>8.7798270893371755E-5</v>
       </c>
@@ -20850,8 +20850,8 @@
       </c>
     </row>
     <row r="354" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B354" s="3"/>
-      <c r="C354" s="3"/>
+      <c r="B354" s="2"/>
+      <c r="C354" s="2"/>
       <c r="H354">
         <v>8.7810951008645532E-5</v>
       </c>
@@ -20860,8 +20860,8 @@
       </c>
     </row>
     <row r="355" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B355" s="3"/>
-      <c r="C355" s="3"/>
+      <c r="B355" s="2"/>
+      <c r="C355" s="2"/>
       <c r="H355">
         <v>8.7819164265129691E-5</v>
       </c>
@@ -20870,8 +20870,8 @@
       </c>
     </row>
     <row r="356" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B356" s="3"/>
-      <c r="C356" s="3"/>
+      <c r="B356" s="2"/>
+      <c r="C356" s="2"/>
       <c r="H356">
         <v>8.7826801152737747E-5</v>
       </c>
@@ -20880,8 +20880,8 @@
       </c>
     </row>
     <row r="357" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B357" s="3"/>
-      <c r="C357" s="3"/>
+      <c r="B357" s="2"/>
+      <c r="C357" s="2"/>
       <c r="H357">
         <v>8.783559077809798E-5</v>
       </c>
@@ -20890,8 +20890,8 @@
       </c>
     </row>
     <row r="358" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B358" s="3"/>
-      <c r="C358" s="3"/>
+      <c r="B358" s="2"/>
+      <c r="C358" s="2"/>
       <c r="H358">
         <v>8.7844380403458212E-5</v>
       </c>
@@ -20900,8 +20900,8 @@
       </c>
     </row>
     <row r="359" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B359" s="3"/>
-      <c r="C359" s="3"/>
+      <c r="B359" s="2"/>
+      <c r="C359" s="2"/>
       <c r="H359">
         <v>8.7853314121037464E-5</v>
       </c>
@@ -20910,8 +20910,8 @@
       </c>
     </row>
     <row r="360" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B360" s="3"/>
-      <c r="C360" s="3"/>
+      <c r="B360" s="2"/>
+      <c r="C360" s="2"/>
       <c r="H360">
         <v>8.7862247838616715E-5</v>
       </c>
@@ -20920,8 +20920,8 @@
       </c>
     </row>
     <row r="361" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B361" s="3"/>
-      <c r="C361" s="3"/>
+      <c r="B361" s="2"/>
+      <c r="C361" s="2"/>
       <c r="H361">
         <v>8.7871325648414985E-5</v>
       </c>
@@ -20930,8 +20930,8 @@
       </c>
     </row>
     <row r="362" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B362" s="3"/>
-      <c r="C362" s="3"/>
+      <c r="B362" s="2"/>
+      <c r="C362" s="2"/>
       <c r="H362">
         <v>8.7880547550432274E-5</v>
       </c>
@@ -20940,8 +20940,8 @@
       </c>
     </row>
     <row r="363" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B363" s="3"/>
-      <c r="C363" s="3"/>
+      <c r="B363" s="2"/>
+      <c r="C363" s="2"/>
       <c r="H363">
         <v>8.7889625360230544E-5</v>
       </c>
@@ -20950,8 +20950,8 @@
       </c>
     </row>
     <row r="364" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B364" s="3"/>
-      <c r="C364" s="3"/>
+      <c r="B364" s="2"/>
+      <c r="C364" s="2"/>
       <c r="H364">
         <v>8.7898703170028814E-5</v>
       </c>
@@ -20960,8 +20960,8 @@
       </c>
     </row>
     <row r="365" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B365" s="3"/>
-      <c r="C365" s="3"/>
+      <c r="B365" s="2"/>
+      <c r="C365" s="2"/>
       <c r="H365">
         <v>8.7907925072046116E-5</v>
       </c>
@@ -20970,8 +20970,8 @@
       </c>
     </row>
     <row r="366" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B366" s="3"/>
-      <c r="C366" s="3"/>
+      <c r="B366" s="2"/>
+      <c r="C366" s="2"/>
       <c r="H366">
         <v>8.7917002881844386E-5</v>
       </c>
@@ -20980,8 +20980,8 @@
       </c>
     </row>
     <row r="367" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B367" s="3"/>
-      <c r="C367" s="3"/>
+      <c r="B367" s="2"/>
+      <c r="C367" s="2"/>
       <c r="H367">
         <v>8.79256484149856E-5</v>
       </c>
@@ -20990,8 +20990,8 @@
       </c>
     </row>
     <row r="368" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B368" s="3"/>
-      <c r="C368" s="3"/>
+      <c r="B368" s="2"/>
+      <c r="C368" s="2"/>
       <c r="H368">
         <v>8.7932708933717582E-5</v>
       </c>
@@ -21000,8 +21000,8 @@
       </c>
     </row>
     <row r="369" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B369" s="3"/>
-      <c r="C369" s="3"/>
+      <c r="B369" s="2"/>
+      <c r="C369" s="2"/>
       <c r="H369">
         <v>8.793904899135447E-5</v>
       </c>
@@ -21010,8 +21010,8 @@
       </c>
     </row>
     <row r="370" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B370" s="3"/>
-      <c r="C370" s="3"/>
+      <c r="B370" s="2"/>
+      <c r="C370" s="2"/>
       <c r="H370">
         <v>8.7945389048991359E-5</v>
       </c>
@@ -21020,8 +21020,8 @@
       </c>
     </row>
     <row r="371" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B371" s="3"/>
-      <c r="C371" s="3"/>
+      <c r="B371" s="2"/>
+      <c r="C371" s="2"/>
       <c r="H371">
         <v>8.7951729106628247E-5</v>
       </c>
@@ -21030,8 +21030,8 @@
       </c>
     </row>
     <row r="372" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B372" s="3"/>
-      <c r="C372" s="3"/>
+      <c r="B372" s="2"/>
+      <c r="C372" s="2"/>
       <c r="H372">
         <v>8.7959365994236317E-5</v>
       </c>
@@ -21040,8 +21040,8 @@
       </c>
     </row>
     <row r="373" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B373" s="3"/>
-      <c r="C373" s="3"/>
+      <c r="B373" s="2"/>
+      <c r="C373" s="2"/>
       <c r="H373">
         <v>8.7966858789625355E-5</v>
       </c>
@@ -21050,8 +21050,8 @@
       </c>
     </row>
     <row r="374" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B374" s="3"/>
-      <c r="C374" s="3"/>
+      <c r="B374" s="2"/>
+      <c r="C374" s="2"/>
       <c r="H374">
         <v>8.7974495677233425E-5</v>
       </c>
@@ -21060,8 +21060,8 @@
       </c>
     </row>
     <row r="375" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B375" s="3"/>
-      <c r="C375" s="3"/>
+      <c r="B375" s="2"/>
+      <c r="C375" s="2"/>
       <c r="H375">
         <v>8.7981988472622476E-5</v>
       </c>
@@ -21070,8 +21070,8 @@
       </c>
     </row>
     <row r="376" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B376" s="3"/>
-      <c r="C376" s="3"/>
+      <c r="B376" s="2"/>
+      <c r="C376" s="2"/>
       <c r="H376">
         <v>8.7989625360230546E-5</v>
       </c>
@@ -21080,8 +21080,8 @@
       </c>
     </row>
     <row r="377" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B377" s="3"/>
-      <c r="C377" s="3"/>
+      <c r="B377" s="2"/>
+      <c r="C377" s="2"/>
       <c r="H377">
         <v>8.7997118155619598E-5</v>
       </c>
@@ -21090,8 +21090,8 @@
       </c>
     </row>
     <row r="378" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B378" s="3"/>
-      <c r="C378" s="3"/>
+      <c r="B378" s="2"/>
+      <c r="C378" s="2"/>
       <c r="H378">
         <v>8.8004755043227667E-5</v>
       </c>
@@ -21100,8 +21100,8 @@
       </c>
     </row>
     <row r="379" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B379" s="3"/>
-      <c r="C379" s="3"/>
+      <c r="B379" s="2"/>
+      <c r="C379" s="2"/>
       <c r="H379">
         <v>8.8012247838616719E-5</v>
       </c>
@@ -21110,8 +21110,8 @@
       </c>
     </row>
     <row r="380" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B380" s="3"/>
-      <c r="C380" s="3"/>
+      <c r="B380" s="2"/>
+      <c r="C380" s="2"/>
       <c r="H380">
         <v>8.8019884726224789E-5</v>
       </c>
@@ -21120,8 +21120,8 @@
       </c>
     </row>
     <row r="381" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B381" s="3"/>
-      <c r="C381" s="3"/>
+      <c r="B381" s="2"/>
+      <c r="C381" s="2"/>
       <c r="H381">
         <v>8.8025792507204621E-5</v>
       </c>
@@ -21130,8 +21130,8 @@
       </c>
     </row>
     <row r="382" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B382" s="3"/>
-      <c r="C382" s="3"/>
+      <c r="B382" s="2"/>
+      <c r="C382" s="2"/>
       <c r="H382">
         <v>8.803170028818444E-5</v>
       </c>
@@ -21140,8 +21140,8 @@
       </c>
     </row>
     <row r="383" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B383" s="3"/>
-      <c r="C383" s="3"/>
+      <c r="B383" s="2"/>
+      <c r="C383" s="2"/>
       <c r="H383">
         <v>8.8037608069164273E-5</v>
       </c>
@@ -21150,8 +21150,8 @@
       </c>
     </row>
     <row r="384" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B384" s="3"/>
-      <c r="C384" s="3"/>
+      <c r="B384" s="2"/>
+      <c r="C384" s="2"/>
       <c r="H384">
         <v>8.8043515850144092E-5</v>
       </c>
@@ -21160,8 +21160,8 @@
       </c>
     </row>
     <row r="385" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B385" s="3"/>
-      <c r="C385" s="3"/>
+      <c r="B385" s="2"/>
+      <c r="C385" s="2"/>
       <c r="H385">
         <v>8.8049423631123924E-5</v>
       </c>
@@ -21170,8 +21170,8 @@
       </c>
     </row>
     <row r="386" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B386" s="3"/>
-      <c r="C386" s="3"/>
+      <c r="B386" s="2"/>
+      <c r="C386" s="2"/>
       <c r="H386">
         <v>8.8055475504322762E-5</v>
       </c>
@@ -21180,8 +21180,8 @@
       </c>
     </row>
     <row r="387" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B387" s="3"/>
-      <c r="C387" s="3"/>
+      <c r="B387" s="2"/>
+      <c r="C387" s="2"/>
       <c r="H387">
         <v>8.8061959654178683E-5</v>
       </c>
@@ -21190,8 +21190,8 @@
       </c>
     </row>
     <row r="388" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B388" s="3"/>
-      <c r="C388" s="3"/>
+      <c r="B388" s="2"/>
+      <c r="C388" s="2"/>
       <c r="H388">
         <v>8.8068299711815558E-5</v>
       </c>
@@ -21200,8 +21200,8 @@
       </c>
     </row>
     <row r="389" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B389" s="3"/>
-      <c r="C389" s="3"/>
+      <c r="B389" s="2"/>
+      <c r="C389" s="2"/>
       <c r="H389">
         <v>8.8074639769452446E-5</v>
       </c>
@@ -21210,8 +21210,8 @@
       </c>
     </row>
     <row r="390" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B390" s="3"/>
-      <c r="C390" s="3"/>
+      <c r="B390" s="2"/>
+      <c r="C390" s="2"/>
       <c r="H390">
         <v>8.8081123919308353E-5</v>
       </c>
@@ -21220,8 +21220,8 @@
       </c>
     </row>
     <row r="391" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B391" s="3"/>
-      <c r="C391" s="3"/>
+      <c r="B391" s="2"/>
+      <c r="C391" s="2"/>
       <c r="H391">
         <v>8.8087463976945242E-5</v>
       </c>
@@ -21230,8 +21230,8 @@
       </c>
     </row>
     <row r="392" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B392" s="3"/>
-      <c r="C392" s="3"/>
+      <c r="B392" s="2"/>
+      <c r="C392" s="2"/>
       <c r="H392">
         <v>8.809380403458213E-5</v>
       </c>
@@ -21240,8 +21240,8 @@
       </c>
     </row>
     <row r="393" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B393" s="3"/>
-      <c r="C393" s="3"/>
+      <c r="B393" s="2"/>
+      <c r="C393" s="2"/>
       <c r="H393">
         <v>8.8100288184438037E-5</v>
       </c>
@@ -21250,8 +21250,8 @@
       </c>
     </row>
     <row r="394" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B394" s="3"/>
-      <c r="C394" s="3"/>
+      <c r="B394" s="2"/>
+      <c r="C394" s="2"/>
       <c r="H394">
         <v>8.8106628242074926E-5</v>
       </c>
@@ -21260,8 +21260,8 @@
       </c>
     </row>
     <row r="395" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B395" s="3"/>
-      <c r="C395" s="3"/>
+      <c r="B395" s="2"/>
+      <c r="C395" s="2"/>
       <c r="H395">
         <v>8.8112968299711814E-5</v>
       </c>
@@ -21270,8 +21270,8 @@
       </c>
     </row>
     <row r="396" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B396" s="3"/>
-      <c r="C396" s="3"/>
+      <c r="B396" s="2"/>
+      <c r="C396" s="2"/>
       <c r="H396">
         <v>8.8119452449567722E-5</v>
       </c>
@@ -21280,8 +21280,8 @@
       </c>
     </row>
     <row r="397" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B397" s="3"/>
-      <c r="C397" s="3"/>
+      <c r="B397" s="2"/>
+      <c r="C397" s="2"/>
       <c r="H397">
         <v>8.812579250720461E-5</v>
       </c>
@@ -21290,8 +21290,8 @@
       </c>
     </row>
     <row r="398" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B398" s="3"/>
-      <c r="C398" s="3"/>
+      <c r="B398" s="2"/>
+      <c r="C398" s="2"/>
       <c r="H398">
         <v>8.8132132564841499E-5</v>
       </c>
@@ -21300,8 +21300,8 @@
       </c>
     </row>
     <row r="399" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B399" s="3"/>
-      <c r="C399" s="3"/>
+      <c r="B399" s="2"/>
+      <c r="C399" s="2"/>
       <c r="H399">
         <v>8.8138616714697406E-5</v>
       </c>
@@ -21310,8 +21310,8 @@
       </c>
     </row>
     <row r="400" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B400" s="3"/>
-      <c r="C400" s="3"/>
+      <c r="B400" s="2"/>
+      <c r="C400" s="2"/>
       <c r="H400">
         <v>8.8144956772334294E-5</v>
       </c>
@@ -21320,8 +21320,8 @@
       </c>
     </row>
     <row r="401" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B401" s="3"/>
-      <c r="C401" s="3"/>
+      <c r="B401" s="2"/>
+      <c r="C401" s="2"/>
       <c r="H401">
         <v>8.8151296829971183E-5</v>
       </c>
@@ -21330,8 +21330,8 @@
       </c>
     </row>
     <row r="402" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B402" s="3"/>
-      <c r="C402" s="3"/>
+      <c r="B402" s="2"/>
+      <c r="C402" s="2"/>
       <c r="H402">
         <v>8.815778097982709E-5</v>
       </c>
@@ -21340,8 +21340,8 @@
       </c>
     </row>
     <row r="403" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B403" s="3"/>
-      <c r="C403" s="3"/>
+      <c r="B403" s="2"/>
+      <c r="C403" s="2"/>
       <c r="H403">
         <v>8.8164121037463978E-5</v>
       </c>
@@ -21350,8 +21350,8 @@
       </c>
     </row>
     <row r="404" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B404" s="3"/>
-      <c r="C404" s="3"/>
+      <c r="B404" s="2"/>
+      <c r="C404" s="2"/>
       <c r="H404">
         <v>8.8170605187319886E-5</v>
       </c>
@@ -21360,8 +21360,8 @@
       </c>
     </row>
     <row r="405" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B405" s="3"/>
-      <c r="C405" s="3"/>
+      <c r="B405" s="2"/>
+      <c r="C405" s="2"/>
       <c r="H405">
         <v>8.8177089337175793E-5</v>
       </c>
@@ -21370,8 +21370,8 @@
       </c>
     </row>
     <row r="406" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B406" s="3"/>
-      <c r="C406" s="3"/>
+      <c r="B406" s="2"/>
+      <c r="C406" s="2"/>
       <c r="H406">
         <v>8.81835734870317E-5</v>
       </c>
@@ -21380,8 +21380,8 @@
       </c>
     </row>
     <row r="407" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B407" s="3"/>
-      <c r="C407" s="3"/>
+      <c r="B407" s="2"/>
+      <c r="C407" s="2"/>
       <c r="H407">
         <v>8.8190057636887607E-5</v>
       </c>
@@ -21390,8 +21390,8 @@
       </c>
     </row>
     <row r="408" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B408" s="3"/>
-      <c r="C408" s="3"/>
+      <c r="B408" s="2"/>
+      <c r="C408" s="2"/>
       <c r="H408">
         <v>8.8196541786743514E-5</v>
       </c>
@@ -21400,8 +21400,8 @@
       </c>
     </row>
     <row r="409" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B409" s="3"/>
-      <c r="C409" s="3"/>
+      <c r="B409" s="2"/>
+      <c r="C409" s="2"/>
       <c r="H409">
         <v>8.8202881844380403E-5</v>
       </c>
@@ -21410,8 +21410,8 @@
       </c>
     </row>
     <row r="410" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B410" s="3"/>
-      <c r="C410" s="3"/>
+      <c r="B410" s="2"/>
+      <c r="C410" s="2"/>
       <c r="H410">
         <v>8.8209077809798273E-5</v>
       </c>
@@ -21420,8 +21420,8 @@
       </c>
     </row>
     <row r="411" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B411" s="3"/>
-      <c r="C411" s="3"/>
+      <c r="B411" s="2"/>
+      <c r="C411" s="2"/>
       <c r="H411">
         <v>8.8215417867435161E-5</v>
       </c>
@@ -21430,8 +21430,8 @@
       </c>
     </row>
     <row r="412" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B412" s="3"/>
-      <c r="C412" s="3"/>
+      <c r="B412" s="2"/>
+      <c r="C412" s="2"/>
       <c r="H412">
         <v>8.822175792507205E-5</v>
       </c>
@@ -21440,8 +21440,8 @@
       </c>
     </row>
     <row r="413" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B413" s="3"/>
-      <c r="C413" s="3"/>
+      <c r="B413" s="2"/>
+      <c r="C413" s="2"/>
       <c r="H413">
         <v>8.8228097982708938E-5</v>
       </c>
@@ -21450,8 +21450,8 @@
       </c>
     </row>
     <row r="414" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B414" s="3"/>
-      <c r="C414" s="3"/>
+      <c r="B414" s="2"/>
+      <c r="C414" s="2"/>
       <c r="H414">
         <v>8.8234438040345827E-5</v>
       </c>
@@ -21460,8 +21460,8 @@
       </c>
     </row>
     <row r="415" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B415" s="3"/>
-      <c r="C415" s="3"/>
+      <c r="B415" s="2"/>
+      <c r="C415" s="2"/>
       <c r="H415">
         <v>8.8240778097982702E-5</v>
       </c>
@@ -21470,8 +21470,8 @@
       </c>
     </row>
     <row r="416" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B416" s="3"/>
-      <c r="C416" s="3"/>
+      <c r="B416" s="2"/>
+      <c r="C416" s="2"/>
       <c r="H416">
         <v>8.824711815561959E-5</v>
       </c>
@@ -21480,8 +21480,8 @@
       </c>
     </row>
     <row r="417" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B417" s="3"/>
-      <c r="C417" s="3"/>
+      <c r="B417" s="2"/>
+      <c r="C417" s="2"/>
       <c r="H417">
         <v>8.8253458213256492E-5</v>
       </c>
@@ -21490,8 +21490,8 @@
       </c>
     </row>
     <row r="418" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B418" s="3"/>
-      <c r="C418" s="3"/>
+      <c r="B418" s="2"/>
+      <c r="C418" s="2"/>
       <c r="H418">
         <v>8.8259798270893381E-5</v>
       </c>
@@ -21500,8 +21500,8 @@
       </c>
     </row>
     <row r="419" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B419" s="3"/>
-      <c r="C419" s="3"/>
+      <c r="B419" s="2"/>
+      <c r="C419" s="2"/>
       <c r="H419">
         <v>8.8266138328530256E-5</v>
       </c>
@@ -21510,8 +21510,8 @@
       </c>
     </row>
     <row r="420" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B420" s="3"/>
-      <c r="C420" s="3"/>
+      <c r="B420" s="2"/>
+      <c r="C420" s="2"/>
       <c r="H420">
         <v>8.8272478386167144E-5</v>
       </c>
@@ -21520,8 +21520,8 @@
       </c>
     </row>
     <row r="421" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B421" s="3"/>
-      <c r="C421" s="3"/>
+      <c r="B421" s="2"/>
+      <c r="C421" s="2"/>
       <c r="H421">
         <v>8.8278818443804033E-5</v>
       </c>
@@ -21530,8 +21530,8 @@
       </c>
     </row>
     <row r="422" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B422" s="3"/>
-      <c r="C422" s="3"/>
+      <c r="B422" s="2"/>
+      <c r="C422" s="2"/>
       <c r="H422">
         <v>8.8285014409221902E-5</v>
       </c>
@@ -21540,8 +21540,8 @@
       </c>
     </row>
     <row r="423" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B423" s="3"/>
-      <c r="C423" s="3"/>
+      <c r="B423" s="2"/>
+      <c r="C423" s="2"/>
       <c r="H423">
         <v>8.8291354466858791E-5</v>
       </c>
@@ -21550,8 +21550,8 @@
       </c>
     </row>
     <row r="424" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B424" s="3"/>
-      <c r="C424" s="3"/>
+      <c r="B424" s="2"/>
+      <c r="C424" s="2"/>
       <c r="H424">
         <v>8.8297694524495679E-5</v>
       </c>
@@ -21560,8 +21560,8 @@
       </c>
     </row>
     <row r="425" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B425" s="3"/>
-      <c r="C425" s="3"/>
+      <c r="B425" s="2"/>
+      <c r="C425" s="2"/>
       <c r="H425">
         <v>8.8303890489913549E-5</v>
       </c>
@@ -21570,8 +21570,8 @@
       </c>
     </row>
     <row r="426" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B426" s="3"/>
-      <c r="C426" s="3"/>
+      <c r="B426" s="2"/>
+      <c r="C426" s="2"/>
       <c r="H426">
         <v>8.8310230547550438E-5</v>
       </c>
@@ -21580,8 +21580,8 @@
       </c>
     </row>
     <row r="427" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B427" s="3"/>
-      <c r="C427" s="3"/>
+      <c r="B427" s="2"/>
+      <c r="C427" s="2"/>
       <c r="H427">
         <v>8.8316714697406345E-5</v>
       </c>
@@ -21590,8 +21590,8 @@
       </c>
     </row>
     <row r="428" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B428" s="3"/>
-      <c r="C428" s="3"/>
+      <c r="B428" s="2"/>
+      <c r="C428" s="2"/>
       <c r="H428">
         <v>8.8323054755043233E-5</v>
       </c>
@@ -21600,8 +21600,8 @@
       </c>
     </row>
     <row r="429" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B429" s="3"/>
-      <c r="C429" s="3"/>
+      <c r="B429" s="2"/>
+      <c r="C429" s="2"/>
       <c r="H429">
         <v>8.8329394812680108E-5</v>
       </c>
@@ -21610,8 +21610,8 @@
       </c>
     </row>
     <row r="430" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B430" s="3"/>
-      <c r="C430" s="3"/>
+      <c r="B430" s="2"/>
+      <c r="C430" s="2"/>
       <c r="H430">
         <v>8.8335734870316997E-5</v>
       </c>
@@ -21620,8 +21620,8 @@
       </c>
     </row>
     <row r="431" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B431" s="3"/>
-      <c r="C431" s="3"/>
+      <c r="B431" s="2"/>
+      <c r="C431" s="2"/>
       <c r="H431">
         <v>8.8342219020172918E-5</v>
       </c>
@@ -21630,8 +21630,8 @@
       </c>
     </row>
     <row r="432" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B432" s="3"/>
-      <c r="C432" s="3"/>
+      <c r="B432" s="2"/>
+      <c r="C432" s="2"/>
       <c r="H432">
         <v>8.8348559077809793E-5</v>
       </c>
@@ -21640,8 +21640,8 @@
       </c>
     </row>
     <row r="433" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B433" s="3"/>
-      <c r="C433" s="3"/>
+      <c r="B433" s="2"/>
+      <c r="C433" s="2"/>
       <c r="H433">
         <v>8.8354899135446681E-5</v>
       </c>
@@ -21650,8 +21650,8 @@
       </c>
     </row>
     <row r="434" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B434" s="3"/>
-      <c r="C434" s="3"/>
+      <c r="B434" s="2"/>
+      <c r="C434" s="2"/>
       <c r="H434">
         <v>8.8361095100864551E-5</v>
       </c>
@@ -21660,8 +21660,8 @@
       </c>
     </row>
     <row r="435" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B435" s="3"/>
-      <c r="C435" s="3"/>
+      <c r="B435" s="2"/>
+      <c r="C435" s="2"/>
       <c r="H435">
         <v>8.8367291066282421E-5</v>
       </c>
@@ -21670,8 +21670,8 @@
       </c>
     </row>
     <row r="436" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B436" s="3"/>
-      <c r="C436" s="3"/>
+      <c r="B436" s="2"/>
+      <c r="C436" s="2"/>
       <c r="H436">
         <v>8.8373487031700291E-5</v>
       </c>
@@ -21680,8 +21680,8 @@
       </c>
     </row>
     <row r="437" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B437" s="3"/>
-      <c r="C437" s="3"/>
+      <c r="B437" s="2"/>
+      <c r="C437" s="2"/>
       <c r="H437">
         <v>8.837968299711816E-5</v>
       </c>
@@ -21690,8 +21690,8 @@
       </c>
     </row>
     <row r="438" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B438" s="3"/>
-      <c r="C438" s="3"/>
+      <c r="B438" s="2"/>
+      <c r="C438" s="2"/>
       <c r="H438">
         <v>8.8385878962536017E-5</v>
       </c>
@@ -21700,8 +21700,8 @@
       </c>
     </row>
     <row r="439" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B439" s="3"/>
-      <c r="C439" s="3"/>
+      <c r="B439" s="2"/>
+      <c r="C439" s="2"/>
       <c r="H439">
         <v>8.8392074927953887E-5</v>
       </c>
@@ -21710,8 +21710,8 @@
       </c>
     </row>
     <row r="440" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B440" s="3"/>
-      <c r="C440" s="3"/>
+      <c r="B440" s="2"/>
+      <c r="C440" s="2"/>
       <c r="H440">
         <v>8.8398270893371756E-5</v>
       </c>
@@ -21720,8 +21720,8 @@
       </c>
     </row>
     <row r="441" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B441" s="3"/>
-      <c r="C441" s="3"/>
+      <c r="B441" s="2"/>
+      <c r="C441" s="2"/>
       <c r="H441">
         <v>8.8404466858789626E-5</v>
       </c>
@@ -21730,8 +21730,8 @@
       </c>
     </row>
     <row r="442" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B442" s="3"/>
-      <c r="C442" s="3"/>
+      <c r="B442" s="2"/>
+      <c r="C442" s="2"/>
       <c r="H442">
         <v>8.8410662824207496E-5</v>
       </c>
@@ -21740,8 +21740,8 @@
       </c>
     </row>
     <row r="443" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B443" s="3"/>
-      <c r="C443" s="3"/>
+      <c r="B443" s="2"/>
+      <c r="C443" s="2"/>
       <c r="H443">
         <v>8.8416858789625366E-5</v>
       </c>
@@ -21750,8 +21750,8 @@
       </c>
     </row>
     <row r="444" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B444" s="3"/>
-      <c r="C444" s="3"/>
+      <c r="B444" s="2"/>
+      <c r="C444" s="2"/>
       <c r="H444">
         <v>8.8423054755043222E-5</v>
       </c>
@@ -21760,8 +21760,8 @@
       </c>
     </row>
     <row r="445" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B445" s="3"/>
-      <c r="C445" s="3"/>
+      <c r="B445" s="2"/>
+      <c r="C445" s="2"/>
       <c r="H445">
         <v>8.8429250720461092E-5</v>
       </c>
@@ -21770,8 +21770,8 @@
       </c>
     </row>
     <row r="446" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B446" s="3"/>
-      <c r="C446" s="3"/>
+      <c r="B446" s="2"/>
+      <c r="C446" s="2"/>
       <c r="H446">
         <v>8.8435446685878962E-5</v>
       </c>
@@ -21780,8 +21780,8 @@
       </c>
     </row>
     <row r="447" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B447" s="3"/>
-      <c r="C447" s="3"/>
+      <c r="B447" s="2"/>
+      <c r="C447" s="2"/>
       <c r="H447">
         <v>8.8441642651296832E-5</v>
       </c>
@@ -21790,8 +21790,8 @@
       </c>
     </row>
     <row r="448" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B448" s="3"/>
-      <c r="C448" s="3"/>
+      <c r="B448" s="2"/>
+      <c r="C448" s="2"/>
       <c r="H448">
         <v>8.8447982708933707E-5</v>
       </c>
@@ -21800,8 +21800,8 @@
       </c>
     </row>
     <row r="449" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B449" s="3"/>
-      <c r="C449" s="3"/>
+      <c r="B449" s="2"/>
+      <c r="C449" s="2"/>
       <c r="H449">
         <v>8.845417867435159E-5</v>
       </c>
@@ -21810,8 +21810,8 @@
       </c>
     </row>
     <row r="450" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B450" s="3"/>
-      <c r="C450" s="3"/>
+      <c r="B450" s="2"/>
+      <c r="C450" s="2"/>
       <c r="H450">
         <v>8.846037463976946E-5</v>
       </c>
@@ -21820,8 +21820,8 @@
       </c>
     </row>
     <row r="451" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B451" s="3"/>
-      <c r="C451" s="3"/>
+      <c r="B451" s="2"/>
+      <c r="C451" s="2"/>
       <c r="H451">
         <v>8.8466570605187316E-5</v>
       </c>
@@ -21830,8 +21830,8 @@
       </c>
     </row>
     <row r="452" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B452" s="3"/>
-      <c r="C452" s="3"/>
+      <c r="B452" s="2"/>
+      <c r="C452" s="2"/>
       <c r="H452">
         <v>8.8472766570605186E-5</v>
       </c>
@@ -21840,8 +21840,8 @@
       </c>
     </row>
     <row r="453" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B453" s="3"/>
-      <c r="C453" s="3"/>
+      <c r="B453" s="2"/>
+      <c r="C453" s="2"/>
       <c r="H453">
         <v>8.8478962536023056E-5</v>
       </c>
@@ -21850,8 +21850,8 @@
       </c>
     </row>
     <row r="454" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B454" s="3"/>
-      <c r="C454" s="3"/>
+      <c r="B454" s="2"/>
+      <c r="C454" s="2"/>
       <c r="H454">
         <v>8.8485014409221907E-5</v>
       </c>
@@ -21860,8 +21860,8 @@
       </c>
     </row>
     <row r="455" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B455" s="3"/>
-      <c r="C455" s="3"/>
+      <c r="B455" s="2"/>
+      <c r="C455" s="2"/>
       <c r="H455">
         <v>8.8491210374639764E-5</v>
       </c>
@@ -21870,8 +21870,8 @@
       </c>
     </row>
     <row r="456" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B456" s="3"/>
-      <c r="C456" s="3"/>
+      <c r="B456" s="2"/>
+      <c r="C456" s="2"/>
       <c r="H456">
         <v>8.8497262247838615E-5</v>
       </c>
@@ -21880,8 +21880,8 @@
       </c>
     </row>
     <row r="457" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B457" s="3"/>
-      <c r="C457" s="3"/>
+      <c r="B457" s="2"/>
+      <c r="C457" s="2"/>
       <c r="H457">
         <v>8.8503458213256485E-5</v>
       </c>
@@ -21890,8 +21890,8 @@
       </c>
     </row>
     <row r="458" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B458" s="3"/>
-      <c r="C458" s="3"/>
+      <c r="B458" s="2"/>
+      <c r="C458" s="2"/>
       <c r="H458">
         <v>8.8509654178674354E-5</v>
       </c>
@@ -21900,8 +21900,8 @@
       </c>
     </row>
     <row r="459" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B459" s="3"/>
-      <c r="C459" s="3"/>
+      <c r="B459" s="2"/>
+      <c r="C459" s="2"/>
       <c r="H459">
         <v>8.8515706051873206E-5</v>
       </c>
@@ -21910,8 +21910,8 @@
       </c>
     </row>
     <row r="460" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B460" s="3"/>
-      <c r="C460" s="3"/>
+      <c r="B460" s="2"/>
+      <c r="C460" s="2"/>
       <c r="H460">
         <v>8.8521902017291062E-5</v>
       </c>
@@ -21920,8 +21920,8 @@
       </c>
     </row>
     <row r="461" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B461" s="3"/>
-      <c r="C461" s="3"/>
+      <c r="B461" s="2"/>
+      <c r="C461" s="2"/>
       <c r="H461">
         <v>8.8527953890489913E-5</v>
       </c>
@@ -21930,8 +21930,8 @@
       </c>
     </row>
     <row r="462" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B462" s="3"/>
-      <c r="C462" s="3"/>
+      <c r="B462" s="2"/>
+      <c r="C462" s="2"/>
       <c r="H462">
         <v>8.8534149855907783E-5</v>
       </c>
@@ -21940,8 +21940,8 @@
       </c>
     </row>
     <row r="463" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B463" s="3"/>
-      <c r="C463" s="3"/>
+      <c r="B463" s="2"/>
+      <c r="C463" s="2"/>
       <c r="H463">
         <v>8.8540345821325653E-5</v>
       </c>
@@ -21950,8 +21950,8 @@
       </c>
     </row>
     <row r="464" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B464" s="3"/>
-      <c r="C464" s="3"/>
+      <c r="B464" s="2"/>
+      <c r="C464" s="2"/>
       <c r="H464">
         <v>8.8546397694524491E-5</v>
       </c>
@@ -21960,8 +21960,8 @@
       </c>
     </row>
     <row r="465" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B465" s="3"/>
-      <c r="C465" s="3"/>
+      <c r="B465" s="2"/>
+      <c r="C465" s="2"/>
       <c r="H465">
         <v>8.8552593659942374E-5</v>
       </c>
@@ -21970,8 +21970,8 @@
       </c>
     </row>
     <row r="466" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B466" s="3"/>
-      <c r="C466" s="3"/>
+      <c r="B466" s="2"/>
+      <c r="C466" s="2"/>
       <c r="H466">
         <v>8.855878962536023E-5</v>
       </c>
@@ -21980,8 +21980,8 @@
       </c>
     </row>
     <row r="467" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B467" s="3"/>
-      <c r="C467" s="3"/>
+      <c r="B467" s="2"/>
+      <c r="C467" s="2"/>
       <c r="H467">
         <v>8.8564841498559068E-5</v>
       </c>
@@ -21990,8 +21990,8 @@
       </c>
     </row>
     <row r="468" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B468" s="3"/>
-      <c r="C468" s="3"/>
+      <c r="B468" s="2"/>
+      <c r="C468" s="2"/>
       <c r="H468">
         <v>8.8571037463976938E-5</v>
       </c>
@@ -22000,8 +22000,8 @@
       </c>
     </row>
     <row r="469" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B469" s="3"/>
-      <c r="C469" s="3"/>
+      <c r="B469" s="2"/>
+      <c r="C469" s="2"/>
       <c r="H469">
         <v>8.8577233429394821E-5</v>
       </c>
@@ -22010,8 +22010,8 @@
       </c>
     </row>
     <row r="470" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B470" s="3"/>
-      <c r="C470" s="3"/>
+      <c r="B470" s="2"/>
+      <c r="C470" s="2"/>
       <c r="H470">
         <v>8.8583285302593659E-5</v>
       </c>
@@ -22020,8 +22020,8 @@
       </c>
     </row>
     <row r="471" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B471" s="3"/>
-      <c r="C471" s="3"/>
+      <c r="B471" s="2"/>
+      <c r="C471" s="2"/>
       <c r="H471">
         <v>8.8589481268011529E-5</v>
       </c>
@@ -22030,8 +22030,8 @@
       </c>
     </row>
     <row r="472" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B472" s="3"/>
-      <c r="C472" s="3"/>
+      <c r="B472" s="2"/>
+      <c r="C472" s="2"/>
       <c r="H472">
         <v>8.859553314121038E-5</v>
       </c>
@@ -22040,8 +22040,8 @@
       </c>
     </row>
     <row r="473" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B473" s="3"/>
-      <c r="C473" s="3"/>
+      <c r="B473" s="2"/>
+      <c r="C473" s="2"/>
       <c r="H473">
         <v>8.8601585014409231E-5</v>
       </c>
@@ -22050,8 +22050,8 @@
       </c>
     </row>
     <row r="474" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B474" s="3"/>
-      <c r="C474" s="3"/>
+      <c r="B474" s="2"/>
+      <c r="C474" s="2"/>
       <c r="H474">
         <v>8.8607636887608069E-5</v>
       </c>
@@ -22060,8 +22060,8 @@
       </c>
     </row>
     <row r="475" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B475" s="3"/>
-      <c r="C475" s="3"/>
+      <c r="B475" s="2"/>
+      <c r="C475" s="2"/>
       <c r="H475">
         <v>8.861368876080692E-5</v>
       </c>
@@ -22070,8 +22070,8 @@
       </c>
     </row>
     <row r="476" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B476" s="3"/>
-      <c r="C476" s="3"/>
+      <c r="B476" s="2"/>
+      <c r="C476" s="2"/>
       <c r="H476">
         <v>8.8620028818443808E-5</v>
       </c>
@@ -22080,8 +22080,8 @@
       </c>
     </row>
     <row r="477" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B477" s="3"/>
-      <c r="C477" s="3"/>
+      <c r="B477" s="2"/>
+      <c r="C477" s="2"/>
       <c r="H477">
         <v>8.8626657060518734E-5</v>
       </c>
@@ -22090,8 +22090,8 @@
       </c>
     </row>
     <row r="478" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B478" s="3"/>
-      <c r="C478" s="3"/>
+      <c r="B478" s="2"/>
+      <c r="C478" s="2"/>
       <c r="H478">
         <v>8.8633141210374641E-5</v>
       </c>
@@ -22100,8 +22100,8 @@
       </c>
     </row>
     <row r="479" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B479" s="3"/>
-      <c r="C479" s="3"/>
+      <c r="B479" s="2"/>
+      <c r="C479" s="2"/>
       <c r="H479">
         <v>8.8640057636887604E-5</v>
       </c>
@@ -22110,8 +22110,8 @@
       </c>
     </row>
     <row r="480" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B480" s="3"/>
-      <c r="C480" s="3"/>
+      <c r="B480" s="2"/>
+      <c r="C480" s="2"/>
       <c r="H480">
         <v>8.8646829971181562E-5</v>
       </c>
@@ -22120,8 +22120,8 @@
       </c>
     </row>
     <row r="481" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B481" s="3"/>
-      <c r="C481" s="3"/>
+      <c r="B481" s="2"/>
+      <c r="C481" s="2"/>
       <c r="H481">
         <v>8.8653602305475507E-5</v>
       </c>
@@ -22130,8 +22130,8 @@
       </c>
     </row>
     <row r="482" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B482" s="3"/>
-      <c r="C482" s="3"/>
+      <c r="B482" s="2"/>
+      <c r="C482" s="2"/>
       <c r="H482">
         <v>8.866051873198847E-5</v>
       </c>
@@ -22140,8 +22140,8 @@
       </c>
     </row>
     <row r="483" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B483" s="3"/>
-      <c r="C483" s="3"/>
+      <c r="B483" s="2"/>
+      <c r="C483" s="2"/>
       <c r="H483">
         <v>8.8667146974063396E-5</v>
       </c>
@@ -22150,8 +22150,8 @@
       </c>
     </row>
     <row r="484" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B484" s="3"/>
-      <c r="C484" s="3"/>
+      <c r="B484" s="2"/>
+      <c r="C484" s="2"/>
       <c r="H484">
         <v>8.8673775216138322E-5</v>
       </c>
@@ -22160,8 +22160,8 @@
       </c>
     </row>
     <row r="485" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B485" s="3"/>
-      <c r="C485" s="3"/>
+      <c r="B485" s="2"/>
+      <c r="C485" s="2"/>
       <c r="H485">
         <v>8.868054755043228E-5</v>
       </c>
@@ -22170,8 +22170,8 @@
       </c>
     </row>
     <row r="486" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B486" s="3"/>
-      <c r="C486" s="3"/>
+      <c r="B486" s="2"/>
+      <c r="C486" s="2"/>
       <c r="H486">
         <v>8.8687175792507206E-5</v>
       </c>
@@ -22180,8 +22180,8 @@
       </c>
     </row>
     <row r="487" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B487" s="3"/>
-      <c r="C487" s="3"/>
+      <c r="B487" s="2"/>
+      <c r="C487" s="2"/>
       <c r="H487">
         <v>8.8693804034582131E-5</v>
       </c>
@@ -22190,8 +22190,8 @@
       </c>
     </row>
     <row r="488" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B488" s="3"/>
-      <c r="C488" s="3"/>
+      <c r="B488" s="2"/>
+      <c r="C488" s="2"/>
       <c r="H488">
         <v>8.8700288184438038E-5</v>
       </c>
@@ -22200,8 +22200,8 @@
       </c>
     </row>
     <row r="489" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B489" s="3"/>
-      <c r="C489" s="3"/>
+      <c r="B489" s="2"/>
+      <c r="C489" s="2"/>
       <c r="H489">
         <v>8.8706772334293946E-5</v>
       </c>
@@ -22210,8 +22210,8 @@
       </c>
     </row>
     <row r="490" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B490" s="3"/>
-      <c r="C490" s="3"/>
+      <c r="B490" s="2"/>
+      <c r="C490" s="2"/>
       <c r="H490">
         <v>8.8713112391930834E-5</v>
       </c>
@@ -22220,8 +22220,8 @@
       </c>
     </row>
     <row r="491" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B491" s="3"/>
-      <c r="C491" s="3"/>
+      <c r="B491" s="2"/>
+      <c r="C491" s="2"/>
       <c r="H491">
         <v>8.8719596541786741E-5</v>
       </c>
@@ -22230,8 +22230,8 @@
       </c>
     </row>
     <row r="492" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B492" s="3"/>
-      <c r="C492" s="3"/>
+      <c r="B492" s="2"/>
+      <c r="C492" s="2"/>
       <c r="H492">
         <v>8.8726080691642662E-5</v>
       </c>
@@ -22240,8 +22240,8 @@
       </c>
     </row>
     <row r="493" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B493" s="3"/>
-      <c r="C493" s="3"/>
+      <c r="B493" s="2"/>
+      <c r="C493" s="2"/>
       <c r="H493">
         <v>8.8732564841498556E-5</v>
       </c>
@@ -22250,8 +22250,8 @@
       </c>
     </row>
     <row r="494" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B494" s="3"/>
-      <c r="C494" s="3"/>
+      <c r="B494" s="2"/>
+      <c r="C494" s="2"/>
       <c r="H494">
         <v>8.8738904899135444E-5</v>
       </c>
@@ -22260,8 +22260,8 @@
       </c>
     </row>
     <row r="495" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B495" s="3"/>
-      <c r="C495" s="3"/>
+      <c r="B495" s="2"/>
+      <c r="C495" s="2"/>
       <c r="H495">
         <v>8.8745389048991351E-5</v>
       </c>
@@ -22270,8 +22270,8 @@
       </c>
     </row>
     <row r="496" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B496" s="3"/>
-      <c r="C496" s="3"/>
+      <c r="B496" s="2"/>
+      <c r="C496" s="2"/>
       <c r="H496">
         <v>8.8751873198847258E-5</v>
       </c>
@@ -22280,8 +22280,8 @@
       </c>
     </row>
     <row r="497" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B497" s="3"/>
-      <c r="C497" s="3"/>
+      <c r="B497" s="2"/>
+      <c r="C497" s="2"/>
       <c r="H497">
         <v>8.8758645533141216E-5</v>
       </c>
@@ -22290,8 +22290,8 @@
       </c>
     </row>
     <row r="498" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B498" s="3"/>
-      <c r="C498" s="3"/>
+      <c r="B498" s="2"/>
+      <c r="C498" s="2"/>
       <c r="H498">
         <v>8.876556195965418E-5</v>
       </c>
@@ -22300,8 +22300,8 @@
       </c>
     </row>
     <row r="499" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B499" s="3"/>
-      <c r="C499" s="3"/>
+      <c r="B499" s="2"/>
+      <c r="C499" s="2"/>
       <c r="H499">
         <v>8.8772478386167143E-5</v>
       </c>
@@ -22310,8 +22310,8 @@
       </c>
     </row>
     <row r="500" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B500" s="3"/>
-      <c r="C500" s="3"/>
+      <c r="B500" s="2"/>
+      <c r="C500" s="2"/>
       <c r="H500">
         <v>8.8779250720461101E-5</v>
       </c>
@@ -22320,8 +22320,8 @@
       </c>
     </row>
     <row r="501" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B501" s="3"/>
-      <c r="C501" s="3"/>
+      <c r="B501" s="2"/>
+      <c r="C501" s="2"/>
       <c r="H501">
         <v>8.8786599423631133E-5</v>
       </c>
@@ -22330,8 +22330,8 @@
       </c>
     </row>
     <row r="502" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B502" s="3"/>
-      <c r="C502" s="3"/>
+      <c r="B502" s="2"/>
+      <c r="C502" s="2"/>
       <c r="H502">
         <v>8.8793948126801152E-5</v>
       </c>
@@ -22340,8 +22340,8 @@
       </c>
     </row>
     <row r="503" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B503" s="3"/>
-      <c r="C503" s="3"/>
+      <c r="B503" s="2"/>
+      <c r="C503" s="2"/>
       <c r="H503">
         <v>8.8801440922190204E-5</v>
       </c>
